--- a/Historial_Facturas_2026.xlsx
+++ b/Historial_Facturas_2026.xlsx
@@ -21,7 +21,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="$#,##0"/>
   </numFmts>
-  <fonts count="3">
+  <fonts count="4">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -38,6 +38,12 @@
       <name val="Calibri"/>
       <color rgb="000563C1"/>
       <sz val="11"/>
+      <u val="single"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <color rgb="000563C1"/>
+      <sz val="10"/>
       <u val="single"/>
     </font>
   </fonts>
@@ -82,7 +88,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="12">
+  <cellXfs count="14">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -115,6 +121,12 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -575,7 +587,7 @@
           <t>Arriendo</t>
         </is>
       </c>
-      <c r="F2" s="10" t="inlineStr">
+      <c r="F2" s="12" t="inlineStr">
         <is>
           <t>F-14015</t>
         </is>
@@ -625,7 +637,7 @@
           <t>Serv. Admin</t>
         </is>
       </c>
-      <c r="F3" s="11" t="inlineStr">
+      <c r="F3" s="13" t="inlineStr">
         <is>
           <t>FEE-14106</t>
         </is>
@@ -673,7 +685,7 @@
           <t>Serv. Admin</t>
         </is>
       </c>
-      <c r="F4" s="10" t="inlineStr">
+      <c r="F4" s="12" t="inlineStr">
         <is>
           <t>FEE-14094</t>
         </is>
@@ -721,7 +733,7 @@
           <t>Serv. Admin</t>
         </is>
       </c>
-      <c r="F5" s="11" t="inlineStr">
+      <c r="F5" s="13" t="inlineStr">
         <is>
           <t>FEE-14104</t>
         </is>
@@ -769,7 +781,7 @@
           <t>Serv. Admin</t>
         </is>
       </c>
-      <c r="F6" s="10" t="inlineStr">
+      <c r="F6" s="12" t="inlineStr">
         <is>
           <t>FEE-14122</t>
         </is>
@@ -817,7 +829,7 @@
           <t>Serv. Admin</t>
         </is>
       </c>
-      <c r="F7" s="11" t="inlineStr">
+      <c r="F7" s="13" t="inlineStr">
         <is>
           <t>FEE-14103</t>
         </is>
@@ -865,7 +877,7 @@
           <t>Serv. Admin</t>
         </is>
       </c>
-      <c r="F8" s="10" t="inlineStr">
+      <c r="F8" s="12" t="inlineStr">
         <is>
           <t>FEE-14096</t>
         </is>
@@ -913,7 +925,7 @@
           <t>Arriendo</t>
         </is>
       </c>
-      <c r="F9" s="11" t="inlineStr">
+      <c r="F9" s="13" t="inlineStr">
         <is>
           <t>F-14034</t>
         </is>
@@ -961,7 +973,7 @@
           <t>Arriendo</t>
         </is>
       </c>
-      <c r="F10" s="11" t="inlineStr">
+      <c r="F10" s="13" t="inlineStr">
         <is>
           <t>F-14035</t>
         </is>
@@ -1009,7 +1021,7 @@
           <t>Arriendo</t>
         </is>
       </c>
-      <c r="F11" s="11" t="inlineStr">
+      <c r="F11" s="13" t="inlineStr">
         <is>
           <t>F-14050</t>
         </is>
@@ -1057,7 +1069,7 @@
           <t>Arriendo</t>
         </is>
       </c>
-      <c r="F12" s="10" t="inlineStr">
+      <c r="F12" s="12" t="inlineStr">
         <is>
           <t>F-14041</t>
         </is>
@@ -1101,7 +1113,7 @@
           <t>Arriendo</t>
         </is>
       </c>
-      <c r="F13" s="11" t="inlineStr">
+      <c r="F13" s="13" t="inlineStr">
         <is>
           <t>F-14047</t>
         </is>
@@ -1149,7 +1161,7 @@
           <t>Arriendo</t>
         </is>
       </c>
-      <c r="F14" s="10" t="inlineStr">
+      <c r="F14" s="12" t="inlineStr">
         <is>
           <t>F-14043</t>
         </is>
@@ -1197,7 +1209,7 @@
           <t>Arriendo</t>
         </is>
       </c>
-      <c r="F15" s="11" t="inlineStr">
+      <c r="F15" s="13" t="inlineStr">
         <is>
           <t>F-14039</t>
         </is>
@@ -1245,7 +1257,7 @@
           <t>Arriendo</t>
         </is>
       </c>
-      <c r="F16" s="10" t="inlineStr">
+      <c r="F16" s="12" t="inlineStr">
         <is>
           <t>F-14040</t>
         </is>
@@ -1293,7 +1305,7 @@
           <t>Arriendo</t>
         </is>
       </c>
-      <c r="F17" s="10" t="inlineStr">
+      <c r="F17" s="12" t="inlineStr">
         <is>
           <t>F-14130</t>
         </is>
@@ -1341,7 +1353,7 @@
           <t>Arriendo</t>
         </is>
       </c>
-      <c r="F18" s="11" t="inlineStr">
+      <c r="F18" s="13" t="inlineStr">
         <is>
           <t>F-14038</t>
         </is>
@@ -1389,7 +1401,7 @@
           <t>Arriendo</t>
         </is>
       </c>
-      <c r="F19" s="10" t="inlineStr">
+      <c r="F19" s="12" t="inlineStr">
         <is>
           <t>F-14042</t>
         </is>
@@ -1437,7 +1449,7 @@
           <t>Arriendo</t>
         </is>
       </c>
-      <c r="F20" s="11" t="inlineStr">
+      <c r="F20" s="13" t="inlineStr">
         <is>
           <t>F-14045</t>
         </is>
@@ -1485,7 +1497,7 @@
           <t>Arriendo</t>
         </is>
       </c>
-      <c r="F21" s="10" t="inlineStr">
+      <c r="F21" s="12" t="inlineStr">
         <is>
           <t>F-14051</t>
         </is>
@@ -1533,7 +1545,7 @@
           <t>Arriendo</t>
         </is>
       </c>
-      <c r="F22" s="11" t="inlineStr">
+      <c r="F22" s="13" t="inlineStr">
         <is>
           <t>F-14036</t>
         </is>
@@ -1581,7 +1593,7 @@
           <t>Arriendo</t>
         </is>
       </c>
-      <c r="F23" s="11" t="inlineStr">
+      <c r="F23" s="13" t="inlineStr">
         <is>
           <t>F-14037</t>
         </is>
@@ -1629,7 +1641,7 @@
           <t>Arriendo</t>
         </is>
       </c>
-      <c r="F24" s="10" t="inlineStr">
+      <c r="F24" s="12" t="inlineStr">
         <is>
           <t>F-14048</t>
         </is>
@@ -1677,7 +1689,7 @@
           <t>Arriendo</t>
         </is>
       </c>
-      <c r="F25" s="10" t="inlineStr">
+      <c r="F25" s="12" t="inlineStr">
         <is>
           <t>F-14049</t>
         </is>
@@ -1725,7 +1737,7 @@
           <t>Arriendo</t>
         </is>
       </c>
-      <c r="F26" s="11" t="inlineStr">
+      <c r="F26" s="13" t="inlineStr">
         <is>
           <t>F-14044</t>
         </is>
@@ -1773,7 +1785,7 @@
           <t>Arriendo</t>
         </is>
       </c>
-      <c r="F27" s="10" t="inlineStr">
+      <c r="F27" s="12" t="inlineStr">
         <is>
           <t>F-14046</t>
         </is>
@@ -1821,7 +1833,7 @@
           <t>Serv. Admin</t>
         </is>
       </c>
-      <c r="F28" s="11" t="inlineStr">
+      <c r="F28" s="13" t="inlineStr">
         <is>
           <t>FEE-14098</t>
         </is>
@@ -1869,7 +1881,7 @@
           <t>Serv. Mant.</t>
         </is>
       </c>
-      <c r="F29" s="10" t="inlineStr">
+      <c r="F29" s="12" t="inlineStr">
         <is>
           <t>F-14124</t>
         </is>
@@ -1915,7 +1927,7 @@
           <t>Serv. Admin</t>
         </is>
       </c>
-      <c r="F30" s="11" t="inlineStr">
+      <c r="F30" s="13" t="inlineStr">
         <is>
           <t>FEE-14099</t>
         </is>
@@ -1963,7 +1975,7 @@
           <t>Serv. Admin</t>
         </is>
       </c>
-      <c r="F31" s="10" t="inlineStr">
+      <c r="F31" s="12" t="inlineStr">
         <is>
           <t>FEE-14093</t>
         </is>
@@ -2011,7 +2023,7 @@
           <t>Serv. Admin</t>
         </is>
       </c>
-      <c r="F32" s="11" t="inlineStr">
+      <c r="F32" s="13" t="inlineStr">
         <is>
           <t>FEE-14102</t>
         </is>
@@ -2059,7 +2071,7 @@
           <t>Serv. Admin</t>
         </is>
       </c>
-      <c r="F33" s="10" t="inlineStr">
+      <c r="F33" s="12" t="inlineStr">
         <is>
           <t>FEE-14107</t>
         </is>
@@ -2107,7 +2119,7 @@
           <t>Serv. Admin</t>
         </is>
       </c>
-      <c r="F34" s="11" t="inlineStr">
+      <c r="F34" s="13" t="inlineStr">
         <is>
           <t>FEE-14121</t>
         </is>
@@ -2155,7 +2167,7 @@
           <t>Serv. Admin</t>
         </is>
       </c>
-      <c r="F35" s="11" t="inlineStr">
+      <c r="F35" s="13" t="inlineStr">
         <is>
           <t>FEE-14131</t>
         </is>
@@ -2203,7 +2215,7 @@
           <t>Serv. Admin</t>
         </is>
       </c>
-      <c r="F36" s="10" t="inlineStr">
+      <c r="F36" s="12" t="inlineStr">
         <is>
           <t>FEE-14119</t>
         </is>
@@ -2251,7 +2263,7 @@
           <t>Serv. Admin</t>
         </is>
       </c>
-      <c r="F37" s="11" t="inlineStr">
+      <c r="F37" s="13" t="inlineStr">
         <is>
           <t>FEE-14100</t>
         </is>
@@ -2299,7 +2311,7 @@
           <t>Serv. Admin</t>
         </is>
       </c>
-      <c r="F38" s="10" t="inlineStr">
+      <c r="F38" s="12" t="inlineStr">
         <is>
           <t>FEE-14111</t>
         </is>
@@ -2343,7 +2355,7 @@
           <t>Serv. Admin</t>
         </is>
       </c>
-      <c r="F39" s="11" t="inlineStr">
+      <c r="F39" s="13" t="inlineStr">
         <is>
           <t>FEE-14108</t>
         </is>
@@ -2391,7 +2403,7 @@
           <t>Arriendo</t>
         </is>
       </c>
-      <c r="F40" s="10" t="inlineStr">
+      <c r="F40" s="12" t="inlineStr">
         <is>
           <t>F-14126</t>
         </is>
@@ -2439,7 +2451,7 @@
           <t>Serv. Admin</t>
         </is>
       </c>
-      <c r="F41" s="10" t="inlineStr">
+      <c r="F41" s="12" t="inlineStr">
         <is>
           <t>FEE-14114</t>
         </is>
@@ -2487,7 +2499,7 @@
           <t>Serv. Admin</t>
         </is>
       </c>
-      <c r="F42" s="11" t="inlineStr">
+      <c r="F42" s="13" t="inlineStr">
         <is>
           <t>FEE-14116</t>
         </is>
@@ -2535,7 +2547,7 @@
           <t>Arriendo</t>
         </is>
       </c>
-      <c r="F43" s="10" t="inlineStr">
+      <c r="F43" s="12" t="inlineStr">
         <is>
           <t>F-14033</t>
         </is>
@@ -2583,7 +2595,7 @@
           <t>Arriendo</t>
         </is>
       </c>
-      <c r="F44" s="11" t="inlineStr">
+      <c r="F44" s="13" t="inlineStr">
         <is>
           <t>F-14018</t>
         </is>
@@ -2631,7 +2643,7 @@
           <t>Arriendo</t>
         </is>
       </c>
-      <c r="F45" s="10" t="inlineStr">
+      <c r="F45" s="12" t="inlineStr">
         <is>
           <t>F-14029</t>
         </is>
@@ -2679,7 +2691,7 @@
           <t>Arriendo</t>
         </is>
       </c>
-      <c r="F46" s="11" t="inlineStr">
+      <c r="F46" s="13" t="inlineStr">
         <is>
           <t>F-14032</t>
         </is>
@@ -2727,7 +2739,7 @@
           <t>Arriendo</t>
         </is>
       </c>
-      <c r="F47" s="10" t="inlineStr">
+      <c r="F47" s="12" t="inlineStr">
         <is>
           <t>F-14019</t>
         </is>
@@ -2775,7 +2787,7 @@
           <t>Arriendo</t>
         </is>
       </c>
-      <c r="F48" s="11" t="inlineStr">
+      <c r="F48" s="13" t="inlineStr">
         <is>
           <t>F-14021</t>
         </is>
@@ -2823,7 +2835,7 @@
           <t>Arriendo</t>
         </is>
       </c>
-      <c r="F49" s="10" t="inlineStr">
+      <c r="F49" s="12" t="inlineStr">
         <is>
           <t>F-14017</t>
         </is>
@@ -2871,7 +2883,7 @@
           <t>Arriendo</t>
         </is>
       </c>
-      <c r="F50" s="11" t="inlineStr">
+      <c r="F50" s="13" t="inlineStr">
         <is>
           <t>F-14022</t>
         </is>
@@ -2919,7 +2931,7 @@
           <t>Arriendo</t>
         </is>
       </c>
-      <c r="F51" s="10" t="inlineStr">
+      <c r="F51" s="12" t="inlineStr">
         <is>
           <t>F-14010</t>
         </is>
@@ -2967,7 +2979,7 @@
           <t>Arriendo</t>
         </is>
       </c>
-      <c r="F52" s="10" t="inlineStr">
+      <c r="F52" s="12" t="inlineStr">
         <is>
           <t>F-14011</t>
         </is>
@@ -3015,7 +3027,7 @@
           <t>Arriendo</t>
         </is>
       </c>
-      <c r="F53" s="10" t="inlineStr">
+      <c r="F53" s="12" t="inlineStr">
         <is>
           <t>F-14012</t>
         </is>
@@ -3063,7 +3075,7 @@
           <t>Arriendo</t>
         </is>
       </c>
-      <c r="F54" s="11" t="inlineStr">
+      <c r="F54" s="13" t="inlineStr">
         <is>
           <t>F-14025</t>
         </is>
@@ -3111,7 +3123,7 @@
           <t>Arriendo</t>
         </is>
       </c>
-      <c r="F55" s="10" t="inlineStr">
+      <c r="F55" s="12" t="inlineStr">
         <is>
           <t>F-14016</t>
         </is>
@@ -3159,7 +3171,7 @@
           <t>Arriendo</t>
         </is>
       </c>
-      <c r="F56" s="11" t="inlineStr">
+      <c r="F56" s="13" t="inlineStr">
         <is>
           <t>F-14030</t>
         </is>
@@ -3207,7 +3219,7 @@
           <t>Arriendo</t>
         </is>
       </c>
-      <c r="F57" s="10" t="inlineStr">
+      <c r="F57" s="12" t="inlineStr">
         <is>
           <t>F-14020</t>
         </is>
@@ -3255,7 +3267,7 @@
           <t>Arriendo</t>
         </is>
       </c>
-      <c r="F58" s="11" t="inlineStr">
+      <c r="F58" s="13" t="inlineStr">
         <is>
           <t>F-14023</t>
         </is>
@@ -3299,7 +3311,7 @@
           <t>Arriendo</t>
         </is>
       </c>
-      <c r="F59" s="10" t="inlineStr">
+      <c r="F59" s="12" t="inlineStr">
         <is>
           <t>F-14024</t>
         </is>
@@ -3347,7 +3359,7 @@
           <t>Arriendo</t>
         </is>
       </c>
-      <c r="F60" s="11" t="inlineStr">
+      <c r="F60" s="13" t="inlineStr">
         <is>
           <t>F-14031</t>
         </is>
@@ -3395,7 +3407,7 @@
           <t>Arriendo</t>
         </is>
       </c>
-      <c r="F61" s="10" t="inlineStr">
+      <c r="F61" s="12" t="inlineStr">
         <is>
           <t>F-14026</t>
         </is>
@@ -3439,7 +3451,7 @@
           <t>Arriendo</t>
         </is>
       </c>
-      <c r="F62" s="11" t="inlineStr">
+      <c r="F62" s="13" t="inlineStr">
         <is>
           <t>F-14028</t>
         </is>
@@ -3487,7 +3499,7 @@
           <t>Arriendo</t>
         </is>
       </c>
-      <c r="F63" s="10" t="inlineStr">
+      <c r="F63" s="12" t="inlineStr">
         <is>
           <t>F-14027</t>
         </is>
@@ -3535,7 +3547,7 @@
           <t>Arriendo</t>
         </is>
       </c>
-      <c r="F64" s="11" t="inlineStr">
+      <c r="F64" s="13" t="inlineStr">
         <is>
           <t>F-14129</t>
         </is>
@@ -3583,7 +3595,7 @@
           <t>Serv. Admin</t>
         </is>
       </c>
-      <c r="F65" s="10" t="inlineStr">
+      <c r="F65" s="12" t="inlineStr">
         <is>
           <t>FEE-14086</t>
         </is>
@@ -3631,7 +3643,7 @@
           <t>Arriendo</t>
         </is>
       </c>
-      <c r="F66" s="11" t="inlineStr">
+      <c r="F66" s="13" t="inlineStr">
         <is>
           <t>F-14067</t>
         </is>
@@ -3677,7 +3689,7 @@
           <t>Serv. Admin</t>
         </is>
       </c>
-      <c r="F67" s="11" t="inlineStr">
+      <c r="F67" s="13" t="inlineStr">
         <is>
           <t>FEE-14091</t>
         </is>
@@ -3725,7 +3737,7 @@
           <t>Arriendo</t>
         </is>
       </c>
-      <c r="F68" s="10" t="inlineStr">
+      <c r="F68" s="12" t="inlineStr">
         <is>
           <t>F-14069</t>
         </is>
@@ -3771,7 +3783,7 @@
           <t>Arriendo</t>
         </is>
       </c>
-      <c r="F69" s="10" t="inlineStr">
+      <c r="F69" s="12" t="inlineStr">
         <is>
           <t>F-14072</t>
         </is>
@@ -3817,7 +3829,7 @@
           <t>Arriendo</t>
         </is>
       </c>
-      <c r="F70" s="10" t="inlineStr">
+      <c r="F70" s="12" t="inlineStr">
         <is>
           <t>F-14073</t>
         </is>
@@ -3863,7 +3875,7 @@
           <t>Arriendo</t>
         </is>
       </c>
-      <c r="F71" s="10" t="inlineStr">
+      <c r="F71" s="12" t="inlineStr">
         <is>
           <t>F-14077</t>
         </is>
@@ -3909,7 +3921,7 @@
           <t>Arriendo</t>
         </is>
       </c>
-      <c r="F72" s="10" t="inlineStr">
+      <c r="F72" s="12" t="inlineStr">
         <is>
           <t>F-14078</t>
         </is>
@@ -3955,7 +3967,7 @@
           <t>Habilitación</t>
         </is>
       </c>
-      <c r="F73" s="10" t="inlineStr">
+      <c r="F73" s="12" t="inlineStr">
         <is>
           <t>F-14079</t>
         </is>
@@ -4003,7 +4015,7 @@
           <t>Serv. Admin</t>
         </is>
       </c>
-      <c r="F74" s="10" t="inlineStr">
+      <c r="F74" s="12" t="inlineStr">
         <is>
           <t>FEE-14084</t>
         </is>
@@ -4051,7 +4063,7 @@
           <t>Serv. Admin</t>
         </is>
       </c>
-      <c r="F75" s="10" t="inlineStr">
+      <c r="F75" s="12" t="inlineStr">
         <is>
           <t>FEE-14085</t>
         </is>
@@ -4099,7 +4111,7 @@
           <t>Serv. Admin</t>
         </is>
       </c>
-      <c r="F76" s="10" t="inlineStr">
+      <c r="F76" s="12" t="inlineStr">
         <is>
           <t>FEE-14112</t>
         </is>
@@ -4147,7 +4159,7 @@
           <t>Serv. Admin</t>
         </is>
       </c>
-      <c r="F77" s="10" t="inlineStr">
+      <c r="F77" s="12" t="inlineStr">
         <is>
           <t>FEE-14117</t>
         </is>
@@ -4195,7 +4207,7 @@
           <t>Serv. Admin</t>
         </is>
       </c>
-      <c r="F78" s="10" t="inlineStr">
+      <c r="F78" s="12" t="inlineStr">
         <is>
           <t>FEE-14118</t>
         </is>
@@ -4243,7 +4255,7 @@
           <t>Arriendo</t>
         </is>
       </c>
-      <c r="F79" s="11" t="inlineStr">
+      <c r="F79" s="13" t="inlineStr">
         <is>
           <t>F-10</t>
         </is>
@@ -4291,7 +4303,7 @@
           <t>Arriendo</t>
         </is>
       </c>
-      <c r="F80" s="11" t="inlineStr">
+      <c r="F80" s="13" t="inlineStr">
         <is>
           <t>F-6</t>
         </is>
@@ -4339,7 +4351,7 @@
           <t>Arriendo</t>
         </is>
       </c>
-      <c r="F81" s="10" t="inlineStr">
+      <c r="F81" s="12" t="inlineStr">
         <is>
           <t>F-14068</t>
         </is>
@@ -4385,7 +4397,7 @@
           <t>Serv. Admin</t>
         </is>
       </c>
-      <c r="F82" s="10" t="inlineStr">
+      <c r="F82" s="12" t="inlineStr">
         <is>
           <t>FEE-14088</t>
         </is>
@@ -4433,7 +4445,7 @@
           <t>Arriendo</t>
         </is>
       </c>
-      <c r="F83" s="11" t="inlineStr">
+      <c r="F83" s="13" t="inlineStr">
         <is>
           <t>F-14071</t>
         </is>
@@ -4481,7 +4493,7 @@
           <t>Serv. Admin</t>
         </is>
       </c>
-      <c r="F84" s="11" t="inlineStr">
+      <c r="F84" s="13" t="inlineStr">
         <is>
           <t>FEE-14087</t>
         </is>
@@ -4529,7 +4541,7 @@
           <t>Arriendo</t>
         </is>
       </c>
-      <c r="F85" s="10" t="inlineStr">
+      <c r="F85" s="12" t="inlineStr">
         <is>
           <t>F-14076</t>
         </is>
@@ -4575,7 +4587,7 @@
           <t>Serv. Admin</t>
         </is>
       </c>
-      <c r="F86" s="10" t="inlineStr">
+      <c r="F86" s="12" t="inlineStr">
         <is>
           <t>FEE-14109</t>
         </is>
@@ -4623,7 +4635,7 @@
           <t>Arriendo</t>
         </is>
       </c>
-      <c r="F87" s="11" t="inlineStr">
+      <c r="F87" s="13" t="inlineStr">
         <is>
           <t>F-14074</t>
         </is>
@@ -4669,7 +4681,7 @@
           <t>Serv. Admin</t>
         </is>
       </c>
-      <c r="F88" s="11" t="inlineStr">
+      <c r="F88" s="13" t="inlineStr">
         <is>
           <t>FEE-14105</t>
         </is>
@@ -4717,7 +4729,7 @@
           <t>Serv. Admin</t>
         </is>
       </c>
-      <c r="F89" s="10" t="inlineStr">
+      <c r="F89" s="12" t="inlineStr">
         <is>
           <t>FEE-14101</t>
         </is>
@@ -4765,7 +4777,7 @@
           <t>Arriendo</t>
         </is>
       </c>
-      <c r="F90" s="11" t="inlineStr">
+      <c r="F90" s="13" t="inlineStr">
         <is>
           <t>F-14080</t>
         </is>
@@ -4811,7 +4823,7 @@
           <t>Serv. Admin</t>
         </is>
       </c>
-      <c r="F91" s="11" t="inlineStr">
+      <c r="F91" s="13" t="inlineStr">
         <is>
           <t>FEE-14097</t>
         </is>
@@ -4859,7 +4871,7 @@
           <t>Arriendo</t>
         </is>
       </c>
-      <c r="F92" s="10" t="inlineStr">
+      <c r="F92" s="12" t="inlineStr">
         <is>
           <t>F-14066</t>
         </is>
@@ -4907,7 +4919,7 @@
           <t>Arriendo</t>
         </is>
       </c>
-      <c r="F93" s="11" t="inlineStr">
+      <c r="F93" s="13" t="inlineStr">
         <is>
           <t>F-14075</t>
         </is>
@@ -4955,7 +4967,7 @@
           <t>Serv. Admin</t>
         </is>
       </c>
-      <c r="F94" s="11" t="inlineStr">
+      <c r="F94" s="13" t="inlineStr">
         <is>
           <t>FEE-14115</t>
         </is>
@@ -5003,7 +5015,7 @@
           <t>Arriendo</t>
         </is>
       </c>
-      <c r="F95" s="10" t="inlineStr">
+      <c r="F95" s="12" t="inlineStr">
         <is>
           <t>F-14070</t>
         </is>
@@ -5049,7 +5061,7 @@
           <t>Serv. Admin</t>
         </is>
       </c>
-      <c r="F96" s="10" t="inlineStr">
+      <c r="F96" s="12" t="inlineStr">
         <is>
           <t>FEE-14083</t>
         </is>
@@ -5097,7 +5109,7 @@
           <t>Arriendo</t>
         </is>
       </c>
-      <c r="F97" s="11" t="inlineStr">
+      <c r="F97" s="13" t="inlineStr">
         <is>
           <t>F-14081</t>
         </is>
@@ -5143,7 +5155,7 @@
           <t>Serv. Admin</t>
         </is>
       </c>
-      <c r="F98" s="11" t="inlineStr">
+      <c r="F98" s="13" t="inlineStr">
         <is>
           <t>FEE-14113</t>
         </is>
@@ -5191,7 +5203,7 @@
           <t>Serv. Admin</t>
         </is>
       </c>
-      <c r="F99" s="10" t="inlineStr">
+      <c r="F99" s="12" t="inlineStr">
         <is>
           <t>FEE-14092</t>
         </is>
@@ -5239,7 +5251,7 @@
           <t>Serv. Admin</t>
         </is>
       </c>
-      <c r="F100" s="10" t="inlineStr">
+      <c r="F100" s="12" t="inlineStr">
         <is>
           <t>FEE-14095</t>
         </is>
@@ -5287,7 +5299,7 @@
           <t>Arriendo</t>
         </is>
       </c>
-      <c r="F101" s="11" t="inlineStr">
+      <c r="F101" s="13" t="inlineStr">
         <is>
           <t>F-7</t>
         </is>
@@ -5335,7 +5347,7 @@
           <t>Arriendo</t>
         </is>
       </c>
-      <c r="F102" s="10" t="inlineStr">
+      <c r="F102" s="12" t="inlineStr">
         <is>
           <t>F-8</t>
         </is>
@@ -5383,7 +5395,7 @@
           <t>Serv. Admin</t>
         </is>
       </c>
-      <c r="F103" s="10" t="inlineStr">
+      <c r="F103" s="12" t="inlineStr">
         <is>
           <t>FEE-14110</t>
         </is>
@@ -5431,7 +5443,7 @@
           <t>Serv. Admin</t>
         </is>
       </c>
-      <c r="F104" s="11" t="inlineStr">
+      <c r="F104" s="13" t="inlineStr">
         <is>
           <t>FEE-14123</t>
         </is>
@@ -5477,7 +5489,7 @@
           <t>Arriendo</t>
         </is>
       </c>
-      <c r="F105" s="10" t="inlineStr">
+      <c r="F105" s="12" t="inlineStr">
         <is>
           <t>F-14082</t>
         </is>
@@ -5523,7 +5535,7 @@
           <t>Arriendo</t>
         </is>
       </c>
-      <c r="F106" s="11" t="inlineStr">
+      <c r="F106" s="13" t="inlineStr">
         <is>
           <t>F-14127</t>
         </is>
@@ -5571,7 +5583,7 @@
           <t>Arriendo</t>
         </is>
       </c>
-      <c r="F107" s="10" t="inlineStr">
+      <c r="F107" s="12" t="inlineStr">
         <is>
           <t>F-5</t>
         </is>
@@ -5619,7 +5631,7 @@
           <t>Arriendo</t>
         </is>
       </c>
-      <c r="F108" s="11" t="inlineStr">
+      <c r="F108" s="13" t="inlineStr">
         <is>
           <t>F-4</t>
         </is>
@@ -5667,7 +5679,7 @@
           <t>Serv. Admin</t>
         </is>
       </c>
-      <c r="F109" s="11" t="inlineStr">
+      <c r="F109" s="13" t="inlineStr">
         <is>
           <t>FEE-14090</t>
         </is>
@@ -5715,7 +5727,7 @@
           <t>Arriendo</t>
         </is>
       </c>
-      <c r="F110" s="10" t="inlineStr">
+      <c r="F110" s="12" t="inlineStr">
         <is>
           <t>F-14014</t>
         </is>
@@ -5764,7 +5776,7 @@
           <t>Arriendo</t>
         </is>
       </c>
-      <c r="F111" s="11" t="inlineStr">
+      <c r="F111" s="13" t="inlineStr">
         <is>
           <t>F-14054</t>
         </is>
@@ -5812,7 +5824,7 @@
           <t>Arriendo</t>
         </is>
       </c>
-      <c r="F112" s="10" t="inlineStr">
+      <c r="F112" s="12" t="inlineStr">
         <is>
           <t>F-14128</t>
         </is>
@@ -5860,7 +5872,7 @@
           <t>Arriendo</t>
         </is>
       </c>
-      <c r="F113" s="11" t="inlineStr">
+      <c r="F113" s="13" t="inlineStr">
         <is>
           <t>F-14056</t>
         </is>
@@ -5908,7 +5920,7 @@
           <t>Arriendo</t>
         </is>
       </c>
-      <c r="F114" s="10" t="inlineStr">
+      <c r="F114" s="12" t="inlineStr">
         <is>
           <t>F-14058</t>
         </is>
@@ -5956,7 +5968,7 @@
           <t>Arriendo</t>
         </is>
       </c>
-      <c r="F115" s="11" t="inlineStr">
+      <c r="F115" s="13" t="inlineStr">
         <is>
           <t>F-14065</t>
         </is>
@@ -6004,7 +6016,7 @@
           <t>Arriendo</t>
         </is>
       </c>
-      <c r="F116" s="10" t="inlineStr">
+      <c r="F116" s="12" t="inlineStr">
         <is>
           <t>F-14062</t>
         </is>
@@ -6052,7 +6064,7 @@
           <t>Arriendo</t>
         </is>
       </c>
-      <c r="F117" s="11" t="inlineStr">
+      <c r="F117" s="13" t="inlineStr">
         <is>
           <t>F-14053</t>
         </is>
@@ -6100,7 +6112,7 @@
           <t>Arriendo</t>
         </is>
       </c>
-      <c r="F118" s="10" t="inlineStr">
+      <c r="F118" s="12" t="inlineStr">
         <is>
           <t>F-14059</t>
         </is>
@@ -6148,7 +6160,7 @@
           <t>Arriendo</t>
         </is>
       </c>
-      <c r="F119" s="11" t="inlineStr">
+      <c r="F119" s="13" t="inlineStr">
         <is>
           <t>F-14013</t>
         </is>
@@ -6196,7 +6208,7 @@
           <t>Arriendo</t>
         </is>
       </c>
-      <c r="F120" s="10" t="inlineStr">
+      <c r="F120" s="12" t="inlineStr">
         <is>
           <t>F-14055</t>
         </is>
@@ -6244,7 +6256,7 @@
           <t>Arriendo</t>
         </is>
       </c>
-      <c r="F121" s="11" t="inlineStr">
+      <c r="F121" s="13" t="inlineStr">
         <is>
           <t>F-14060</t>
         </is>
@@ -6292,7 +6304,7 @@
           <t>Arriendo</t>
         </is>
       </c>
-      <c r="F122" s="11" t="inlineStr">
+      <c r="F122" s="13" t="inlineStr">
         <is>
           <t>F-14061</t>
         </is>
@@ -6336,7 +6348,7 @@
           <t>Arriendo</t>
         </is>
       </c>
-      <c r="F123" s="10" t="inlineStr">
+      <c r="F123" s="12" t="inlineStr">
         <is>
           <t>F-14057</t>
         </is>
@@ -6384,7 +6396,7 @@
           <t>Arriendo</t>
         </is>
       </c>
-      <c r="F124" s="11" t="inlineStr">
+      <c r="F124" s="13" t="inlineStr">
         <is>
           <t>F-14052</t>
         </is>
@@ -6432,7 +6444,7 @@
           <t>Arriendo</t>
         </is>
       </c>
-      <c r="F125" s="10" t="inlineStr">
+      <c r="F125" s="12" t="inlineStr">
         <is>
           <t>F-12</t>
         </is>
@@ -6480,7 +6492,7 @@
           <t>Arriendo</t>
         </is>
       </c>
-      <c r="F126" s="11" t="inlineStr">
+      <c r="F126" s="13" t="inlineStr">
         <is>
           <t>F-14064</t>
         </is>
@@ -6528,7 +6540,7 @@
           <t>Arriendo</t>
         </is>
       </c>
-      <c r="F127" s="10" t="inlineStr">
+      <c r="F127" s="12" t="inlineStr">
         <is>
           <t>F-14063</t>
         </is>
@@ -6576,7 +6588,7 @@
           <t>Serv. Admin</t>
         </is>
       </c>
-      <c r="F128" s="11" t="inlineStr">
+      <c r="F128" s="13" t="inlineStr">
         <is>
           <t>FEE-14089</t>
         </is>
@@ -6624,7 +6636,7 @@
           <t>Serv. Mant.</t>
         </is>
       </c>
-      <c r="F129" s="10" t="inlineStr">
+      <c r="F129" s="12" t="inlineStr">
         <is>
           <t>F-14125</t>
         </is>
@@ -6670,7 +6682,7 @@
           <t>Serv. Admin</t>
         </is>
       </c>
-      <c r="F130" s="11" t="inlineStr">
+      <c r="F130" s="13" t="inlineStr">
         <is>
           <t>FEE-14120</t>
         </is>
@@ -6718,7 +6730,7 @@
           <t>Arriendo</t>
         </is>
       </c>
-      <c r="F131" s="10" t="inlineStr">
+      <c r="F131" s="12" t="inlineStr">
         <is>
           <t>F-11</t>
         </is>
@@ -6766,7 +6778,7 @@
           <t>Arriendo</t>
         </is>
       </c>
-      <c r="F132" s="10" t="inlineStr">
+      <c r="F132" s="12" t="inlineStr">
         <is>
           <t>F-9</t>
         </is>
@@ -6814,7 +6826,7 @@
           <t>Arriendo</t>
         </is>
       </c>
-      <c r="F133" s="11" t="inlineStr">
+      <c r="F133" s="13" t="inlineStr">
         <is>
           <t>F-14132</t>
         </is>
@@ -6858,7 +6870,7 @@
           <t>Arriendo</t>
         </is>
       </c>
-      <c r="F134" s="11" t="inlineStr">
+      <c r="F134" s="13" t="inlineStr">
         <is>
           <t>F-14133</t>
         </is>
@@ -6906,7 +6918,7 @@
           <t>Arriendo</t>
         </is>
       </c>
-      <c r="F135" s="11" t="inlineStr">
+      <c r="F135" s="13" t="inlineStr">
         <is>
           <t>F-14136</t>
         </is>
@@ -6954,7 +6966,7 @@
           <t>Serv. Admin</t>
         </is>
       </c>
-      <c r="F136" s="11" t="inlineStr">
+      <c r="F136" s="13" t="inlineStr">
         <is>
           <t>FEE-14221</t>
         </is>
@@ -7002,7 +7014,7 @@
           <t>Arriendo</t>
         </is>
       </c>
-      <c r="F137" s="10" t="inlineStr">
+      <c r="F137" s="12" t="inlineStr">
         <is>
           <t>F-14139</t>
         </is>
@@ -7050,7 +7062,7 @@
           <t>Arriendo</t>
         </is>
       </c>
-      <c r="F138" s="11" t="inlineStr">
+      <c r="F138" s="13" t="inlineStr">
         <is>
           <t>F-14145</t>
         </is>
@@ -7098,7 +7110,7 @@
           <t>Arriendo</t>
         </is>
       </c>
-      <c r="F139" s="10" t="inlineStr">
+      <c r="F139" s="12" t="inlineStr">
         <is>
           <t>F-14141</t>
         </is>
@@ -7146,7 +7158,7 @@
           <t>Arriendo</t>
         </is>
       </c>
-      <c r="F140" s="11" t="inlineStr">
+      <c r="F140" s="13" t="inlineStr">
         <is>
           <t>F-14137</t>
         </is>
@@ -7194,7 +7206,7 @@
           <t>Arriendo</t>
         </is>
       </c>
-      <c r="F141" s="10" t="inlineStr">
+      <c r="F141" s="12" t="inlineStr">
         <is>
           <t>F-14138</t>
         </is>
@@ -7242,7 +7254,7 @@
           <t>Serv. Admin</t>
         </is>
       </c>
-      <c r="F142" s="10" t="inlineStr">
+      <c r="F142" s="12" t="inlineStr">
         <is>
           <t>FEE-14222</t>
         </is>
@@ -7290,7 +7302,7 @@
           <t>Arriendo</t>
         </is>
       </c>
-      <c r="F143" s="11" t="inlineStr">
+      <c r="F143" s="13" t="inlineStr">
         <is>
           <t>F-14135</t>
         </is>
@@ -7338,7 +7350,7 @@
           <t>Serv. Admin</t>
         </is>
       </c>
-      <c r="F144" s="11" t="inlineStr">
+      <c r="F144" s="13" t="inlineStr">
         <is>
           <t>FEE-14220</t>
         </is>
@@ -7386,7 +7398,7 @@
           <t>Arriendo</t>
         </is>
       </c>
-      <c r="F145" s="10" t="inlineStr">
+      <c r="F145" s="12" t="inlineStr">
         <is>
           <t>F-14140</t>
         </is>
@@ -7434,7 +7446,7 @@
           <t>Arriendo</t>
         </is>
       </c>
-      <c r="F146" s="11" t="inlineStr">
+      <c r="F146" s="13" t="inlineStr">
         <is>
           <t>F-14142</t>
         </is>
@@ -7482,7 +7494,7 @@
           <t>Arriendo</t>
         </is>
       </c>
-      <c r="F147" s="10" t="inlineStr">
+      <c r="F147" s="12" t="inlineStr">
         <is>
           <t>F-14148</t>
         </is>
@@ -7530,7 +7542,7 @@
           <t>Serv. Admin</t>
         </is>
       </c>
-      <c r="F148" s="10" t="inlineStr">
+      <c r="F148" s="12" t="inlineStr">
         <is>
           <t>FEE-14224</t>
         </is>
@@ -7578,7 +7590,7 @@
           <t>Arriendo</t>
         </is>
       </c>
-      <c r="F149" s="11" t="inlineStr">
+      <c r="F149" s="13" t="inlineStr">
         <is>
           <t>F-14134</t>
         </is>
@@ -7626,7 +7638,7 @@
           <t>Serv. Admin</t>
         </is>
       </c>
-      <c r="F150" s="11" t="inlineStr">
+      <c r="F150" s="13" t="inlineStr">
         <is>
           <t>FEE-14219</t>
         </is>
@@ -7674,7 +7686,7 @@
           <t>Arriendo</t>
         </is>
       </c>
-      <c r="F151" s="10" t="inlineStr">
+      <c r="F151" s="12" t="inlineStr">
         <is>
           <t>F-14146</t>
         </is>
@@ -7722,7 +7734,7 @@
           <t>Arriendo</t>
         </is>
       </c>
-      <c r="F152" s="10" t="inlineStr">
+      <c r="F152" s="12" t="inlineStr">
         <is>
           <t>F-14147</t>
         </is>
@@ -7770,7 +7782,7 @@
           <t>Arriendo</t>
         </is>
       </c>
-      <c r="F153" s="11" t="inlineStr">
+      <c r="F153" s="13" t="inlineStr">
         <is>
           <t>F-14143</t>
         </is>
@@ -7818,7 +7830,7 @@
           <t>Serv. Admin</t>
         </is>
       </c>
-      <c r="F154" s="11" t="inlineStr">
+      <c r="F154" s="13" t="inlineStr">
         <is>
           <t>FEE-14223</t>
         </is>
@@ -7866,7 +7878,7 @@
           <t>Arriendo</t>
         </is>
       </c>
-      <c r="F155" s="10" t="inlineStr">
+      <c r="F155" s="12" t="inlineStr">
         <is>
           <t>F-14144</t>
         </is>
@@ -7914,7 +7926,7 @@
           <t>Arriendo</t>
         </is>
       </c>
-      <c r="F156" s="11" t="inlineStr">
+      <c r="F156" s="13" t="inlineStr">
         <is>
           <t>F-14149</t>
         </is>
@@ -7962,7 +7974,7 @@
           <t>Arriendo</t>
         </is>
       </c>
-      <c r="F157" s="10" t="inlineStr">
+      <c r="F157" s="12" t="inlineStr">
         <is>
           <t>F-14152</t>
         </is>
@@ -8010,7 +8022,7 @@
           <t>Serv. Admin</t>
         </is>
       </c>
-      <c r="F158" s="10" t="inlineStr">
+      <c r="F158" s="12" t="inlineStr">
         <is>
           <t>FEE-14207</t>
         </is>
@@ -8058,7 +8070,7 @@
           <t>Arriendo</t>
         </is>
       </c>
-      <c r="F159" s="11" t="inlineStr">
+      <c r="F159" s="13" t="inlineStr">
         <is>
           <t>F-14204</t>
         </is>
@@ -8106,7 +8118,7 @@
           <t>Arriendo</t>
         </is>
       </c>
-      <c r="F160" s="10" t="inlineStr">
+      <c r="F160" s="12" t="inlineStr">
         <is>
           <t>F-14170</t>
         </is>
@@ -8154,7 +8166,7 @@
           <t>Arriendo</t>
         </is>
       </c>
-      <c r="F161" s="11" t="inlineStr">
+      <c r="F161" s="13" t="inlineStr">
         <is>
           <t>F-14154</t>
         </is>
@@ -8202,7 +8214,7 @@
           <t>Serv. Admin</t>
         </is>
       </c>
-      <c r="F162" s="11" t="inlineStr">
+      <c r="F162" s="13" t="inlineStr">
         <is>
           <t>FEE-14218</t>
         </is>
@@ -8248,7 +8260,7 @@
           <t>Arriendo</t>
         </is>
       </c>
-      <c r="F163" s="10" t="inlineStr">
+      <c r="F163" s="12" t="inlineStr">
         <is>
           <t>F-14159</t>
         </is>
@@ -8296,7 +8308,7 @@
           <t>Serv. Admin</t>
         </is>
       </c>
-      <c r="F164" s="10" t="inlineStr">
+      <c r="F164" s="12" t="inlineStr">
         <is>
           <t>FEE-14208</t>
         </is>
@@ -8344,7 +8356,7 @@
           <t>Arriendo</t>
         </is>
       </c>
-      <c r="F165" s="11" t="inlineStr">
+      <c r="F165" s="13" t="inlineStr">
         <is>
           <t>F-14151</t>
         </is>
@@ -8392,7 +8404,7 @@
           <t>Serv. Admin</t>
         </is>
       </c>
-      <c r="F166" s="11" t="inlineStr">
+      <c r="F166" s="13" t="inlineStr">
         <is>
           <t>FEE-14206</t>
         </is>
@@ -8440,7 +8452,7 @@
           <t>Arriendo</t>
         </is>
       </c>
-      <c r="F167" s="10" t="inlineStr">
+      <c r="F167" s="12" t="inlineStr">
         <is>
           <t>F-14156</t>
         </is>
@@ -8488,7 +8500,7 @@
           <t>Serv. Admin</t>
         </is>
       </c>
-      <c r="F168" s="10" t="inlineStr">
+      <c r="F168" s="12" t="inlineStr">
         <is>
           <t>FEE-14210</t>
         </is>
@@ -8536,7 +8548,7 @@
           <t>Arriendo</t>
         </is>
       </c>
-      <c r="F169" s="11" t="inlineStr">
+      <c r="F169" s="13" t="inlineStr">
         <is>
           <t>F-14155</t>
         </is>
@@ -8584,7 +8596,7 @@
           <t>Arriendo</t>
         </is>
       </c>
-      <c r="F170" s="11" t="inlineStr">
+      <c r="F170" s="13" t="inlineStr">
         <is>
           <t>F-14162</t>
         </is>
@@ -8632,7 +8644,7 @@
           <t>Arriendo</t>
         </is>
       </c>
-      <c r="F171" s="11" t="inlineStr">
+      <c r="F171" s="13" t="inlineStr">
         <is>
           <t>F-14169</t>
         </is>
@@ -8680,7 +8692,7 @@
           <t>Serv. Admin</t>
         </is>
       </c>
-      <c r="F172" s="11" t="inlineStr">
+      <c r="F172" s="13" t="inlineStr">
         <is>
           <t>FEE-14211</t>
         </is>
@@ -8728,7 +8740,7 @@
           <t>Arriendo</t>
         </is>
       </c>
-      <c r="F173" s="10" t="inlineStr">
+      <c r="F173" s="12" t="inlineStr">
         <is>
           <t>F-14205</t>
         </is>
@@ -8776,7 +8788,7 @@
           <t>Serv. Admin</t>
         </is>
       </c>
-      <c r="F174" s="10" t="inlineStr">
+      <c r="F174" s="12" t="inlineStr">
         <is>
           <t>FEE-14217</t>
         </is>
@@ -8824,7 +8836,7 @@
           <t>Arriendo</t>
         </is>
       </c>
-      <c r="F175" s="11" t="inlineStr">
+      <c r="F175" s="13" t="inlineStr">
         <is>
           <t>F-14150</t>
         </is>
@@ -8872,7 +8884,7 @@
           <t>Arriendo</t>
         </is>
       </c>
-      <c r="F176" s="10" t="inlineStr">
+      <c r="F176" s="12" t="inlineStr">
         <is>
           <t>F-14166</t>
         </is>
@@ -8920,7 +8932,7 @@
           <t>Serv. Admin</t>
         </is>
       </c>
-      <c r="F177" s="10" t="inlineStr">
+      <c r="F177" s="12" t="inlineStr">
         <is>
           <t>FEE-14216</t>
         </is>
@@ -8968,7 +8980,7 @@
           <t>Arriendo</t>
         </is>
       </c>
-      <c r="F178" s="11" t="inlineStr">
+      <c r="F178" s="13" t="inlineStr">
         <is>
           <t>F-14153</t>
         </is>
@@ -9016,7 +9028,7 @@
           <t>Serv. Admin</t>
         </is>
       </c>
-      <c r="F179" s="11" t="inlineStr">
+      <c r="F179" s="13" t="inlineStr">
         <is>
           <t>FEE-14209</t>
         </is>
@@ -9064,7 +9076,7 @@
           <t>Arriendo</t>
         </is>
       </c>
-      <c r="F180" s="10" t="inlineStr">
+      <c r="F180" s="12" t="inlineStr">
         <is>
           <t>F-14157</t>
         </is>
@@ -9112,7 +9124,7 @@
           <t>Serv. Admin</t>
         </is>
       </c>
-      <c r="F181" s="10" t="inlineStr">
+      <c r="F181" s="12" t="inlineStr">
         <is>
           <t>FEE-14213</t>
         </is>
@@ -9160,7 +9172,7 @@
           <t>Arriendo</t>
         </is>
       </c>
-      <c r="F182" s="11" t="inlineStr">
+      <c r="F182" s="13" t="inlineStr">
         <is>
           <t>F-14158</t>
         </is>
@@ -9208,7 +9220,7 @@
           <t>Arriendo</t>
         </is>
       </c>
-      <c r="F183" s="10" t="inlineStr">
+      <c r="F183" s="12" t="inlineStr">
         <is>
           <t>F-14168</t>
         </is>
@@ -9256,7 +9268,7 @@
           <t>Arriendo</t>
         </is>
       </c>
-      <c r="F184" s="11" t="inlineStr">
+      <c r="F184" s="13" t="inlineStr">
         <is>
           <t>F-14167</t>
         </is>
@@ -9304,7 +9316,7 @@
           <t>Serv. Admin</t>
         </is>
       </c>
-      <c r="F185" s="11" t="inlineStr">
+      <c r="F185" s="13" t="inlineStr">
         <is>
           <t>FEE-14212</t>
         </is>
@@ -9352,7 +9364,7 @@
           <t>Arriendo</t>
         </is>
       </c>
-      <c r="F186" s="10" t="inlineStr">
+      <c r="F186" s="12" t="inlineStr">
         <is>
           <t>F-14160</t>
         </is>
@@ -9400,7 +9412,7 @@
           <t>Serv. Admin</t>
         </is>
       </c>
-      <c r="F187" s="10" t="inlineStr">
+      <c r="F187" s="12" t="inlineStr">
         <is>
           <t>FEE-14214</t>
         </is>
@@ -9448,7 +9460,7 @@
           <t>Arriendo</t>
         </is>
       </c>
-      <c r="F188" s="11" t="inlineStr">
+      <c r="F188" s="13" t="inlineStr">
         <is>
           <t>F-14163</t>
         </is>
@@ -9496,7 +9508,7 @@
           <t>Arriendo</t>
         </is>
       </c>
-      <c r="F189" s="10" t="inlineStr">
+      <c r="F189" s="12" t="inlineStr">
         <is>
           <t>F-14161</t>
         </is>
@@ -9544,7 +9556,7 @@
           <t>Serv. Admin</t>
         </is>
       </c>
-      <c r="F190" s="10" t="inlineStr">
+      <c r="F190" s="12" t="inlineStr">
         <is>
           <t>FEE-14215</t>
         </is>
@@ -9592,7 +9604,7 @@
           <t>Arriendo</t>
         </is>
       </c>
-      <c r="F191" s="11" t="inlineStr">
+      <c r="F191" s="13" t="inlineStr">
         <is>
           <t>F-14171</t>
         </is>
@@ -9640,7 +9652,7 @@
           <t>Arriendo</t>
         </is>
       </c>
-      <c r="F192" s="10" t="inlineStr">
+      <c r="F192" s="12" t="inlineStr">
         <is>
           <t>F-14176</t>
         </is>
@@ -9688,7 +9700,7 @@
           <t>Serv. Admin</t>
         </is>
       </c>
-      <c r="F193" s="10" t="inlineStr">
+      <c r="F193" s="12" t="inlineStr">
         <is>
           <t>FEE-14227</t>
         </is>
@@ -9736,7 +9748,7 @@
           <t>Arriendo</t>
         </is>
       </c>
-      <c r="F194" s="11" t="inlineStr">
+      <c r="F194" s="13" t="inlineStr">
         <is>
           <t>F-14182</t>
         </is>
@@ -9784,7 +9796,7 @@
           <t>Serv. Admin</t>
         </is>
       </c>
-      <c r="F195" s="11" t="inlineStr">
+      <c r="F195" s="13" t="inlineStr">
         <is>
           <t>FEE-14232</t>
         </is>
@@ -9832,7 +9844,7 @@
           <t>Arriendo</t>
         </is>
       </c>
-      <c r="F196" s="10" t="inlineStr">
+      <c r="F196" s="12" t="inlineStr">
         <is>
           <t>F-14173</t>
         </is>
@@ -9880,7 +9892,7 @@
           <t>Arriendo</t>
         </is>
       </c>
-      <c r="F197" s="10" t="inlineStr">
+      <c r="F197" s="12" t="inlineStr">
         <is>
           <t>F-14175</t>
         </is>
@@ -9928,7 +9940,7 @@
           <t>Arriendo</t>
         </is>
       </c>
-      <c r="F198" s="10" t="inlineStr">
+      <c r="F198" s="12" t="inlineStr">
         <is>
           <t>F-14196</t>
         </is>
@@ -9976,7 +9988,7 @@
           <t>Arriendo</t>
         </is>
       </c>
-      <c r="F199" s="10" t="inlineStr">
+      <c r="F199" s="12" t="inlineStr">
         <is>
           <t>F-14200</t>
         </is>
@@ -10024,7 +10036,7 @@
           <t>Arriendo</t>
         </is>
       </c>
-      <c r="F200" s="10" t="inlineStr">
+      <c r="F200" s="12" t="inlineStr">
         <is>
           <t>F-14201</t>
         </is>
@@ -10072,7 +10084,7 @@
           <t>Arriendo</t>
         </is>
       </c>
-      <c r="F201" s="10" t="inlineStr">
+      <c r="F201" s="12" t="inlineStr">
         <is>
           <t>F-14248</t>
         </is>
@@ -10120,7 +10132,7 @@
           <t>Arriendo</t>
         </is>
       </c>
-      <c r="F202" s="10" t="inlineStr">
+      <c r="F202" s="12" t="inlineStr">
         <is>
           <t>F-14249</t>
         </is>
@@ -10168,7 +10180,7 @@
           <t>Arriendo</t>
         </is>
       </c>
-      <c r="F203" s="10" t="inlineStr">
+      <c r="F203" s="12" t="inlineStr">
         <is>
           <t>F-14250</t>
         </is>
@@ -10216,7 +10228,7 @@
           <t>Arriendo</t>
         </is>
       </c>
-      <c r="F204" s="10" t="inlineStr">
+      <c r="F204" s="12" t="inlineStr">
         <is>
           <t>F-14252</t>
         </is>
@@ -10264,7 +10276,7 @@
           <t>Arriendo</t>
         </is>
       </c>
-      <c r="F205" s="10" t="inlineStr">
+      <c r="F205" s="12" t="inlineStr">
         <is>
           <t>F-14253</t>
         </is>
@@ -10312,7 +10324,7 @@
           <t>Habilitación</t>
         </is>
       </c>
-      <c r="F206" s="10" t="inlineStr">
+      <c r="F206" s="12" t="inlineStr">
         <is>
           <t>F-14189</t>
         </is>
@@ -10360,7 +10372,7 @@
           <t>Habilitación</t>
         </is>
       </c>
-      <c r="F207" s="10" t="inlineStr">
+      <c r="F207" s="12" t="inlineStr">
         <is>
           <t>F-14251</t>
         </is>
@@ -10408,7 +10420,7 @@
           <t>Serv. Admin</t>
         </is>
       </c>
-      <c r="F208" s="10" t="inlineStr">
+      <c r="F208" s="12" t="inlineStr">
         <is>
           <t>FEE-14225</t>
         </is>
@@ -10456,7 +10468,7 @@
           <t>Serv. Admin</t>
         </is>
       </c>
-      <c r="F209" s="10" t="inlineStr">
+      <c r="F209" s="12" t="inlineStr">
         <is>
           <t>FEE-14226</t>
         </is>
@@ -10504,7 +10516,7 @@
           <t>Serv. Admin</t>
         </is>
       </c>
-      <c r="F210" s="10" t="inlineStr">
+      <c r="F210" s="12" t="inlineStr">
         <is>
           <t>FEE-14240</t>
         </is>
@@ -10552,7 +10564,7 @@
           <t>Serv. Admin</t>
         </is>
       </c>
-      <c r="F211" s="10" t="inlineStr">
+      <c r="F211" s="12" t="inlineStr">
         <is>
           <t>FEE-14243</t>
         </is>
@@ -10600,7 +10612,7 @@
           <t>Serv. Admin</t>
         </is>
       </c>
-      <c r="F212" s="10" t="inlineStr">
+      <c r="F212" s="12" t="inlineStr">
         <is>
           <t>FEE-14244</t>
         </is>
@@ -10648,7 +10660,7 @@
           <t>Serv. Admin</t>
         </is>
       </c>
-      <c r="F213" s="10" t="inlineStr">
+      <c r="F213" s="12" t="inlineStr">
         <is>
           <t>FEE-14254</t>
         </is>
@@ -10696,7 +10708,7 @@
           <t>Serv. Admin</t>
         </is>
       </c>
-      <c r="F214" s="10" t="inlineStr">
+      <c r="F214" s="12" t="inlineStr">
         <is>
           <t>FEE-14255</t>
         </is>
@@ -10744,7 +10756,7 @@
           <t>Serv. Admin</t>
         </is>
       </c>
-      <c r="F215" s="10" t="inlineStr">
+      <c r="F215" s="12" t="inlineStr">
         <is>
           <t>FEE-14256</t>
         </is>
@@ -10792,7 +10804,7 @@
           <t>Serv. Admin</t>
         </is>
       </c>
-      <c r="F216" s="10" t="inlineStr">
+      <c r="F216" s="12" t="inlineStr">
         <is>
           <t>FEE-14257</t>
         </is>
@@ -10840,7 +10852,7 @@
           <t>Serv. Admin</t>
         </is>
       </c>
-      <c r="F217" s="10" t="inlineStr">
+      <c r="F217" s="12" t="inlineStr">
         <is>
           <t>FEE-14258</t>
         </is>
@@ -10888,7 +10900,7 @@
           <t>Serv. Admin</t>
         </is>
       </c>
-      <c r="F218" s="10" t="inlineStr">
+      <c r="F218" s="12" t="inlineStr">
         <is>
           <t>FEE-14259</t>
         </is>
@@ -10936,7 +10948,7 @@
           <t>Arriendo</t>
         </is>
       </c>
-      <c r="F219" s="11" t="inlineStr">
+      <c r="F219" s="13" t="inlineStr">
         <is>
           <t>F-14</t>
         </is>
@@ -10984,7 +10996,7 @@
           <t>Arriendo</t>
         </is>
       </c>
-      <c r="F220" s="11" t="inlineStr">
+      <c r="F220" s="13" t="inlineStr">
         <is>
           <t>F-19</t>
         </is>
@@ -11032,7 +11044,7 @@
           <t>Arriendo</t>
         </is>
       </c>
-      <c r="F221" s="10" t="inlineStr">
+      <c r="F221" s="12" t="inlineStr">
         <is>
           <t>F-14178</t>
         </is>
@@ -11080,7 +11092,7 @@
           <t>Serv. Admin</t>
         </is>
       </c>
-      <c r="F222" s="10" t="inlineStr">
+      <c r="F222" s="12" t="inlineStr">
         <is>
           <t>FEE-14230</t>
         </is>
@@ -11128,7 +11140,7 @@
           <t>Arriendo</t>
         </is>
       </c>
-      <c r="F223" s="11" t="inlineStr">
+      <c r="F223" s="13" t="inlineStr">
         <is>
           <t>F-14181</t>
         </is>
@@ -11176,7 +11188,7 @@
           <t>Serv. Admin</t>
         </is>
       </c>
-      <c r="F224" s="11" t="inlineStr">
+      <c r="F224" s="13" t="inlineStr">
         <is>
           <t>FEE-14229</t>
         </is>
@@ -11224,7 +11236,7 @@
           <t>Arriendo</t>
         </is>
       </c>
-      <c r="F225" s="10" t="inlineStr">
+      <c r="F225" s="12" t="inlineStr">
         <is>
           <t>F-14183</t>
         </is>
@@ -11272,7 +11284,7 @@
           <t>Arriendo</t>
         </is>
       </c>
-      <c r="F226" s="11" t="inlineStr">
+      <c r="F226" s="13" t="inlineStr">
         <is>
           <t>F-14194</t>
         </is>
@@ -11320,7 +11332,7 @@
           <t>Serv. Admin</t>
         </is>
       </c>
-      <c r="F227" s="11" t="inlineStr">
+      <c r="F227" s="13" t="inlineStr">
         <is>
           <t>FEE-14238</t>
         </is>
@@ -11368,7 +11380,7 @@
           <t>Arriendo</t>
         </is>
       </c>
-      <c r="F228" s="10" t="inlineStr">
+      <c r="F228" s="12" t="inlineStr">
         <is>
           <t>F-14190</t>
         </is>
@@ -11416,7 +11428,7 @@
           <t>Serv. Admin</t>
         </is>
       </c>
-      <c r="F229" s="10" t="inlineStr">
+      <c r="F229" s="12" t="inlineStr">
         <is>
           <t>FEE-14237</t>
         </is>
@@ -11464,7 +11476,7 @@
           <t>Arriendo</t>
         </is>
       </c>
-      <c r="F230" s="11" t="inlineStr">
+      <c r="F230" s="13" t="inlineStr">
         <is>
           <t>F-14186</t>
         </is>
@@ -11512,7 +11524,7 @@
           <t>Serv. Admin</t>
         </is>
       </c>
-      <c r="F231" s="11" t="inlineStr">
+      <c r="F231" s="13" t="inlineStr">
         <is>
           <t>FEE-14236</t>
         </is>
@@ -11560,7 +11572,7 @@
           <t>Arriendo</t>
         </is>
       </c>
-      <c r="F232" s="10" t="inlineStr">
+      <c r="F232" s="12" t="inlineStr">
         <is>
           <t>F-14179</t>
         </is>
@@ -11608,7 +11620,7 @@
           <t>Arriendo</t>
         </is>
       </c>
-      <c r="F233" s="11" t="inlineStr">
+      <c r="F233" s="13" t="inlineStr">
         <is>
           <t>F-14198</t>
         </is>
@@ -11656,7 +11668,7 @@
           <t>Arriendo</t>
         </is>
       </c>
-      <c r="F234" s="10" t="inlineStr">
+      <c r="F234" s="12" t="inlineStr">
         <is>
           <t>F-14174</t>
         </is>
@@ -11704,7 +11716,7 @@
           <t>Arriendo</t>
         </is>
       </c>
-      <c r="F235" s="11" t="inlineStr">
+      <c r="F235" s="13" t="inlineStr">
         <is>
           <t>F-14184</t>
         </is>
@@ -11752,7 +11764,7 @@
           <t>Serv. Admin</t>
         </is>
       </c>
-      <c r="F236" s="11" t="inlineStr">
+      <c r="F236" s="13" t="inlineStr">
         <is>
           <t>FEE-14235</t>
         </is>
@@ -11800,7 +11812,7 @@
           <t>Arriendo</t>
         </is>
       </c>
-      <c r="F237" s="10" t="inlineStr">
+      <c r="F237" s="12" t="inlineStr">
         <is>
           <t>F-14188</t>
         </is>
@@ -11848,7 +11860,7 @@
           <t>Arriendo</t>
         </is>
       </c>
-      <c r="F238" s="11" t="inlineStr">
+      <c r="F238" s="13" t="inlineStr">
         <is>
           <t>F-14187</t>
         </is>
@@ -11896,7 +11908,7 @@
           <t>Arriendo</t>
         </is>
       </c>
-      <c r="F239" s="11" t="inlineStr">
+      <c r="F239" s="13" t="inlineStr">
         <is>
           <t>F-14192</t>
         </is>
@@ -11944,7 +11956,7 @@
           <t>Arriendo</t>
         </is>
       </c>
-      <c r="F240" s="10" t="inlineStr">
+      <c r="F240" s="12" t="inlineStr">
         <is>
           <t>F-14260</t>
         </is>
@@ -11992,7 +12004,7 @@
           <t>Arriendo</t>
         </is>
       </c>
-      <c r="F241" s="11" t="inlineStr">
+      <c r="F241" s="13" t="inlineStr">
         <is>
           <t>F-14191</t>
         </is>
@@ -12040,7 +12052,7 @@
           <t>Arriendo</t>
         </is>
       </c>
-      <c r="F242" s="10" t="inlineStr">
+      <c r="F242" s="12" t="inlineStr">
         <is>
           <t>F-14180</t>
         </is>
@@ -12088,7 +12100,7 @@
           <t>Arriendo</t>
         </is>
       </c>
-      <c r="F243" s="11" t="inlineStr">
+      <c r="F243" s="13" t="inlineStr">
         <is>
           <t>F-14199</t>
         </is>
@@ -12136,7 +12148,7 @@
           <t>Serv. Admin</t>
         </is>
       </c>
-      <c r="F244" s="11" t="inlineStr">
+      <c r="F244" s="13" t="inlineStr">
         <is>
           <t>FEE-14242</t>
         </is>
@@ -12184,7 +12196,7 @@
           <t>Arriendo</t>
         </is>
       </c>
-      <c r="F245" s="10" t="inlineStr">
+      <c r="F245" s="12" t="inlineStr">
         <is>
           <t>F-14177</t>
         </is>
@@ -12232,7 +12244,7 @@
           <t>Serv. Admin</t>
         </is>
       </c>
-      <c r="F246" s="10" t="inlineStr">
+      <c r="F246" s="12" t="inlineStr">
         <is>
           <t>FEE-14228</t>
         </is>
@@ -12280,7 +12292,7 @@
           <t>Arriendo</t>
         </is>
       </c>
-      <c r="F247" s="11" t="inlineStr">
+      <c r="F247" s="13" t="inlineStr">
         <is>
           <t>F-14197</t>
         </is>
@@ -12328,7 +12340,7 @@
           <t>Serv. Admin</t>
         </is>
       </c>
-      <c r="F248" s="11" t="inlineStr">
+      <c r="F248" s="13" t="inlineStr">
         <is>
           <t>FEE-14241</t>
         </is>
@@ -12376,7 +12388,7 @@
           <t>Arriendo</t>
         </is>
       </c>
-      <c r="F249" s="10" t="inlineStr">
+      <c r="F249" s="12" t="inlineStr">
         <is>
           <t>F-14193</t>
         </is>
@@ -12424,7 +12436,7 @@
           <t>Arriendo</t>
         </is>
       </c>
-      <c r="F250" s="10" t="inlineStr">
+      <c r="F250" s="12" t="inlineStr">
         <is>
           <t>F-14195</t>
         </is>
@@ -12466,7 +12478,7 @@
           <t>Serv. Admin</t>
         </is>
       </c>
-      <c r="F251" s="10" t="inlineStr">
+      <c r="F251" s="12" t="inlineStr">
         <is>
           <t>FEE-14233</t>
         </is>
@@ -12514,7 +12526,7 @@
           <t>Serv. Admin</t>
         </is>
       </c>
-      <c r="F252" s="10" t="inlineStr">
+      <c r="F252" s="12" t="inlineStr">
         <is>
           <t>FEE-14234</t>
         </is>
@@ -12562,7 +12574,7 @@
           <t>Arriendo</t>
         </is>
       </c>
-      <c r="F253" s="11" t="inlineStr">
+      <c r="F253" s="13" t="inlineStr">
         <is>
           <t>F-18</t>
         </is>
@@ -12610,7 +12622,7 @@
           <t>Arriendo</t>
         </is>
       </c>
-      <c r="F254" s="10" t="inlineStr">
+      <c r="F254" s="12" t="inlineStr">
         <is>
           <t>F-15</t>
         </is>
@@ -12658,7 +12670,7 @@
           <t>Serv. Admin</t>
         </is>
       </c>
-      <c r="F255" s="10" t="inlineStr">
+      <c r="F255" s="12" t="inlineStr">
         <is>
           <t>FEE-14239</t>
         </is>
@@ -12706,7 +12718,7 @@
           <t>Arriendo</t>
         </is>
       </c>
-      <c r="F256" s="11" t="inlineStr">
+      <c r="F256" s="13" t="inlineStr">
         <is>
           <t>F-14185</t>
         </is>
@@ -12754,7 +12766,7 @@
           <t>Serv. Admin</t>
         </is>
       </c>
-      <c r="F257" s="11" t="inlineStr">
+      <c r="F257" s="13" t="inlineStr">
         <is>
           <t>FEE-14245</t>
         </is>
@@ -12800,7 +12812,7 @@
           <t>Arriendo</t>
         </is>
       </c>
-      <c r="F258" s="10" t="inlineStr">
+      <c r="F258" s="12" t="inlineStr">
         <is>
           <t>F-14172</t>
         </is>
@@ -12848,7 +12860,7 @@
           <t>Arriendo</t>
         </is>
       </c>
-      <c r="F259" s="11" t="inlineStr">
+      <c r="F259" s="13" t="inlineStr">
         <is>
           <t>F-14203</t>
         </is>
@@ -12896,7 +12908,7 @@
           <t>Arriendo</t>
         </is>
       </c>
-      <c r="F260" s="10" t="inlineStr">
+      <c r="F260" s="12" t="inlineStr">
         <is>
           <t>F-14202</t>
         </is>
@@ -12944,7 +12956,7 @@
           <t>Arriendo</t>
         </is>
       </c>
-      <c r="F261" s="11" t="inlineStr">
+      <c r="F261" s="13" t="inlineStr">
         <is>
           <t>F-17</t>
         </is>
@@ -12992,7 +13004,7 @@
           <t>Arriendo</t>
         </is>
       </c>
-      <c r="F262" s="10" t="inlineStr">
+      <c r="F262" s="12" t="inlineStr">
         <is>
           <t>F-16</t>
         </is>
@@ -13040,7 +13052,7 @@
           <t>Serv. Admin</t>
         </is>
       </c>
-      <c r="F263" s="10" t="inlineStr">
+      <c r="F263" s="12" t="inlineStr">
         <is>
           <t>FEE-14231</t>
         </is>
@@ -13088,7 +13100,7 @@
           <t>Arriendo</t>
         </is>
       </c>
-      <c r="F264" s="11" t="inlineStr">
+      <c r="F264" s="13" t="inlineStr">
         <is>
           <t>F-14246</t>
         </is>
@@ -13136,7 +13148,7 @@
           <t>Arriendo</t>
         </is>
       </c>
-      <c r="F265" s="11" t="inlineStr">
+      <c r="F265" s="13" t="inlineStr">
         <is>
           <t>F-14247</t>
         </is>
@@ -13182,7 +13194,7 @@
           <t>Arriendo</t>
         </is>
       </c>
-      <c r="F266" s="10" t="inlineStr">
+      <c r="F266" s="12" t="inlineStr">
         <is>
           <t>F-21</t>
         </is>
@@ -13230,7 +13242,7 @@
           <t>Arriendo</t>
         </is>
       </c>
-      <c r="F267" s="11" t="inlineStr">
+      <c r="F267" s="13" t="inlineStr">
         <is>
           <t>F-13</t>
         </is>
@@ -13278,7 +13290,7 @@
           <t>Arriendo</t>
         </is>
       </c>
-      <c r="F268" s="11" t="inlineStr">
+      <c r="F268" s="13" t="inlineStr">
         <is>
           <t>F-20</t>
         </is>
@@ -13322,7 +13334,7 @@
           <t>Serv. Contables</t>
         </is>
       </c>
-      <c r="F269" s="10" t="inlineStr">
+      <c r="F269" s="12" t="inlineStr">
         <is>
           <t>F-14410</t>
         </is>
@@ -13362,7 +13374,7 @@
           <t>Serv. Contables</t>
         </is>
       </c>
-      <c r="F270" s="11" t="inlineStr">
+      <c r="F270" s="13" t="inlineStr">
         <is>
           <t>F-14422</t>
         </is>
@@ -13402,7 +13414,7 @@
           <t>Serv. Contables</t>
         </is>
       </c>
-      <c r="F271" s="10" t="inlineStr">
+      <c r="F271" s="12" t="inlineStr">
         <is>
           <t>F-14411</t>
         </is>
@@ -13442,7 +13454,7 @@
           <t>Serv. Contables</t>
         </is>
       </c>
-      <c r="F272" s="11" t="inlineStr">
+      <c r="F272" s="13" t="inlineStr">
         <is>
           <t>F-14400</t>
         </is>
@@ -13482,7 +13494,7 @@
           <t>Serv. Contables</t>
         </is>
       </c>
-      <c r="F273" s="10" t="inlineStr">
+      <c r="F273" s="12" t="inlineStr">
         <is>
           <t>F-14406</t>
         </is>
@@ -13522,7 +13534,7 @@
           <t>Serv. Contables</t>
         </is>
       </c>
-      <c r="F274" s="11" t="inlineStr">
+      <c r="F274" s="13" t="inlineStr">
         <is>
           <t>F-14403</t>
         </is>
@@ -13562,7 +13574,7 @@
           <t>Serv. Contables</t>
         </is>
       </c>
-      <c r="F275" s="10" t="inlineStr">
+      <c r="F275" s="12" t="inlineStr">
         <is>
           <t>F-14409</t>
         </is>
@@ -13602,7 +13614,7 @@
           <t>Serv. Contables</t>
         </is>
       </c>
-      <c r="F276" s="11" t="inlineStr">
+      <c r="F276" s="13" t="inlineStr">
         <is>
           <t>F-14388</t>
         </is>
@@ -13642,7 +13654,7 @@
           <t>Serv. Contables</t>
         </is>
       </c>
-      <c r="F277" s="10" t="inlineStr">
+      <c r="F277" s="12" t="inlineStr">
         <is>
           <t>F-14386</t>
         </is>
@@ -13682,7 +13694,7 @@
           <t>Serv. Contables</t>
         </is>
       </c>
-      <c r="F278" s="11" t="inlineStr">
+      <c r="F278" s="13" t="inlineStr">
         <is>
           <t>F-14391</t>
         </is>
@@ -13722,7 +13734,7 @@
           <t>Asesoría</t>
         </is>
       </c>
-      <c r="F279" s="10" t="inlineStr">
+      <c r="F279" s="12" t="inlineStr">
         <is>
           <t>F-14419</t>
         </is>
@@ -13762,7 +13774,7 @@
           <t>Serv. Contables</t>
         </is>
       </c>
-      <c r="F280" s="10" t="inlineStr">
+      <c r="F280" s="12" t="inlineStr">
         <is>
           <t>F-14413</t>
         </is>
@@ -13802,7 +13814,7 @@
           <t>Asesoría</t>
         </is>
       </c>
-      <c r="F281" s="11" t="inlineStr">
+      <c r="F281" s="13" t="inlineStr">
         <is>
           <t>F-14420</t>
         </is>
@@ -13842,7 +13854,7 @@
           <t>Serv. Contables</t>
         </is>
       </c>
-      <c r="F282" s="11" t="inlineStr">
+      <c r="F282" s="13" t="inlineStr">
         <is>
           <t>F-14414</t>
         </is>
@@ -13882,7 +13894,7 @@
           <t>Serv. Contables</t>
         </is>
       </c>
-      <c r="F283" s="10" t="inlineStr">
+      <c r="F283" s="12" t="inlineStr">
         <is>
           <t>F-14390</t>
         </is>
@@ -13922,7 +13934,7 @@
           <t>Serv. Contables</t>
         </is>
       </c>
-      <c r="F284" s="11" t="inlineStr">
+      <c r="F284" s="13" t="inlineStr">
         <is>
           <t>F-14389</t>
         </is>
@@ -13962,7 +13974,7 @@
           <t>Asesoría</t>
         </is>
       </c>
-      <c r="F285" s="10" t="inlineStr">
+      <c r="F285" s="12" t="inlineStr">
         <is>
           <t>F-14418</t>
         </is>
@@ -14002,7 +14014,7 @@
           <t>Serv. Contables</t>
         </is>
       </c>
-      <c r="F286" s="10" t="inlineStr">
+      <c r="F286" s="12" t="inlineStr">
         <is>
           <t>F-14412</t>
         </is>
@@ -14042,7 +14054,7 @@
           <t>Serv. Contables</t>
         </is>
       </c>
-      <c r="F287" s="11" t="inlineStr">
+      <c r="F287" s="13" t="inlineStr">
         <is>
           <t>F-14392</t>
         </is>
@@ -14082,7 +14094,7 @@
           <t>Serv. Contables</t>
         </is>
       </c>
-      <c r="F288" s="10" t="inlineStr">
+      <c r="F288" s="12" t="inlineStr">
         <is>
           <t>F-14393</t>
         </is>
@@ -14122,7 +14134,7 @@
           <t>Serv. Contables</t>
         </is>
       </c>
-      <c r="F289" s="11" t="inlineStr">
+      <c r="F289" s="13" t="inlineStr">
         <is>
           <t>F-14407</t>
         </is>
@@ -14162,7 +14174,7 @@
           <t>Serv. Contables</t>
         </is>
       </c>
-      <c r="F290" s="10" t="inlineStr">
+      <c r="F290" s="12" t="inlineStr">
         <is>
           <t>F-14404</t>
         </is>
@@ -14202,7 +14214,7 @@
           <t>Serv. Contables</t>
         </is>
       </c>
-      <c r="F291" s="11" t="inlineStr">
+      <c r="F291" s="13" t="inlineStr">
         <is>
           <t>F-14405</t>
         </is>
@@ -14242,7 +14254,7 @@
           <t>Serv. Contables</t>
         </is>
       </c>
-      <c r="F292" s="10" t="inlineStr">
+      <c r="F292" s="12" t="inlineStr">
         <is>
           <t>F-14402</t>
         </is>
@@ -14282,7 +14294,7 @@
           <t>Serv. Contables</t>
         </is>
       </c>
-      <c r="F293" s="11" t="inlineStr">
+      <c r="F293" s="13" t="inlineStr">
         <is>
           <t>F-14408</t>
         </is>
@@ -14322,7 +14334,7 @@
           <t>Serv. Contables</t>
         </is>
       </c>
-      <c r="F294" s="10" t="inlineStr">
+      <c r="F294" s="12" t="inlineStr">
         <is>
           <t>F-14394</t>
         </is>
@@ -14362,7 +14374,7 @@
           <t>Asesoría</t>
         </is>
       </c>
-      <c r="F295" s="11" t="inlineStr">
+      <c r="F295" s="13" t="inlineStr">
         <is>
           <t>F-14415</t>
         </is>
@@ -14402,7 +14414,7 @@
           <t>Asesoría</t>
         </is>
       </c>
-      <c r="F296" s="11" t="inlineStr">
+      <c r="F296" s="13" t="inlineStr">
         <is>
           <t>F-14416</t>
         </is>
@@ -14442,7 +14454,7 @@
           <t>Serv. Contables</t>
         </is>
       </c>
-      <c r="F297" s="11" t="inlineStr">
+      <c r="F297" s="13" t="inlineStr">
         <is>
           <t>F-14396</t>
         </is>
@@ -14482,7 +14494,7 @@
           <t>Serv. Contables</t>
         </is>
       </c>
-      <c r="F298" s="10" t="inlineStr">
+      <c r="F298" s="12" t="inlineStr">
         <is>
           <t>F-14395</t>
         </is>
@@ -14522,7 +14534,7 @@
           <t>Asesoría</t>
         </is>
       </c>
-      <c r="F299" s="11" t="inlineStr">
+      <c r="F299" s="13" t="inlineStr">
         <is>
           <t>F-14417</t>
         </is>
@@ -14562,7 +14574,7 @@
           <t>Serv. Contables</t>
         </is>
       </c>
-      <c r="F300" s="11" t="inlineStr">
+      <c r="F300" s="13" t="inlineStr">
         <is>
           <t>F-14397</t>
         </is>
@@ -14602,7 +14614,7 @@
           <t>Serv. Contables</t>
         </is>
       </c>
-      <c r="F301" s="10" t="inlineStr">
+      <c r="F301" s="12" t="inlineStr">
         <is>
           <t>F-14398</t>
         </is>
@@ -14642,7 +14654,7 @@
           <t>Serv. Contables</t>
         </is>
       </c>
-      <c r="F302" s="11" t="inlineStr">
+      <c r="F302" s="13" t="inlineStr">
         <is>
           <t>F-14387</t>
         </is>
@@ -14682,7 +14694,7 @@
           <t>Serv. Contables</t>
         </is>
       </c>
-      <c r="F303" s="10" t="inlineStr">
+      <c r="F303" s="12" t="inlineStr">
         <is>
           <t>F-14401</t>
         </is>
@@ -14722,7 +14734,7 @@
           <t>Serv. Contables</t>
         </is>
       </c>
-      <c r="F304" s="11" t="inlineStr">
+      <c r="F304" s="13" t="inlineStr">
         <is>
           <t>F-14399</t>
         </is>
@@ -14762,7 +14774,7 @@
           <t>Asesoría</t>
         </is>
       </c>
-      <c r="F305" s="10" t="inlineStr">
+      <c r="F305" s="12" t="inlineStr">
         <is>
           <t>F-14421</t>
         </is>
@@ -14806,7 +14818,7 @@
           <t>Arriendo</t>
         </is>
       </c>
-      <c r="F306" s="11" t="inlineStr">
+      <c r="F306" s="13" t="inlineStr">
         <is>
           <t>F-14283</t>
         </is>
@@ -14850,7 +14862,7 @@
           <t>Arriendo</t>
         </is>
       </c>
-      <c r="F307" s="11" t="inlineStr">
+      <c r="F307" s="13" t="inlineStr">
         <is>
           <t>F-14284</t>
         </is>
@@ -14898,7 +14910,7 @@
           <t>Arriendo</t>
         </is>
       </c>
-      <c r="F308" s="11" t="inlineStr">
+      <c r="F308" s="13" t="inlineStr">
         <is>
           <t>F-14287</t>
         </is>
@@ -14946,7 +14958,7 @@
           <t>Serv. Admin</t>
         </is>
       </c>
-      <c r="F309" s="11" t="inlineStr">
+      <c r="F309" s="13" t="inlineStr">
         <is>
           <t>FEE-14352</t>
         </is>
@@ -14994,7 +15006,7 @@
           <t>Arriendo</t>
         </is>
       </c>
-      <c r="F310" s="10" t="inlineStr">
+      <c r="F310" s="12" t="inlineStr">
         <is>
           <t>F-14290</t>
         </is>
@@ -15042,7 +15054,7 @@
           <t>Arriendo</t>
         </is>
       </c>
-      <c r="F311" s="11" t="inlineStr">
+      <c r="F311" s="13" t="inlineStr">
         <is>
           <t>F-14296</t>
         </is>
@@ -15090,7 +15102,7 @@
           <t>Arriendo</t>
         </is>
       </c>
-      <c r="F312" s="11" t="inlineStr">
+      <c r="F312" s="13" t="inlineStr">
         <is>
           <t>F-14297</t>
         </is>
@@ -15138,7 +15150,7 @@
           <t>Arriendo</t>
         </is>
       </c>
-      <c r="F313" s="10" t="inlineStr">
+      <c r="F313" s="12" t="inlineStr">
         <is>
           <t>F-14292</t>
         </is>
@@ -15186,7 +15198,7 @@
           <t>Arriendo</t>
         </is>
       </c>
-      <c r="F314" s="11" t="inlineStr">
+      <c r="F314" s="13" t="inlineStr">
         <is>
           <t>F-14288</t>
         </is>
@@ -15234,7 +15246,7 @@
           <t>Arriendo</t>
         </is>
       </c>
-      <c r="F315" s="10" t="inlineStr">
+      <c r="F315" s="12" t="inlineStr">
         <is>
           <t>F-14289</t>
         </is>
@@ -15282,7 +15294,7 @@
           <t>Serv. Admin</t>
         </is>
       </c>
-      <c r="F316" s="10" t="inlineStr">
+      <c r="F316" s="12" t="inlineStr">
         <is>
           <t>FEE-14341</t>
         </is>
@@ -15330,7 +15342,7 @@
           <t>Arriendo</t>
         </is>
       </c>
-      <c r="F317" s="11" t="inlineStr">
+      <c r="F317" s="13" t="inlineStr">
         <is>
           <t>F-14286</t>
         </is>
@@ -15378,7 +15390,7 @@
           <t>Serv. Admin</t>
         </is>
       </c>
-      <c r="F318" s="11" t="inlineStr">
+      <c r="F318" s="13" t="inlineStr">
         <is>
           <t>FEE-14351</t>
         </is>
@@ -15426,7 +15438,7 @@
           <t>Arriendo</t>
         </is>
       </c>
-      <c r="F319" s="10" t="inlineStr">
+      <c r="F319" s="12" t="inlineStr">
         <is>
           <t>F-14291</t>
         </is>
@@ -15474,7 +15486,7 @@
           <t>Arriendo</t>
         </is>
       </c>
-      <c r="F320" s="11" t="inlineStr">
+      <c r="F320" s="13" t="inlineStr">
         <is>
           <t>F-14293</t>
         </is>
@@ -15522,7 +15534,7 @@
           <t>Arriendo</t>
         </is>
       </c>
-      <c r="F321" s="10" t="inlineStr">
+      <c r="F321" s="12" t="inlineStr">
         <is>
           <t>F-14374</t>
         </is>
@@ -15570,7 +15582,7 @@
           <t>Serv. Admin</t>
         </is>
       </c>
-      <c r="F322" s="10" t="inlineStr">
+      <c r="F322" s="12" t="inlineStr">
         <is>
           <t>FEE-14377</t>
         </is>
@@ -15618,7 +15630,7 @@
           <t>Serv. Admin</t>
         </is>
       </c>
-      <c r="F323" s="10" t="inlineStr">
+      <c r="F323" s="12" t="inlineStr">
         <is>
           <t>FEE-14378</t>
         </is>
@@ -15666,7 +15678,7 @@
           <t>Arriendo</t>
         </is>
       </c>
-      <c r="F324" s="11" t="inlineStr">
+      <c r="F324" s="13" t="inlineStr">
         <is>
           <t>F-14285</t>
         </is>
@@ -15714,7 +15726,7 @@
           <t>Serv. Admin</t>
         </is>
       </c>
-      <c r="F325" s="11" t="inlineStr">
+      <c r="F325" s="13" t="inlineStr">
         <is>
           <t>FEE-14350</t>
         </is>
@@ -15762,7 +15774,7 @@
           <t>Arriendo</t>
         </is>
       </c>
-      <c r="F326" s="10" t="inlineStr">
+      <c r="F326" s="12" t="inlineStr">
         <is>
           <t>F-14298</t>
         </is>
@@ -15810,7 +15822,7 @@
           <t>Arriendo</t>
         </is>
       </c>
-      <c r="F327" s="10" t="inlineStr">
+      <c r="F327" s="12" t="inlineStr">
         <is>
           <t>F-14299</t>
         </is>
@@ -15858,7 +15870,7 @@
           <t>Arriendo</t>
         </is>
       </c>
-      <c r="F328" s="11" t="inlineStr">
+      <c r="F328" s="13" t="inlineStr">
         <is>
           <t>F-14294</t>
         </is>
@@ -15906,7 +15918,7 @@
           <t>Serv. Admin</t>
         </is>
       </c>
-      <c r="F329" s="11" t="inlineStr">
+      <c r="F329" s="13" t="inlineStr">
         <is>
           <t>FEE-14343</t>
         </is>
@@ -15954,7 +15966,7 @@
           <t>Arriendo</t>
         </is>
       </c>
-      <c r="F330" s="10" t="inlineStr">
+      <c r="F330" s="12" t="inlineStr">
         <is>
           <t>F-14295</t>
         </is>
@@ -16002,7 +16014,7 @@
           <t>Arriendo</t>
         </is>
       </c>
-      <c r="F331" s="11" t="inlineStr">
+      <c r="F331" s="13" t="inlineStr">
         <is>
           <t>F-14261</t>
         </is>
@@ -16050,7 +16062,7 @@
           <t>Arriendo</t>
         </is>
       </c>
-      <c r="F332" s="10" t="inlineStr">
+      <c r="F332" s="12" t="inlineStr">
         <is>
           <t>F-14264</t>
         </is>
@@ -16098,7 +16110,7 @@
           <t>Serv. Admin</t>
         </is>
       </c>
-      <c r="F333" s="10" t="inlineStr">
+      <c r="F333" s="12" t="inlineStr">
         <is>
           <t>FEE-14345</t>
         </is>
@@ -16146,7 +16158,7 @@
           <t>Arriendo</t>
         </is>
       </c>
-      <c r="F334" s="11" t="inlineStr">
+      <c r="F334" s="13" t="inlineStr">
         <is>
           <t>F-14276</t>
         </is>
@@ -16194,7 +16206,7 @@
           <t>Arriendo</t>
         </is>
       </c>
-      <c r="F335" s="10" t="inlineStr">
+      <c r="F335" s="12" t="inlineStr">
         <is>
           <t>F-14282</t>
         </is>
@@ -16242,7 +16254,7 @@
           <t>Arriendo</t>
         </is>
       </c>
-      <c r="F336" s="11" t="inlineStr">
+      <c r="F336" s="13" t="inlineStr">
         <is>
           <t>F-14266</t>
         </is>
@@ -16290,7 +16302,7 @@
           <t>Serv. Admin</t>
         </is>
       </c>
-      <c r="F337" s="11" t="inlineStr">
+      <c r="F337" s="13" t="inlineStr">
         <is>
           <t>FEE-14369</t>
         </is>
@@ -16336,7 +16348,7 @@
           <t>Arriendo</t>
         </is>
       </c>
-      <c r="F338" s="10" t="inlineStr">
+      <c r="F338" s="12" t="inlineStr">
         <is>
           <t>F-14271</t>
         </is>
@@ -16384,7 +16396,7 @@
           <t>Serv. Admin</t>
         </is>
       </c>
-      <c r="F339" s="10" t="inlineStr">
+      <c r="F339" s="12" t="inlineStr">
         <is>
           <t>FEE-14346</t>
         </is>
@@ -16432,7 +16444,7 @@
           <t>Arriendo</t>
         </is>
       </c>
-      <c r="F340" s="11" t="inlineStr">
+      <c r="F340" s="13" t="inlineStr">
         <is>
           <t>F-14263</t>
         </is>
@@ -16480,7 +16492,7 @@
           <t>Serv. Admin</t>
         </is>
       </c>
-      <c r="F341" s="11" t="inlineStr">
+      <c r="F341" s="13" t="inlineStr">
         <is>
           <t>FEE-14342</t>
         </is>
@@ -16528,7 +16540,7 @@
           <t>Arriendo</t>
         </is>
       </c>
-      <c r="F342" s="10" t="inlineStr">
+      <c r="F342" s="12" t="inlineStr">
         <is>
           <t>F-14268</t>
         </is>
@@ -16576,7 +16588,7 @@
           <t>Serv. Admin</t>
         </is>
       </c>
-      <c r="F343" s="10" t="inlineStr">
+      <c r="F343" s="12" t="inlineStr">
         <is>
           <t>FEE-14349</t>
         </is>
@@ -16624,7 +16636,7 @@
           <t>Arriendo</t>
         </is>
       </c>
-      <c r="F344" s="11" t="inlineStr">
+      <c r="F344" s="13" t="inlineStr">
         <is>
           <t>F-14267</t>
         </is>
@@ -16672,7 +16684,7 @@
           <t>Arriendo</t>
         </is>
       </c>
-      <c r="F345" s="11" t="inlineStr">
+      <c r="F345" s="13" t="inlineStr">
         <is>
           <t>F-14274</t>
         </is>
@@ -16720,7 +16732,7 @@
           <t>Arriendo</t>
         </is>
       </c>
-      <c r="F346" s="11" t="inlineStr">
+      <c r="F346" s="13" t="inlineStr">
         <is>
           <t>F-14281</t>
         </is>
@@ -16768,7 +16780,7 @@
           <t>Serv. Admin</t>
         </is>
       </c>
-      <c r="F347" s="11" t="inlineStr">
+      <c r="F347" s="13" t="inlineStr">
         <is>
           <t>FEE-14354</t>
         </is>
@@ -16816,7 +16828,7 @@
           <t>Arriendo</t>
         </is>
       </c>
-      <c r="F348" s="10" t="inlineStr">
+      <c r="F348" s="12" t="inlineStr">
         <is>
           <t>F-14277</t>
         </is>
@@ -16864,7 +16876,7 @@
           <t>Serv. Admin</t>
         </is>
       </c>
-      <c r="F349" s="10" t="inlineStr">
+      <c r="F349" s="12" t="inlineStr">
         <is>
           <t>FEE-14367</t>
         </is>
@@ -16912,7 +16924,7 @@
           <t>Arriendo</t>
         </is>
       </c>
-      <c r="F350" s="11" t="inlineStr">
+      <c r="F350" s="13" t="inlineStr">
         <is>
           <t>F-14262</t>
         </is>
@@ -16960,7 +16972,7 @@
           <t>Arriendo</t>
         </is>
       </c>
-      <c r="F351" s="10" t="inlineStr">
+      <c r="F351" s="12" t="inlineStr">
         <is>
           <t>F-14278</t>
         </is>
@@ -17008,7 +17020,7 @@
           <t>Serv. Admin</t>
         </is>
       </c>
-      <c r="F352" s="10" t="inlineStr">
+      <c r="F352" s="12" t="inlineStr">
         <is>
           <t>FEE-14365</t>
         </is>
@@ -17056,7 +17068,7 @@
           <t>Arriendo</t>
         </is>
       </c>
-      <c r="F353" s="11" t="inlineStr">
+      <c r="F353" s="13" t="inlineStr">
         <is>
           <t>F-14265</t>
         </is>
@@ -17104,7 +17116,7 @@
           <t>Serv. Admin</t>
         </is>
       </c>
-      <c r="F354" s="11" t="inlineStr">
+      <c r="F354" s="13" t="inlineStr">
         <is>
           <t>FEE-14347</t>
         </is>
@@ -17152,7 +17164,7 @@
           <t>Arriendo</t>
         </is>
       </c>
-      <c r="F355" s="10" t="inlineStr">
+      <c r="F355" s="12" t="inlineStr">
         <is>
           <t>F-14269</t>
         </is>
@@ -17200,7 +17212,7 @@
           <t>Serv. Admin</t>
         </is>
       </c>
-      <c r="F356" s="10" t="inlineStr">
+      <c r="F356" s="12" t="inlineStr">
         <is>
           <t>FEE-14358</t>
         </is>
@@ -17248,7 +17260,7 @@
           <t>Arriendo</t>
         </is>
       </c>
-      <c r="F357" s="11" t="inlineStr">
+      <c r="F357" s="13" t="inlineStr">
         <is>
           <t>F-14270</t>
         </is>
@@ -17296,7 +17308,7 @@
           <t>Arriendo</t>
         </is>
       </c>
-      <c r="F358" s="10" t="inlineStr">
+      <c r="F358" s="12" t="inlineStr">
         <is>
           <t>F-14280</t>
         </is>
@@ -17344,7 +17356,7 @@
           <t>Arriendo</t>
         </is>
       </c>
-      <c r="F359" s="11" t="inlineStr">
+      <c r="F359" s="13" t="inlineStr">
         <is>
           <t>F-14279</t>
         </is>
@@ -17392,7 +17404,7 @@
           <t>Arriendo</t>
         </is>
       </c>
-      <c r="F360" s="11" t="inlineStr">
+      <c r="F360" s="13" t="inlineStr">
         <is>
           <t>F-14331</t>
         </is>
@@ -17440,7 +17452,7 @@
           <t>Serv. Admin</t>
         </is>
       </c>
-      <c r="F361" s="11" t="inlineStr">
+      <c r="F361" s="13" t="inlineStr">
         <is>
           <t>FEE-14355</t>
         </is>
@@ -17488,7 +17500,7 @@
           <t>Arriendo</t>
         </is>
       </c>
-      <c r="F362" s="10" t="inlineStr">
+      <c r="F362" s="12" t="inlineStr">
         <is>
           <t>F-14272</t>
         </is>
@@ -17536,7 +17548,7 @@
           <t>Serv. Admin</t>
         </is>
       </c>
-      <c r="F363" s="10" t="inlineStr">
+      <c r="F363" s="12" t="inlineStr">
         <is>
           <t>FEE-14361</t>
         </is>
@@ -17584,7 +17596,7 @@
           <t>Arriendo</t>
         </is>
       </c>
-      <c r="F364" s="11" t="inlineStr">
+      <c r="F364" s="13" t="inlineStr">
         <is>
           <t>F-14275</t>
         </is>
@@ -17632,7 +17644,7 @@
           <t>Arriendo</t>
         </is>
       </c>
-      <c r="F365" s="10" t="inlineStr">
+      <c r="F365" s="12" t="inlineStr">
         <is>
           <t>F-14273</t>
         </is>
@@ -17680,7 +17692,7 @@
           <t>Serv. Admin</t>
         </is>
       </c>
-      <c r="F366" s="10" t="inlineStr">
+      <c r="F366" s="12" t="inlineStr">
         <is>
           <t>FEE-14363</t>
         </is>
@@ -17728,7 +17740,7 @@
           <t>Serv. Admin</t>
         </is>
       </c>
-      <c r="F367" s="10" t="inlineStr">
+      <c r="F367" s="12" t="inlineStr">
         <is>
           <t>FEE-14372</t>
         </is>
@@ -17776,7 +17788,7 @@
           <t>Arriendo</t>
         </is>
       </c>
-      <c r="F368" s="11" t="inlineStr">
+      <c r="F368" s="13" t="inlineStr">
         <is>
           <t>F-14300</t>
         </is>
@@ -17824,7 +17836,7 @@
           <t>Arriendo</t>
         </is>
       </c>
-      <c r="F369" s="10" t="inlineStr">
+      <c r="F369" s="12" t="inlineStr">
         <is>
           <t>F-14305</t>
         </is>
@@ -17872,7 +17884,7 @@
           <t>Serv. Admin</t>
         </is>
       </c>
-      <c r="F370" s="10" t="inlineStr">
+      <c r="F370" s="12" t="inlineStr">
         <is>
           <t>FEE-14334</t>
         </is>
@@ -17920,7 +17932,7 @@
           <t>Arriendo</t>
         </is>
       </c>
-      <c r="F371" s="11" t="inlineStr">
+      <c r="F371" s="13" t="inlineStr">
         <is>
           <t>F-14311</t>
         </is>
@@ -17968,7 +17980,7 @@
           <t>Serv. Admin</t>
         </is>
       </c>
-      <c r="F372" s="11" t="inlineStr">
+      <c r="F372" s="13" t="inlineStr">
         <is>
           <t>FEE-14340</t>
         </is>
@@ -18016,7 +18028,7 @@
           <t>Arriendo</t>
         </is>
       </c>
-      <c r="F373" s="10" t="inlineStr">
+      <c r="F373" s="12" t="inlineStr">
         <is>
           <t>F-14302</t>
         </is>
@@ -18058,7 +18070,7 @@
           <t>Arriendo</t>
         </is>
       </c>
-      <c r="F374" s="10" t="inlineStr">
+      <c r="F374" s="12" t="inlineStr">
         <is>
           <t>F-14304</t>
         </is>
@@ -18106,7 +18118,7 @@
           <t>Arriendo</t>
         </is>
       </c>
-      <c r="F375" s="10" t="inlineStr">
+      <c r="F375" s="12" t="inlineStr">
         <is>
           <t>F-14322</t>
         </is>
@@ -18154,7 +18166,7 @@
           <t>Arriendo</t>
         </is>
       </c>
-      <c r="F376" s="10" t="inlineStr">
+      <c r="F376" s="12" t="inlineStr">
         <is>
           <t>F-14327</t>
         </is>
@@ -18202,7 +18214,7 @@
           <t>Arriendo</t>
         </is>
       </c>
-      <c r="F377" s="10" t="inlineStr">
+      <c r="F377" s="12" t="inlineStr">
         <is>
           <t>F-14328</t>
         </is>
@@ -18250,7 +18262,7 @@
           <t>Arriendo</t>
         </is>
       </c>
-      <c r="F378" s="10" t="inlineStr">
+      <c r="F378" s="12" t="inlineStr">
         <is>
           <t>F-14332</t>
         </is>
@@ -18298,7 +18310,7 @@
           <t>Arriendo</t>
         </is>
       </c>
-      <c r="F379" s="10" t="inlineStr">
+      <c r="F379" s="12" t="inlineStr">
         <is>
           <t>F-14381</t>
         </is>
@@ -18346,7 +18358,7 @@
           <t>Arriendo</t>
         </is>
       </c>
-      <c r="F380" s="10" t="inlineStr">
+      <c r="F380" s="12" t="inlineStr">
         <is>
           <t>F-14384</t>
         </is>
@@ -18394,7 +18406,7 @@
           <t>Habilitación</t>
         </is>
       </c>
-      <c r="F381" s="10" t="inlineStr">
+      <c r="F381" s="12" t="inlineStr">
         <is>
           <t>F-14326</t>
         </is>
@@ -18442,7 +18454,7 @@
           <t>Serv. Admin</t>
         </is>
       </c>
-      <c r="F382" s="10" t="inlineStr">
+      <c r="F382" s="12" t="inlineStr">
         <is>
           <t>FEE-14333</t>
         </is>
@@ -18490,7 +18502,7 @@
           <t>Serv. Admin</t>
         </is>
       </c>
-      <c r="F383" s="10" t="inlineStr">
+      <c r="F383" s="12" t="inlineStr">
         <is>
           <t>FEE-14359</t>
         </is>
@@ -18538,7 +18550,7 @@
           <t>Serv. Admin</t>
         </is>
       </c>
-      <c r="F384" s="10" t="inlineStr">
+      <c r="F384" s="12" t="inlineStr">
         <is>
           <t>FEE-14364</t>
         </is>
@@ -18586,7 +18598,7 @@
           <t>Serv. Admin</t>
         </is>
       </c>
-      <c r="F385" s="10" t="inlineStr">
+      <c r="F385" s="12" t="inlineStr">
         <is>
           <t>FEE-14366</t>
         </is>
@@ -18634,7 +18646,7 @@
           <t>Serv. Admin</t>
         </is>
       </c>
-      <c r="F386" s="10" t="inlineStr">
+      <c r="F386" s="12" t="inlineStr">
         <is>
           <t>FEE-14382</t>
         </is>
@@ -18682,7 +18694,7 @@
           <t>Arriendo</t>
         </is>
       </c>
-      <c r="F387" s="11" t="inlineStr">
+      <c r="F387" s="13" t="inlineStr">
         <is>
           <t>F-22</t>
         </is>
@@ -18730,7 +18742,7 @@
           <t>Arriendo</t>
         </is>
       </c>
-      <c r="F388" s="10" t="inlineStr">
+      <c r="F388" s="12" t="inlineStr">
         <is>
           <t>F-14307</t>
         </is>
@@ -18778,7 +18790,7 @@
           <t>Arriendo</t>
         </is>
       </c>
-      <c r="F389" s="10" t="inlineStr">
+      <c r="F389" s="12" t="inlineStr">
         <is>
           <t>F-14337</t>
         </is>
@@ -18826,7 +18838,7 @@
           <t>Arriendo</t>
         </is>
       </c>
-      <c r="F390" s="11" t="inlineStr">
+      <c r="F390" s="13" t="inlineStr">
         <is>
           <t>F-14310</t>
         </is>
@@ -18874,7 +18886,7 @@
           <t>Arriendo</t>
         </is>
       </c>
-      <c r="F391" s="11" t="inlineStr">
+      <c r="F391" s="13" t="inlineStr">
         <is>
           <t>F-14336</t>
         </is>
@@ -18922,7 +18934,7 @@
           <t>Arriendo</t>
         </is>
       </c>
-      <c r="F392" s="10" t="inlineStr">
+      <c r="F392" s="12" t="inlineStr">
         <is>
           <t>F-14312</t>
         </is>
@@ -18970,7 +18982,7 @@
           <t>Arriendo</t>
         </is>
       </c>
-      <c r="F393" s="11" t="inlineStr">
+      <c r="F393" s="13" t="inlineStr">
         <is>
           <t>F-14321</t>
         </is>
@@ -19018,7 +19030,7 @@
           <t>Serv. Admin</t>
         </is>
       </c>
-      <c r="F394" s="11" t="inlineStr">
+      <c r="F394" s="13" t="inlineStr">
         <is>
           <t>FEE-14356</t>
         </is>
@@ -19066,7 +19078,7 @@
           <t>Arriendo</t>
         </is>
       </c>
-      <c r="F395" s="10" t="inlineStr">
+      <c r="F395" s="12" t="inlineStr">
         <is>
           <t>F-14318</t>
         </is>
@@ -19114,7 +19126,7 @@
           <t>Serv. Admin</t>
         </is>
       </c>
-      <c r="F396" s="10" t="inlineStr">
+      <c r="F396" s="12" t="inlineStr">
         <is>
           <t>FEE-14353</t>
         </is>
@@ -19162,7 +19174,7 @@
           <t>Arriendo</t>
         </is>
       </c>
-      <c r="F397" s="11" t="inlineStr">
+      <c r="F397" s="13" t="inlineStr">
         <is>
           <t>F-14315</t>
         </is>
@@ -19210,7 +19222,7 @@
           <t>Serv. Admin</t>
         </is>
       </c>
-      <c r="F398" s="11" t="inlineStr">
+      <c r="F398" s="13" t="inlineStr">
         <is>
           <t>FEE-14348</t>
         </is>
@@ -19258,7 +19270,7 @@
           <t>Arriendo</t>
         </is>
       </c>
-      <c r="F399" s="10" t="inlineStr">
+      <c r="F399" s="12" t="inlineStr">
         <is>
           <t>F-14308</t>
         </is>
@@ -19306,7 +19318,7 @@
           <t>Arriendo</t>
         </is>
       </c>
-      <c r="F400" s="11" t="inlineStr">
+      <c r="F400" s="13" t="inlineStr">
         <is>
           <t>F-14324</t>
         </is>
@@ -19354,7 +19366,7 @@
           <t>Arriendo</t>
         </is>
       </c>
-      <c r="F401" s="10" t="inlineStr">
+      <c r="F401" s="12" t="inlineStr">
         <is>
           <t>F-14303</t>
         </is>
@@ -19402,7 +19414,7 @@
           <t>Arriendo</t>
         </is>
       </c>
-      <c r="F402" s="11" t="inlineStr">
+      <c r="F402" s="13" t="inlineStr">
         <is>
           <t>F-14313</t>
         </is>
@@ -19450,7 +19462,7 @@
           <t>Serv. Admin</t>
         </is>
       </c>
-      <c r="F403" s="11" t="inlineStr">
+      <c r="F403" s="13" t="inlineStr">
         <is>
           <t>FEE-14344</t>
         </is>
@@ -19498,7 +19510,7 @@
           <t>Arriendo</t>
         </is>
       </c>
-      <c r="F404" s="10" t="inlineStr">
+      <c r="F404" s="12" t="inlineStr">
         <is>
           <t>F-14317</t>
         </is>
@@ -19546,7 +19558,7 @@
           <t>Arriendo</t>
         </is>
       </c>
-      <c r="F405" s="11" t="inlineStr">
+      <c r="F405" s="13" t="inlineStr">
         <is>
           <t>F-14316</t>
         </is>
@@ -19594,7 +19606,7 @@
           <t>Arriendo</t>
         </is>
       </c>
-      <c r="F406" s="11" t="inlineStr">
+      <c r="F406" s="13" t="inlineStr">
         <is>
           <t>F-14320</t>
         </is>
@@ -19642,7 +19654,7 @@
           <t>Arriendo</t>
         </is>
       </c>
-      <c r="F407" s="10" t="inlineStr">
+      <c r="F407" s="12" t="inlineStr">
         <is>
           <t>F-14423</t>
         </is>
@@ -19690,7 +19702,7 @@
           <t>Arriendo</t>
         </is>
       </c>
-      <c r="F408" s="11" t="inlineStr">
+      <c r="F408" s="13" t="inlineStr">
         <is>
           <t>F-14319</t>
         </is>
@@ -19738,7 +19750,7 @@
           <t>Arriendo</t>
         </is>
       </c>
-      <c r="F409" s="10" t="inlineStr">
+      <c r="F409" s="12" t="inlineStr">
         <is>
           <t>F-14309</t>
         </is>
@@ -19786,7 +19798,7 @@
           <t>Arriendo</t>
         </is>
       </c>
-      <c r="F410" s="11" t="inlineStr">
+      <c r="F410" s="13" t="inlineStr">
         <is>
           <t>F-14325</t>
         </is>
@@ -19834,7 +19846,7 @@
           <t>Serv. Admin</t>
         </is>
       </c>
-      <c r="F411" s="11" t="inlineStr">
+      <c r="F411" s="13" t="inlineStr">
         <is>
           <t>FEE-14362</t>
         </is>
@@ -19882,7 +19894,7 @@
           <t>Arriendo</t>
         </is>
       </c>
-      <c r="F412" s="10" t="inlineStr">
+      <c r="F412" s="12" t="inlineStr">
         <is>
           <t>F-14306</t>
         </is>
@@ -19930,7 +19942,7 @@
           <t>Serv. Admin</t>
         </is>
       </c>
-      <c r="F413" s="10" t="inlineStr">
+      <c r="F413" s="12" t="inlineStr">
         <is>
           <t>FEE-14335</t>
         </is>
@@ -19978,7 +19990,7 @@
           <t>Arriendo</t>
         </is>
       </c>
-      <c r="F414" s="11" t="inlineStr">
+      <c r="F414" s="13" t="inlineStr">
         <is>
           <t>F-14323</t>
         </is>
@@ -20026,7 +20038,7 @@
           <t>Serv. Admin</t>
         </is>
       </c>
-      <c r="F415" s="11" t="inlineStr">
+      <c r="F415" s="13" t="inlineStr">
         <is>
           <t>FEE-14360</t>
         </is>
@@ -20074,7 +20086,7 @@
           <t>Arriendo</t>
         </is>
       </c>
-      <c r="F416" s="10" t="inlineStr">
+      <c r="F416" s="12" t="inlineStr">
         <is>
           <t>F-14375</t>
         </is>
@@ -20122,7 +20134,7 @@
           <t>Arriendo</t>
         </is>
       </c>
-      <c r="F417" s="10" t="inlineStr">
+      <c r="F417" s="12" t="inlineStr">
         <is>
           <t>F-14376</t>
         </is>
@@ -20170,7 +20182,7 @@
           <t>Serv. Admin</t>
         </is>
       </c>
-      <c r="F418" s="10" t="inlineStr">
+      <c r="F418" s="12" t="inlineStr">
         <is>
           <t>FEE-14379</t>
         </is>
@@ -20218,7 +20230,7 @@
           <t>Serv. Admin</t>
         </is>
       </c>
-      <c r="F419" s="10" t="inlineStr">
+      <c r="F419" s="12" t="inlineStr">
         <is>
           <t>FEE-14380</t>
         </is>
@@ -20266,7 +20278,7 @@
           <t>Arriendo</t>
         </is>
       </c>
-      <c r="F420" s="11" t="inlineStr">
+      <c r="F420" s="13" t="inlineStr">
         <is>
           <t>F-26</t>
         </is>
@@ -20314,7 +20326,7 @@
           <t>Arriendo</t>
         </is>
       </c>
-      <c r="F421" s="10" t="inlineStr">
+      <c r="F421" s="12" t="inlineStr">
         <is>
           <t>F-23</t>
         </is>
@@ -20362,7 +20374,7 @@
           <t>Serv. Admin</t>
         </is>
       </c>
-      <c r="F422" s="10" t="inlineStr">
+      <c r="F422" s="12" t="inlineStr">
         <is>
           <t>FEE-14357</t>
         </is>
@@ -20410,7 +20422,7 @@
           <t>Arriendo</t>
         </is>
       </c>
-      <c r="F423" s="11" t="inlineStr">
+      <c r="F423" s="13" t="inlineStr">
         <is>
           <t>F-14314</t>
         </is>
@@ -20458,7 +20470,7 @@
           <t>Serv. Admin</t>
         </is>
       </c>
-      <c r="F424" s="11" t="inlineStr">
+      <c r="F424" s="13" t="inlineStr">
         <is>
           <t>FEE-14368</t>
         </is>
@@ -20504,7 +20516,7 @@
           <t>Arriendo</t>
         </is>
       </c>
-      <c r="F425" s="10" t="inlineStr">
+      <c r="F425" s="12" t="inlineStr">
         <is>
           <t>F-14301</t>
         </is>
@@ -20552,7 +20564,7 @@
           <t>Arriendo</t>
         </is>
       </c>
-      <c r="F426" s="11" t="inlineStr">
+      <c r="F426" s="13" t="inlineStr">
         <is>
           <t>F-14330</t>
         </is>
@@ -20600,7 +20612,7 @@
           <t>Arriendo</t>
         </is>
       </c>
-      <c r="F427" s="10" t="inlineStr">
+      <c r="F427" s="12" t="inlineStr">
         <is>
           <t>F-14329</t>
         </is>
@@ -20648,7 +20660,7 @@
           <t>Arriendo</t>
         </is>
       </c>
-      <c r="F428" s="11" t="inlineStr">
+      <c r="F428" s="13" t="inlineStr">
         <is>
           <t>F-25</t>
         </is>
@@ -20696,7 +20708,7 @@
           <t>Arriendo</t>
         </is>
       </c>
-      <c r="F429" s="10" t="inlineStr">
+      <c r="F429" s="12" t="inlineStr">
         <is>
           <t>F-24</t>
         </is>
@@ -20744,7 +20756,7 @@
           <t>Serv. Admin</t>
         </is>
       </c>
-      <c r="F430" s="10" t="inlineStr">
+      <c r="F430" s="12" t="inlineStr">
         <is>
           <t>FEE-14339</t>
         </is>
@@ -20792,7 +20804,7 @@
           <t>Arriendo</t>
         </is>
       </c>
-      <c r="F431" s="11" t="inlineStr">
+      <c r="F431" s="13" t="inlineStr">
         <is>
           <t>F-14373</t>
         </is>
@@ -20840,7 +20852,7 @@
           <t>Habilitación</t>
         </is>
       </c>
-      <c r="F432" s="11" t="inlineStr">
+      <c r="F432" s="13" t="inlineStr">
         <is>
           <t>F-14385</t>
         </is>
@@ -20886,7 +20898,7 @@
           <t>Serv. Admin</t>
         </is>
       </c>
-      <c r="F433" s="10" t="inlineStr">
+      <c r="F433" s="12" t="inlineStr">
         <is>
           <t>FEE-14338</t>
         </is>
@@ -20934,7 +20946,7 @@
           <t>Serv. Admin</t>
         </is>
       </c>
-      <c r="F434" s="10" t="inlineStr">
+      <c r="F434" s="12" t="inlineStr">
         <is>
           <t>FEE-14383</t>
         </is>
@@ -20982,7 +20994,7 @@
           <t>Serv. Admin</t>
         </is>
       </c>
-      <c r="F435" s="11" t="inlineStr">
+      <c r="F435" s="13" t="inlineStr">
         <is>
           <t>FEE-14371</t>
         </is>
@@ -21028,7 +21040,7 @@
           <t>Serv. Admin</t>
         </is>
       </c>
-      <c r="F436" s="10" t="inlineStr">
+      <c r="F436" s="12" t="inlineStr">
         <is>
           <t>FEE-14370</t>
         </is>
@@ -21076,7 +21088,7 @@
           <t>Arriendo</t>
         </is>
       </c>
-      <c r="F437" s="11" t="inlineStr">
+      <c r="F437" s="13" t="inlineStr">
         <is>
           <t>F-27</t>
         </is>
@@ -21124,7 +21136,7 @@
           <t>Arriendo</t>
         </is>
       </c>
-      <c r="F438" s="10" t="inlineStr">
+      <c r="F438" s="12" t="inlineStr">
         <is>
           <t>F-14445</t>
         </is>
@@ -21172,7 +21184,7 @@
           <t>Arriendo</t>
         </is>
       </c>
-      <c r="F439" s="10" t="inlineStr">
+      <c r="F439" s="12" t="inlineStr">
         <is>
           <t>F-14446</t>
         </is>
@@ -21220,7 +21232,7 @@
           <t>Arriendo</t>
         </is>
       </c>
-      <c r="F440" s="10" t="inlineStr">
+      <c r="F440" s="12" t="inlineStr">
         <is>
           <t>F-14449</t>
         </is>
@@ -21268,7 +21280,7 @@
           <t>Serv. Admin</t>
         </is>
       </c>
-      <c r="F441" s="10" t="inlineStr">
+      <c r="F441" s="12" t="inlineStr">
         <is>
           <t>FEE-14516</t>
         </is>
@@ -21316,7 +21328,7 @@
           <t>Arriendo</t>
         </is>
       </c>
-      <c r="F442" s="11" t="inlineStr">
+      <c r="F442" s="13" t="inlineStr">
         <is>
           <t>F-14452</t>
         </is>
@@ -21364,7 +21376,7 @@
           <t>Arriendo</t>
         </is>
       </c>
-      <c r="F443" s="10" t="inlineStr">
+      <c r="F443" s="12" t="inlineStr">
         <is>
           <t>F-14458</t>
         </is>
@@ -21412,7 +21424,7 @@
           <t>Arriendo</t>
         </is>
       </c>
-      <c r="F444" s="11" t="inlineStr">
+      <c r="F444" s="13" t="inlineStr">
         <is>
           <t>F-14454</t>
         </is>
@@ -21460,7 +21472,7 @@
           <t>Arriendo</t>
         </is>
       </c>
-      <c r="F445" s="10" t="inlineStr">
+      <c r="F445" s="12" t="inlineStr">
         <is>
           <t>F-14450</t>
         </is>
@@ -21508,7 +21520,7 @@
           <t>Arriendo</t>
         </is>
       </c>
-      <c r="F446" s="11" t="inlineStr">
+      <c r="F446" s="13" t="inlineStr">
         <is>
           <t>F-14451</t>
         </is>
@@ -21556,7 +21568,7 @@
           <t>Serv. Admin</t>
         </is>
       </c>
-      <c r="F447" s="11" t="inlineStr">
+      <c r="F447" s="13" t="inlineStr">
         <is>
           <t>FEE-14505</t>
         </is>
@@ -21604,7 +21616,7 @@
           <t>Arriendo</t>
         </is>
       </c>
-      <c r="F448" s="10" t="inlineStr">
+      <c r="F448" s="12" t="inlineStr">
         <is>
           <t>F-14448</t>
         </is>
@@ -21652,7 +21664,7 @@
           <t>Serv. Admin</t>
         </is>
       </c>
-      <c r="F449" s="10" t="inlineStr">
+      <c r="F449" s="12" t="inlineStr">
         <is>
           <t>FEE-14515</t>
         </is>
@@ -21700,7 +21712,7 @@
           <t>Arriendo</t>
         </is>
       </c>
-      <c r="F450" s="11" t="inlineStr">
+      <c r="F450" s="13" t="inlineStr">
         <is>
           <t>F-14453</t>
         </is>
@@ -21748,7 +21760,7 @@
           <t>Arriendo</t>
         </is>
       </c>
-      <c r="F451" s="10" t="inlineStr">
+      <c r="F451" s="12" t="inlineStr">
         <is>
           <t>F-14455</t>
         </is>
@@ -21796,7 +21808,7 @@
           <t>Arriendo</t>
         </is>
       </c>
-      <c r="F452" s="11" t="inlineStr">
+      <c r="F452" s="13" t="inlineStr">
         <is>
           <t>F-14461</t>
         </is>
@@ -21844,7 +21856,7 @@
           <t>Serv. Admin</t>
         </is>
       </c>
-      <c r="F453" s="11" t="inlineStr">
+      <c r="F453" s="13" t="inlineStr">
         <is>
           <t>FEE-14536</t>
         </is>
@@ -21892,7 +21904,7 @@
           <t>Arriendo</t>
         </is>
       </c>
-      <c r="F454" s="10" t="inlineStr">
+      <c r="F454" s="12" t="inlineStr">
         <is>
           <t>F-14447</t>
         </is>
@@ -21940,7 +21952,7 @@
           <t>Serv. Admin</t>
         </is>
       </c>
-      <c r="F455" s="10" t="inlineStr">
+      <c r="F455" s="12" t="inlineStr">
         <is>
           <t>FEE-14514</t>
         </is>
@@ -21988,7 +22000,7 @@
           <t>Arriendo</t>
         </is>
       </c>
-      <c r="F456" s="11" t="inlineStr">
+      <c r="F456" s="13" t="inlineStr">
         <is>
           <t>F-14459</t>
         </is>
@@ -22036,7 +22048,7 @@
           <t>Arriendo</t>
         </is>
       </c>
-      <c r="F457" s="11" t="inlineStr">
+      <c r="F457" s="13" t="inlineStr">
         <is>
           <t>F-14460</t>
         </is>
@@ -22084,7 +22096,7 @@
           <t>Arriendo</t>
         </is>
       </c>
-      <c r="F458" s="10" t="inlineStr">
+      <c r="F458" s="12" t="inlineStr">
         <is>
           <t>F-14456</t>
         </is>
@@ -22132,7 +22144,7 @@
           <t>Serv. Admin</t>
         </is>
       </c>
-      <c r="F459" s="10" t="inlineStr">
+      <c r="F459" s="12" t="inlineStr">
         <is>
           <t>FEE-14507</t>
         </is>
@@ -22180,7 +22192,7 @@
           <t>Arriendo</t>
         </is>
       </c>
-      <c r="F460" s="11" t="inlineStr">
+      <c r="F460" s="13" t="inlineStr">
         <is>
           <t>F-14457</t>
         </is>
@@ -22228,7 +22240,7 @@
           <t>Arriendo</t>
         </is>
       </c>
-      <c r="F461" s="10" t="inlineStr">
+      <c r="F461" s="12" t="inlineStr">
         <is>
           <t>F-14424</t>
         </is>
@@ -22276,7 +22288,7 @@
           <t>Arriendo</t>
         </is>
       </c>
-      <c r="F462" s="11" t="inlineStr">
+      <c r="F462" s="13" t="inlineStr">
         <is>
           <t>F-14427</t>
         </is>
@@ -22324,7 +22336,7 @@
           <t>Serv. Admin</t>
         </is>
       </c>
-      <c r="F463" s="11" t="inlineStr">
+      <c r="F463" s="13" t="inlineStr">
         <is>
           <t>FEE-14509</t>
         </is>
@@ -22372,7 +22384,7 @@
           <t>Arriendo</t>
         </is>
       </c>
-      <c r="F464" s="10" t="inlineStr">
+      <c r="F464" s="12" t="inlineStr">
         <is>
           <t>F-14439</t>
         </is>
@@ -22420,7 +22432,7 @@
           <t>Arriendo</t>
         </is>
       </c>
-      <c r="F465" s="11" t="inlineStr">
+      <c r="F465" s="13" t="inlineStr">
         <is>
           <t>F-14444</t>
         </is>
@@ -22468,7 +22480,7 @@
           <t>Arriendo</t>
         </is>
       </c>
-      <c r="F466" s="10" t="inlineStr">
+      <c r="F466" s="12" t="inlineStr">
         <is>
           <t>F-14429</t>
         </is>
@@ -22516,7 +22528,7 @@
           <t>Serv. Admin</t>
         </is>
       </c>
-      <c r="F467" s="10" t="inlineStr">
+      <c r="F467" s="12" t="inlineStr">
         <is>
           <t>FEE-14533</t>
         </is>
@@ -22562,7 +22574,7 @@
           <t>Arriendo</t>
         </is>
       </c>
-      <c r="F468" s="11" t="inlineStr">
+      <c r="F468" s="13" t="inlineStr">
         <is>
           <t>F-14434</t>
         </is>
@@ -22610,7 +22622,7 @@
           <t>Serv. Admin</t>
         </is>
       </c>
-      <c r="F469" s="11" t="inlineStr">
+      <c r="F469" s="13" t="inlineStr">
         <is>
           <t>FEE-14510</t>
         </is>
@@ -22658,7 +22670,7 @@
           <t>Arriendo</t>
         </is>
       </c>
-      <c r="F470" s="10" t="inlineStr">
+      <c r="F470" s="12" t="inlineStr">
         <is>
           <t>F-14426</t>
         </is>
@@ -22706,7 +22718,7 @@
           <t>Serv. Admin</t>
         </is>
       </c>
-      <c r="F471" s="10" t="inlineStr">
+      <c r="F471" s="12" t="inlineStr">
         <is>
           <t>FEE-14506</t>
         </is>
@@ -22754,7 +22766,7 @@
           <t>Arriendo</t>
         </is>
       </c>
-      <c r="F472" s="11" t="inlineStr">
+      <c r="F472" s="13" t="inlineStr">
         <is>
           <t>F-14431</t>
         </is>
@@ -22802,7 +22814,7 @@
           <t>Serv. Admin</t>
         </is>
       </c>
-      <c r="F473" s="11" t="inlineStr">
+      <c r="F473" s="13" t="inlineStr">
         <is>
           <t>FEE-14513</t>
         </is>
@@ -22850,7 +22862,7 @@
           <t>Arriendo</t>
         </is>
       </c>
-      <c r="F474" s="10" t="inlineStr">
+      <c r="F474" s="12" t="inlineStr">
         <is>
           <t>F-14430</t>
         </is>
@@ -22898,7 +22910,7 @@
           <t>Arriendo</t>
         </is>
       </c>
-      <c r="F475" s="10" t="inlineStr">
+      <c r="F475" s="12" t="inlineStr">
         <is>
           <t>F-14437</t>
         </is>
@@ -22946,7 +22958,7 @@
           <t>Arriendo</t>
         </is>
       </c>
-      <c r="F476" s="10" t="inlineStr">
+      <c r="F476" s="12" t="inlineStr">
         <is>
           <t>F-14443</t>
         </is>
@@ -22994,7 +23006,7 @@
           <t>Serv. Admin</t>
         </is>
       </c>
-      <c r="F477" s="10" t="inlineStr">
+      <c r="F477" s="12" t="inlineStr">
         <is>
           <t>FEE-14518</t>
         </is>
@@ -23042,7 +23054,7 @@
           <t>Arriendo</t>
         </is>
       </c>
-      <c r="F478" s="11" t="inlineStr">
+      <c r="F478" s="13" t="inlineStr">
         <is>
           <t>F-14440</t>
         </is>
@@ -23090,7 +23102,7 @@
           <t>Serv. Admin</t>
         </is>
       </c>
-      <c r="F479" s="11" t="inlineStr">
+      <c r="F479" s="13" t="inlineStr">
         <is>
           <t>FEE-14531</t>
         </is>
@@ -23138,7 +23150,7 @@
           <t>Arriendo</t>
         </is>
       </c>
-      <c r="F480" s="10" t="inlineStr">
+      <c r="F480" s="12" t="inlineStr">
         <is>
           <t>F-14425</t>
         </is>
@@ -23186,7 +23198,7 @@
           <t>Arriendo</t>
         </is>
       </c>
-      <c r="F481" s="11" t="inlineStr">
+      <c r="F481" s="13" t="inlineStr">
         <is>
           <t>F-14441</t>
         </is>
@@ -23234,7 +23246,7 @@
           <t>Serv. Admin</t>
         </is>
       </c>
-      <c r="F482" s="11" t="inlineStr">
+      <c r="F482" s="13" t="inlineStr">
         <is>
           <t>FEE-14529</t>
         </is>
@@ -23282,7 +23294,7 @@
           <t>Arriendo</t>
         </is>
       </c>
-      <c r="F483" s="10" t="inlineStr">
+      <c r="F483" s="12" t="inlineStr">
         <is>
           <t>F-14428</t>
         </is>
@@ -23330,7 +23342,7 @@
           <t>Serv. Admin</t>
         </is>
       </c>
-      <c r="F484" s="10" t="inlineStr">
+      <c r="F484" s="12" t="inlineStr">
         <is>
           <t>FEE-14511</t>
         </is>
@@ -23378,7 +23390,7 @@
           <t>Arriendo</t>
         </is>
       </c>
-      <c r="F485" s="11" t="inlineStr">
+      <c r="F485" s="13" t="inlineStr">
         <is>
           <t>F-14432</t>
         </is>
@@ -23426,7 +23438,7 @@
           <t>Serv. Admin</t>
         </is>
       </c>
-      <c r="F486" s="11" t="inlineStr">
+      <c r="F486" s="13" t="inlineStr">
         <is>
           <t>FEE-14522</t>
         </is>
@@ -23474,7 +23486,7 @@
           <t>Arriendo</t>
         </is>
       </c>
-      <c r="F487" s="10" t="inlineStr">
+      <c r="F487" s="12" t="inlineStr">
         <is>
           <t>F-14433</t>
         </is>
@@ -23522,7 +23534,7 @@
           <t>Arriendo</t>
         </is>
       </c>
-      <c r="F488" s="11" t="inlineStr">
+      <c r="F488" s="13" t="inlineStr">
         <is>
           <t>F-14442</t>
         </is>
@@ -23570,7 +23582,7 @@
           <t>Arriendo</t>
         </is>
       </c>
-      <c r="F489" s="10" t="inlineStr">
+      <c r="F489" s="12" t="inlineStr">
         <is>
           <t>F-14540</t>
         </is>
@@ -23618,7 +23630,7 @@
           <t>Serv. Admin</t>
         </is>
       </c>
-      <c r="F490" s="10" t="inlineStr">
+      <c r="F490" s="12" t="inlineStr">
         <is>
           <t>FEE-14519</t>
         </is>
@@ -23666,7 +23678,7 @@
           <t>Serv. Admin</t>
         </is>
       </c>
-      <c r="F491" s="10" t="inlineStr">
+      <c r="F491" s="12" t="inlineStr">
         <is>
           <t>FEE-14547</t>
         </is>
@@ -23714,7 +23726,7 @@
           <t>Arriendo</t>
         </is>
       </c>
-      <c r="F492" s="11" t="inlineStr">
+      <c r="F492" s="13" t="inlineStr">
         <is>
           <t>F-14435</t>
         </is>
@@ -23762,7 +23774,7 @@
           <t>Serv. Admin</t>
         </is>
       </c>
-      <c r="F493" s="11" t="inlineStr">
+      <c r="F493" s="13" t="inlineStr">
         <is>
           <t>FEE-14525</t>
         </is>
@@ -23810,7 +23822,7 @@
           <t>Arriendo</t>
         </is>
       </c>
-      <c r="F494" s="10" t="inlineStr">
+      <c r="F494" s="12" t="inlineStr">
         <is>
           <t>F-14438</t>
         </is>
@@ -23858,7 +23870,7 @@
           <t>Arriendo</t>
         </is>
       </c>
-      <c r="F495" s="11" t="inlineStr">
+      <c r="F495" s="13" t="inlineStr">
         <is>
           <t>F-14436</t>
         </is>
@@ -23906,7 +23918,7 @@
           <t>Serv. Admin</t>
         </is>
       </c>
-      <c r="F496" s="11" t="inlineStr">
+      <c r="F496" s="13" t="inlineStr">
         <is>
           <t>FEE-14527</t>
         </is>
@@ -23954,7 +23966,7 @@
           <t>Serv. Admin</t>
         </is>
       </c>
-      <c r="F497" s="11" t="inlineStr">
+      <c r="F497" s="13" t="inlineStr">
         <is>
           <t>FEE-14539</t>
         </is>
@@ -24002,7 +24014,7 @@
           <t>Arriendo</t>
         </is>
       </c>
-      <c r="F498" s="10" t="inlineStr">
+      <c r="F498" s="12" t="inlineStr">
         <is>
           <t>F-14462</t>
         </is>
@@ -24050,7 +24062,7 @@
           <t>Arriendo</t>
         </is>
       </c>
-      <c r="F499" s="11" t="inlineStr">
+      <c r="F499" s="13" t="inlineStr">
         <is>
           <t>F-14466</t>
         </is>
@@ -24098,7 +24110,7 @@
           <t>Serv. Admin</t>
         </is>
       </c>
-      <c r="F500" s="11" t="inlineStr">
+      <c r="F500" s="13" t="inlineStr">
         <is>
           <t>FEE-14499</t>
         </is>
@@ -24146,7 +24158,7 @@
           <t>Arriendo</t>
         </is>
       </c>
-      <c r="F501" s="10" t="inlineStr">
+      <c r="F501" s="12" t="inlineStr">
         <is>
           <t>F-14471</t>
         </is>
@@ -24194,7 +24206,7 @@
           <t>Arriendo</t>
         </is>
       </c>
-      <c r="F502" s="10" t="inlineStr">
+      <c r="F502" s="12" t="inlineStr">
         <is>
           <t>F-14472</t>
         </is>
@@ -24242,7 +24254,7 @@
           <t>Serv. Admin</t>
         </is>
       </c>
-      <c r="F503" s="10" t="inlineStr">
+      <c r="F503" s="12" t="inlineStr">
         <is>
           <t>FEE-14504</t>
         </is>
@@ -24290,7 +24302,7 @@
           <t>Arriendo</t>
         </is>
       </c>
-      <c r="F504" s="11" t="inlineStr">
+      <c r="F504" s="13" t="inlineStr">
         <is>
           <t>F-14490</t>
         </is>
@@ -24338,7 +24350,7 @@
           <t>Arriendo</t>
         </is>
       </c>
-      <c r="F505" s="11" t="inlineStr">
+      <c r="F505" s="13" t="inlineStr">
         <is>
           <t>F-14491</t>
         </is>
@@ -24386,7 +24398,7 @@
           <t>Arriendo</t>
         </is>
       </c>
-      <c r="F506" s="11" t="inlineStr">
+      <c r="F506" s="13" t="inlineStr">
         <is>
           <t>F-14492</t>
         </is>
@@ -24434,7 +24446,7 @@
           <t>Arriendo</t>
         </is>
       </c>
-      <c r="F507" s="11" t="inlineStr">
+      <c r="F507" s="13" t="inlineStr">
         <is>
           <t>F-14494</t>
         </is>
@@ -24482,7 +24494,7 @@
           <t>Arriendo</t>
         </is>
       </c>
-      <c r="F508" s="11" t="inlineStr">
+      <c r="F508" s="13" t="inlineStr">
         <is>
           <t>F-14495</t>
         </is>
@@ -24530,7 +24542,7 @@
           <t>Arriendo</t>
         </is>
       </c>
-      <c r="F509" s="11" t="inlineStr">
+      <c r="F509" s="13" t="inlineStr">
         <is>
           <t>F-14543</t>
         </is>
@@ -24576,7 +24588,7 @@
           <t>Habilitación</t>
         </is>
       </c>
-      <c r="F510" s="11" t="inlineStr">
+      <c r="F510" s="13" t="inlineStr">
         <is>
           <t>F-14493</t>
         </is>
@@ -24624,7 +24636,7 @@
           <t>Serv. Admin</t>
         </is>
       </c>
-      <c r="F511" s="11" t="inlineStr">
+      <c r="F511" s="13" t="inlineStr">
         <is>
           <t>FEE-14497</t>
         </is>
@@ -24672,7 +24684,7 @@
           <t>Serv. Admin</t>
         </is>
       </c>
-      <c r="F512" s="11" t="inlineStr">
+      <c r="F512" s="13" t="inlineStr">
         <is>
           <t>FEE-14498</t>
         </is>
@@ -24720,7 +24732,7 @@
           <t>Serv. Admin</t>
         </is>
       </c>
-      <c r="F513" s="11" t="inlineStr">
+      <c r="F513" s="13" t="inlineStr">
         <is>
           <t>FEE-14523</t>
         </is>
@@ -24768,7 +24780,7 @@
           <t>Serv. Admin</t>
         </is>
       </c>
-      <c r="F514" s="11" t="inlineStr">
+      <c r="F514" s="13" t="inlineStr">
         <is>
           <t>FEE-14528</t>
         </is>
@@ -24816,7 +24828,7 @@
           <t>Serv. Admin</t>
         </is>
       </c>
-      <c r="F515" s="11" t="inlineStr">
+      <c r="F515" s="13" t="inlineStr">
         <is>
           <t>FEE-14530</t>
         </is>
@@ -24864,7 +24876,7 @@
           <t>Serv. Admin</t>
         </is>
       </c>
-      <c r="F516" s="11" t="inlineStr">
+      <c r="F516" s="13" t="inlineStr">
         <is>
           <t>FEE-14544</t>
         </is>
@@ -24912,7 +24924,7 @@
           <t>Arriendo</t>
         </is>
       </c>
-      <c r="F517" s="10" t="inlineStr">
+      <c r="F517" s="12" t="inlineStr">
         <is>
           <t>F-28</t>
         </is>
@@ -24960,7 +24972,7 @@
           <t>Arriendo</t>
         </is>
       </c>
-      <c r="F518" s="11" t="inlineStr">
+      <c r="F518" s="13" t="inlineStr">
         <is>
           <t>F-14467</t>
         </is>
@@ -25008,7 +25020,7 @@
           <t>Serv. Admin</t>
         </is>
       </c>
-      <c r="F519" s="11" t="inlineStr">
+      <c r="F519" s="13" t="inlineStr">
         <is>
           <t>FEE-14501</t>
         </is>
@@ -25056,7 +25068,7 @@
           <t>Arriendo</t>
         </is>
       </c>
-      <c r="F520" s="10" t="inlineStr">
+      <c r="F520" s="12" t="inlineStr">
         <is>
           <t>F-14470</t>
         </is>
@@ -25104,7 +25116,7 @@
           <t>Serv. Admin</t>
         </is>
       </c>
-      <c r="F521" s="10" t="inlineStr">
+      <c r="F521" s="12" t="inlineStr">
         <is>
           <t>FEE-14500</t>
         </is>
@@ -25152,7 +25164,7 @@
           <t>Arriendo</t>
         </is>
       </c>
-      <c r="F522" s="11" t="inlineStr">
+      <c r="F522" s="13" t="inlineStr">
         <is>
           <t>F-14473</t>
         </is>
@@ -25200,7 +25212,7 @@
           <t>Arriendo</t>
         </is>
       </c>
-      <c r="F523" s="10" t="inlineStr">
+      <c r="F523" s="12" t="inlineStr">
         <is>
           <t>F-14482</t>
         </is>
@@ -25248,7 +25260,7 @@
           <t>Serv. Admin</t>
         </is>
       </c>
-      <c r="F524" s="10" t="inlineStr">
+      <c r="F524" s="12" t="inlineStr">
         <is>
           <t>FEE-14520</t>
         </is>
@@ -25296,7 +25308,7 @@
           <t>Arriendo</t>
         </is>
       </c>
-      <c r="F525" s="11" t="inlineStr">
+      <c r="F525" s="13" t="inlineStr">
         <is>
           <t>F-14479</t>
         </is>
@@ -25344,7 +25356,7 @@
           <t>Serv. Admin</t>
         </is>
       </c>
-      <c r="F526" s="11" t="inlineStr">
+      <c r="F526" s="13" t="inlineStr">
         <is>
           <t>FEE-14517</t>
         </is>
@@ -25392,7 +25404,7 @@
           <t>Arriendo</t>
         </is>
       </c>
-      <c r="F527" s="10" t="inlineStr">
+      <c r="F527" s="12" t="inlineStr">
         <is>
           <t>F-14476</t>
         </is>
@@ -25440,7 +25452,7 @@
           <t>Serv. Admin</t>
         </is>
       </c>
-      <c r="F528" s="10" t="inlineStr">
+      <c r="F528" s="12" t="inlineStr">
         <is>
           <t>FEE-14512</t>
         </is>
@@ -25488,7 +25500,7 @@
           <t>Arriendo</t>
         </is>
       </c>
-      <c r="F529" s="11" t="inlineStr">
+      <c r="F529" s="13" t="inlineStr">
         <is>
           <t>F-14468</t>
         </is>
@@ -25536,7 +25548,7 @@
           <t>Arriendo</t>
         </is>
       </c>
-      <c r="F530" s="10" t="inlineStr">
+      <c r="F530" s="12" t="inlineStr">
         <is>
           <t>F-14484</t>
         </is>
@@ -25584,7 +25596,7 @@
           <t>Arriendo</t>
         </is>
       </c>
-      <c r="F531" s="11" t="inlineStr">
+      <c r="F531" s="13" t="inlineStr">
         <is>
           <t>F-14465</t>
         </is>
@@ -25632,7 +25644,7 @@
           <t>Arriendo</t>
         </is>
       </c>
-      <c r="F532" s="10" t="inlineStr">
+      <c r="F532" s="12" t="inlineStr">
         <is>
           <t>F-14474</t>
         </is>
@@ -25680,7 +25692,7 @@
           <t>Serv. Admin</t>
         </is>
       </c>
-      <c r="F533" s="10" t="inlineStr">
+      <c r="F533" s="12" t="inlineStr">
         <is>
           <t>FEE-14508</t>
         </is>
@@ -25728,7 +25740,7 @@
           <t>Arriendo</t>
         </is>
       </c>
-      <c r="F534" s="11" t="inlineStr">
+      <c r="F534" s="13" t="inlineStr">
         <is>
           <t>F-14478</t>
         </is>
@@ -25776,7 +25788,7 @@
           <t>Arriendo</t>
         </is>
       </c>
-      <c r="F535" s="10" t="inlineStr">
+      <c r="F535" s="12" t="inlineStr">
         <is>
           <t>F-14477</t>
         </is>
@@ -25824,7 +25836,7 @@
           <t>Arriendo</t>
         </is>
       </c>
-      <c r="F536" s="10" t="inlineStr">
+      <c r="F536" s="12" t="inlineStr">
         <is>
           <t>F-14481</t>
         </is>
@@ -25872,7 +25884,7 @@
           <t>Arriendo</t>
         </is>
       </c>
-      <c r="F537" s="11" t="inlineStr">
+      <c r="F537" s="13" t="inlineStr">
         <is>
           <t>F-14541</t>
         </is>
@@ -25920,7 +25932,7 @@
           <t>Arriendo</t>
         </is>
       </c>
-      <c r="F538" s="10" t="inlineStr">
+      <c r="F538" s="12" t="inlineStr">
         <is>
           <t>F-14480</t>
         </is>
@@ -25968,7 +25980,7 @@
           <t>Arriendo</t>
         </is>
       </c>
-      <c r="F539" s="11" t="inlineStr">
+      <c r="F539" s="13" t="inlineStr">
         <is>
           <t>F-14469</t>
         </is>
@@ -26016,7 +26028,7 @@
           <t>Arriendo</t>
         </is>
       </c>
-      <c r="F540" s="10" t="inlineStr">
+      <c r="F540" s="12" t="inlineStr">
         <is>
           <t>F-14485</t>
         </is>
@@ -26064,7 +26076,7 @@
           <t>Serv. Admin</t>
         </is>
       </c>
-      <c r="F541" s="10" t="inlineStr">
+      <c r="F541" s="12" t="inlineStr">
         <is>
           <t>FEE-14526</t>
         </is>
@@ -26112,7 +26124,7 @@
           <t>Arriendo</t>
         </is>
       </c>
-      <c r="F542" s="11" t="inlineStr">
+      <c r="F542" s="13" t="inlineStr">
         <is>
           <t>F-14464</t>
         </is>
@@ -26158,7 +26170,7 @@
           <t>Serv. Admin</t>
         </is>
       </c>
-      <c r="F543" s="11" t="inlineStr">
+      <c r="F543" s="13" t="inlineStr">
         <is>
           <t>FEE-14496</t>
         </is>
@@ -26206,7 +26218,7 @@
           <t>Arriendo</t>
         </is>
       </c>
-      <c r="F544" s="10" t="inlineStr">
+      <c r="F544" s="12" t="inlineStr">
         <is>
           <t>F-14483</t>
         </is>
@@ -26254,7 +26266,7 @@
           <t>Serv. Admin</t>
         </is>
       </c>
-      <c r="F545" s="10" t="inlineStr">
+      <c r="F545" s="12" t="inlineStr">
         <is>
           <t>FEE-14524</t>
         </is>
@@ -26302,7 +26314,7 @@
           <t>Arriendo</t>
         </is>
       </c>
-      <c r="F546" s="11" t="inlineStr">
+      <c r="F546" s="13" t="inlineStr">
         <is>
           <t>F-14488</t>
         </is>
@@ -26350,7 +26362,7 @@
           <t>Arriendo</t>
         </is>
       </c>
-      <c r="F547" s="11" t="inlineStr">
+      <c r="F547" s="13" t="inlineStr">
         <is>
           <t>F-14489</t>
         </is>
@@ -26398,7 +26410,7 @@
           <t>Serv. Admin</t>
         </is>
       </c>
-      <c r="F548" s="11" t="inlineStr">
+      <c r="F548" s="13" t="inlineStr">
         <is>
           <t>FEE-14537</t>
         </is>
@@ -26446,7 +26458,7 @@
           <t>Serv. Admin</t>
         </is>
       </c>
-      <c r="F549" s="11" t="inlineStr">
+      <c r="F549" s="13" t="inlineStr">
         <is>
           <t>FEE-14538</t>
         </is>
@@ -26494,7 +26506,7 @@
           <t>Arriendo</t>
         </is>
       </c>
-      <c r="F550" s="10" t="inlineStr">
+      <c r="F550" s="12" t="inlineStr">
         <is>
           <t>F-32</t>
         </is>
@@ -26542,7 +26554,7 @@
           <t>Arriendo</t>
         </is>
       </c>
-      <c r="F551" s="10" t="inlineStr">
+      <c r="F551" s="12" t="inlineStr">
         <is>
           <t>F-35</t>
         </is>
@@ -26590,7 +26602,7 @@
           <t>Arriendo</t>
         </is>
       </c>
-      <c r="F552" s="11" t="inlineStr">
+      <c r="F552" s="13" t="inlineStr">
         <is>
           <t>F-29</t>
         </is>
@@ -26638,7 +26650,7 @@
           <t>Serv. Admin</t>
         </is>
       </c>
-      <c r="F553" s="11" t="inlineStr">
+      <c r="F553" s="13" t="inlineStr">
         <is>
           <t>FEE-14521</t>
         </is>
@@ -26686,7 +26698,7 @@
           <t>Arriendo</t>
         </is>
       </c>
-      <c r="F554" s="10" t="inlineStr">
+      <c r="F554" s="12" t="inlineStr">
         <is>
           <t>F-14475</t>
         </is>
@@ -26734,7 +26746,7 @@
           <t>Serv. Admin</t>
         </is>
       </c>
-      <c r="F555" s="10" t="inlineStr">
+      <c r="F555" s="12" t="inlineStr">
         <is>
           <t>FEE-14532</t>
         </is>
@@ -26780,7 +26792,7 @@
           <t>Arriendo</t>
         </is>
       </c>
-      <c r="F556" s="11" t="inlineStr">
+      <c r="F556" s="13" t="inlineStr">
         <is>
           <t>F-14463</t>
         </is>
@@ -26828,7 +26840,7 @@
           <t>Arriendo</t>
         </is>
       </c>
-      <c r="F557" s="11" t="inlineStr">
+      <c r="F557" s="13" t="inlineStr">
         <is>
           <t>F-14546</t>
         </is>
@@ -26876,7 +26888,7 @@
           <t>Arriendo</t>
         </is>
       </c>
-      <c r="F558" s="10" t="inlineStr">
+      <c r="F558" s="12" t="inlineStr">
         <is>
           <t>F-14487</t>
         </is>
@@ -26924,7 +26936,7 @@
           <t>Arriendo</t>
         </is>
       </c>
-      <c r="F559" s="11" t="inlineStr">
+      <c r="F559" s="13" t="inlineStr">
         <is>
           <t>F-14486</t>
         </is>
@@ -26972,7 +26984,7 @@
           <t>Arriendo</t>
         </is>
       </c>
-      <c r="F560" s="10" t="inlineStr">
+      <c r="F560" s="12" t="inlineStr">
         <is>
           <t>F-31</t>
         </is>
@@ -27020,7 +27032,7 @@
           <t>Arriendo</t>
         </is>
       </c>
-      <c r="F561" s="11" t="inlineStr">
+      <c r="F561" s="13" t="inlineStr">
         <is>
           <t>F-30</t>
         </is>
@@ -27068,7 +27080,7 @@
           <t>Serv. Admin</t>
         </is>
       </c>
-      <c r="F562" s="11" t="inlineStr">
+      <c r="F562" s="13" t="inlineStr">
         <is>
           <t>FEE-14503</t>
         </is>
@@ -27116,7 +27128,7 @@
           <t>Arriendo</t>
         </is>
       </c>
-      <c r="F563" s="10" t="inlineStr">
+      <c r="F563" s="12" t="inlineStr">
         <is>
           <t>F-34</t>
         </is>
@@ -27164,7 +27176,7 @@
           <t>Serv. Admin</t>
         </is>
       </c>
-      <c r="F564" s="10" t="inlineStr">
+      <c r="F564" s="12" t="inlineStr">
         <is>
           <t>FEE-14545</t>
         </is>
@@ -27212,7 +27224,7 @@
           <t>Arriendo</t>
         </is>
       </c>
-      <c r="F565" s="11" t="inlineStr">
+      <c r="F565" s="13" t="inlineStr">
         <is>
           <t>F-14542</t>
         </is>
@@ -27260,7 +27272,7 @@
           <t>Serv. Admin</t>
         </is>
       </c>
-      <c r="F566" s="10" t="inlineStr">
+      <c r="F566" s="12" t="inlineStr">
         <is>
           <t>FEE-14502</t>
         </is>
@@ -27308,7 +27320,7 @@
           <t>Serv. Admin</t>
         </is>
       </c>
-      <c r="F567" s="11" t="inlineStr">
+      <c r="F567" s="13" t="inlineStr">
         <is>
           <t>FEE-14535</t>
         </is>
@@ -27354,7 +27366,7 @@
           <t>Serv. Admin</t>
         </is>
       </c>
-      <c r="F568" s="10" t="inlineStr">
+      <c r="F568" s="12" t="inlineStr">
         <is>
           <t>FEE-14534</t>
         </is>
@@ -27402,7 +27414,7 @@
           <t>Arriendo</t>
         </is>
       </c>
-      <c r="F569" s="11" t="inlineStr">
+      <c r="F569" s="13" t="inlineStr">
         <is>
           <t>F-33</t>
         </is>
@@ -27450,7 +27462,7 @@
           <t>Arriendo</t>
         </is>
       </c>
-      <c r="F570" s="10" t="inlineStr">
+      <c r="F570" s="12" t="inlineStr">
         <is>
           <t>F-14548</t>
         </is>
@@ -27498,7 +27510,7 @@
           <t>Arriendo</t>
         </is>
       </c>
-      <c r="F571" s="10" t="inlineStr">
+      <c r="F571" s="12" t="inlineStr">
         <is>
           <t>F-14549</t>
         </is>
@@ -27546,7 +27558,7 @@
           <t>Arriendo</t>
         </is>
       </c>
-      <c r="F572" s="10" t="inlineStr">
+      <c r="F572" s="12" t="inlineStr">
         <is>
           <t>F-14552</t>
         </is>
@@ -27594,7 +27606,7 @@
           <t>Serv. Admin</t>
         </is>
       </c>
-      <c r="F573" s="10" t="inlineStr">
+      <c r="F573" s="12" t="inlineStr">
         <is>
           <t>FEE-14624</t>
         </is>
@@ -27642,7 +27654,7 @@
           <t>Arriendo</t>
         </is>
       </c>
-      <c r="F574" s="11" t="inlineStr">
+      <c r="F574" s="13" t="inlineStr">
         <is>
           <t>F-14554</t>
         </is>
@@ -27690,7 +27702,7 @@
           <t>Arriendo</t>
         </is>
       </c>
-      <c r="F575" s="10" t="inlineStr">
+      <c r="F575" s="12" t="inlineStr">
         <is>
           <t>F-14561</t>
         </is>
@@ -27738,7 +27750,7 @@
           <t>Arriendo</t>
         </is>
       </c>
-      <c r="F576" s="11" t="inlineStr">
+      <c r="F576" s="13" t="inlineStr">
         <is>
           <t>F-14557</t>
         </is>
@@ -27786,7 +27798,7 @@
           <t>Arriendo</t>
         </is>
       </c>
-      <c r="F577" s="10" t="inlineStr">
+      <c r="F577" s="12" t="inlineStr">
         <is>
           <t>F-14553</t>
         </is>
@@ -27834,7 +27846,7 @@
           <t>Arriendo</t>
         </is>
       </c>
-      <c r="F578" s="11" t="inlineStr">
+      <c r="F578" s="13" t="inlineStr">
         <is>
           <t>F-14555</t>
         </is>
@@ -27882,7 +27894,7 @@
           <t>Serv. Admin</t>
         </is>
       </c>
-      <c r="F579" s="11" t="inlineStr">
+      <c r="F579" s="13" t="inlineStr">
         <is>
           <t>FEE-14625</t>
         </is>
@@ -27930,7 +27942,7 @@
           <t>Arriendo</t>
         </is>
       </c>
-      <c r="F580" s="10" t="inlineStr">
+      <c r="F580" s="12" t="inlineStr">
         <is>
           <t>F-14551</t>
         </is>
@@ -27978,7 +27990,7 @@
           <t>Serv. Admin</t>
         </is>
       </c>
-      <c r="F581" s="10" t="inlineStr">
+      <c r="F581" s="12" t="inlineStr">
         <is>
           <t>FEE-14623</t>
         </is>
@@ -28026,7 +28038,7 @@
           <t>Arriendo</t>
         </is>
       </c>
-      <c r="F582" s="11" t="inlineStr">
+      <c r="F582" s="13" t="inlineStr">
         <is>
           <t>F-14556</t>
         </is>
@@ -28074,7 +28086,7 @@
           <t>Arriendo</t>
         </is>
       </c>
-      <c r="F583" s="10" t="inlineStr">
+      <c r="F583" s="12" t="inlineStr">
         <is>
           <t>F-14558</t>
         </is>
@@ -28122,7 +28134,7 @@
           <t>Arriendo</t>
         </is>
       </c>
-      <c r="F584" s="11" t="inlineStr">
+      <c r="F584" s="13" t="inlineStr">
         <is>
           <t>F-14564</t>
         </is>
@@ -28170,7 +28182,7 @@
           <t>Serv. Admin</t>
         </is>
       </c>
-      <c r="F585" s="11" t="inlineStr">
+      <c r="F585" s="13" t="inlineStr">
         <is>
           <t>FEE-14628</t>
         </is>
@@ -28218,7 +28230,7 @@
           <t>Arriendo</t>
         </is>
       </c>
-      <c r="F586" s="10" t="inlineStr">
+      <c r="F586" s="12" t="inlineStr">
         <is>
           <t>F-14550</t>
         </is>
@@ -28266,7 +28278,7 @@
           <t>Serv. Admin</t>
         </is>
       </c>
-      <c r="F587" s="10" t="inlineStr">
+      <c r="F587" s="12" t="inlineStr">
         <is>
           <t>FEE-14622</t>
         </is>
@@ -28314,7 +28326,7 @@
           <t>Arriendo</t>
         </is>
       </c>
-      <c r="F588" s="11" t="inlineStr">
+      <c r="F588" s="13" t="inlineStr">
         <is>
           <t>F-14562</t>
         </is>
@@ -28362,7 +28374,7 @@
           <t>Arriendo</t>
         </is>
       </c>
-      <c r="F589" s="11" t="inlineStr">
+      <c r="F589" s="13" t="inlineStr">
         <is>
           <t>F-14563</t>
         </is>
@@ -28410,7 +28422,7 @@
           <t>Arriendo</t>
         </is>
       </c>
-      <c r="F590" s="10" t="inlineStr">
+      <c r="F590" s="12" t="inlineStr">
         <is>
           <t>F-14559</t>
         </is>
@@ -28458,7 +28470,7 @@
           <t>Serv. Admin</t>
         </is>
       </c>
-      <c r="F591" s="10" t="inlineStr">
+      <c r="F591" s="12" t="inlineStr">
         <is>
           <t>FEE-14626</t>
         </is>
@@ -28506,7 +28518,7 @@
           <t>Arriendo</t>
         </is>
       </c>
-      <c r="F592" s="11" t="inlineStr">
+      <c r="F592" s="13" t="inlineStr">
         <is>
           <t>F-14560</t>
         </is>
@@ -28554,7 +28566,7 @@
           <t>Arriendo</t>
         </is>
       </c>
-      <c r="F593" s="10" t="inlineStr">
+      <c r="F593" s="12" t="inlineStr">
         <is>
           <t>F-14565</t>
         </is>
@@ -28602,7 +28614,7 @@
           <t>Arriendo</t>
         </is>
       </c>
-      <c r="F594" s="11" t="inlineStr">
+      <c r="F594" s="13" t="inlineStr">
         <is>
           <t>F-14568</t>
         </is>
@@ -28650,7 +28662,7 @@
           <t>Serv. Admin</t>
         </is>
       </c>
-      <c r="F595" s="11" t="inlineStr">
+      <c r="F595" s="13" t="inlineStr">
         <is>
           <t>FEE-14630</t>
         </is>
@@ -28698,7 +28710,7 @@
           <t>Arriendo</t>
         </is>
       </c>
-      <c r="F596" s="10" t="inlineStr">
+      <c r="F596" s="12" t="inlineStr">
         <is>
           <t>F-14580</t>
         </is>
@@ -28746,7 +28758,7 @@
           <t>Arriendo</t>
         </is>
       </c>
-      <c r="F597" s="11" t="inlineStr">
+      <c r="F597" s="13" t="inlineStr">
         <is>
           <t>F-14586</t>
         </is>
@@ -28794,7 +28806,7 @@
           <t>Arriendo</t>
         </is>
       </c>
-      <c r="F598" s="10" t="inlineStr">
+      <c r="F598" s="12" t="inlineStr">
         <is>
           <t>F-14570</t>
         </is>
@@ -28842,7 +28854,7 @@
           <t>Serv. Admin</t>
         </is>
       </c>
-      <c r="F599" s="10" t="inlineStr">
+      <c r="F599" s="12" t="inlineStr">
         <is>
           <t>FEE-14620</t>
         </is>
@@ -28888,7 +28900,7 @@
           <t>Arriendo</t>
         </is>
       </c>
-      <c r="F600" s="11" t="inlineStr">
+      <c r="F600" s="13" t="inlineStr">
         <is>
           <t>F-14576</t>
         </is>
@@ -28936,7 +28948,7 @@
           <t>Serv. Admin</t>
         </is>
       </c>
-      <c r="F601" s="11" t="inlineStr">
+      <c r="F601" s="13" t="inlineStr">
         <is>
           <t>FEE-14635</t>
         </is>
@@ -28984,7 +28996,7 @@
           <t>Arriendo</t>
         </is>
       </c>
-      <c r="F602" s="10" t="inlineStr">
+      <c r="F602" s="12" t="inlineStr">
         <is>
           <t>F-14567</t>
         </is>
@@ -29032,7 +29044,7 @@
           <t>Serv. Admin</t>
         </is>
       </c>
-      <c r="F603" s="10" t="inlineStr">
+      <c r="F603" s="12" t="inlineStr">
         <is>
           <t>FEE-14629</t>
         </is>
@@ -29080,7 +29092,7 @@
           <t>Arriendo</t>
         </is>
       </c>
-      <c r="F604" s="11" t="inlineStr">
+      <c r="F604" s="13" t="inlineStr">
         <is>
           <t>F-14572</t>
         </is>
@@ -29128,7 +29140,7 @@
           <t>Serv. Admin</t>
         </is>
       </c>
-      <c r="F605" s="11" t="inlineStr">
+      <c r="F605" s="13" t="inlineStr">
         <is>
           <t>FEE-14632</t>
         </is>
@@ -29176,7 +29188,7 @@
           <t>Arriendo</t>
         </is>
       </c>
-      <c r="F606" s="10" t="inlineStr">
+      <c r="F606" s="12" t="inlineStr">
         <is>
           <t>F-14571</t>
         </is>
@@ -29224,7 +29236,7 @@
           <t>Arriendo</t>
         </is>
       </c>
-      <c r="F607" s="10" t="inlineStr">
+      <c r="F607" s="12" t="inlineStr">
         <is>
           <t>F-14578</t>
         </is>
@@ -29272,7 +29284,7 @@
           <t>Arriendo</t>
         </is>
       </c>
-      <c r="F608" s="10" t="inlineStr">
+      <c r="F608" s="12" t="inlineStr">
         <is>
           <t>F-14585</t>
         </is>
@@ -29320,7 +29332,7 @@
           <t>Serv. Admin</t>
         </is>
       </c>
-      <c r="F609" s="10" t="inlineStr">
+      <c r="F609" s="12" t="inlineStr">
         <is>
           <t>FEE-14637</t>
         </is>
@@ -29368,7 +29380,7 @@
           <t>Arriendo</t>
         </is>
       </c>
-      <c r="F610" s="11" t="inlineStr">
+      <c r="F610" s="13" t="inlineStr">
         <is>
           <t>F-14581</t>
         </is>
@@ -29416,7 +29428,7 @@
           <t>Serv. Admin</t>
         </is>
       </c>
-      <c r="F611" s="11" t="inlineStr">
+      <c r="F611" s="13" t="inlineStr">
         <is>
           <t>FEE-14638</t>
         </is>
@@ -29464,7 +29476,7 @@
           <t>Arriendo</t>
         </is>
       </c>
-      <c r="F612" s="10" t="inlineStr">
+      <c r="F612" s="12" t="inlineStr">
         <is>
           <t>F-14566</t>
         </is>
@@ -29512,7 +29524,7 @@
           <t>Arriendo</t>
         </is>
       </c>
-      <c r="F613" s="11" t="inlineStr">
+      <c r="F613" s="13" t="inlineStr">
         <is>
           <t>F-14582</t>
         </is>
@@ -29560,7 +29572,7 @@
           <t>Serv. Admin</t>
         </is>
       </c>
-      <c r="F614" s="11" t="inlineStr">
+      <c r="F614" s="13" t="inlineStr">
         <is>
           <t>FEE-14639</t>
         </is>
@@ -29608,7 +29620,7 @@
           <t>Arriendo</t>
         </is>
       </c>
-      <c r="F615" s="10" t="inlineStr">
+      <c r="F615" s="12" t="inlineStr">
         <is>
           <t>F-14569</t>
         </is>
@@ -29656,7 +29668,7 @@
           <t>Serv. Admin</t>
         </is>
       </c>
-      <c r="F616" s="10" t="inlineStr">
+      <c r="F616" s="12" t="inlineStr">
         <is>
           <t>FEE-14631</t>
         </is>
@@ -29704,7 +29716,7 @@
           <t>Arriendo</t>
         </is>
       </c>
-      <c r="F617" s="11" t="inlineStr">
+      <c r="F617" s="13" t="inlineStr">
         <is>
           <t>F-14574</t>
         </is>
@@ -29752,7 +29764,7 @@
           <t>Serv. Admin</t>
         </is>
       </c>
-      <c r="F618" s="11" t="inlineStr">
+      <c r="F618" s="13" t="inlineStr">
         <is>
           <t>FEE-14634</t>
         </is>
@@ -29800,7 +29812,7 @@
           <t>Arriendo</t>
         </is>
       </c>
-      <c r="F619" s="10" t="inlineStr">
+      <c r="F619" s="12" t="inlineStr">
         <is>
           <t>F-14575</t>
         </is>
@@ -29848,7 +29860,7 @@
           <t>Arriendo</t>
         </is>
       </c>
-      <c r="F620" s="11" t="inlineStr">
+      <c r="F620" s="13" t="inlineStr">
         <is>
           <t>F-14584</t>
         </is>
@@ -29896,7 +29908,7 @@
           <t>Arriendo</t>
         </is>
       </c>
-      <c r="F621" s="10" t="inlineStr">
+      <c r="F621" s="12" t="inlineStr">
         <is>
           <t>F-14583</t>
         </is>
@@ -29944,7 +29956,7 @@
           <t>Arriendo</t>
         </is>
       </c>
-      <c r="F622" s="10" t="inlineStr">
+      <c r="F622" s="12" t="inlineStr">
         <is>
           <t>F-14668</t>
         </is>
@@ -29992,7 +30004,7 @@
           <t>Serv. Admin</t>
         </is>
       </c>
-      <c r="F623" s="10" t="inlineStr">
+      <c r="F623" s="12" t="inlineStr">
         <is>
           <t>FEE-14640</t>
         </is>
@@ -30040,7 +30052,7 @@
           <t>Serv. Admin</t>
         </is>
       </c>
-      <c r="F624" s="10" t="inlineStr">
+      <c r="F624" s="12" t="inlineStr">
         <is>
           <t>FEE-14669</t>
         </is>
@@ -30088,7 +30100,7 @@
           <t>Arriendo</t>
         </is>
       </c>
-      <c r="F625" s="11" t="inlineStr">
+      <c r="F625" s="13" t="inlineStr">
         <is>
           <t>F-14573</t>
         </is>
@@ -30136,7 +30148,7 @@
           <t>Serv. Admin</t>
         </is>
       </c>
-      <c r="F626" s="11" t="inlineStr">
+      <c r="F626" s="13" t="inlineStr">
         <is>
           <t>FEE-14633</t>
         </is>
@@ -30184,7 +30196,7 @@
           <t>Arriendo</t>
         </is>
       </c>
-      <c r="F627" s="10" t="inlineStr">
+      <c r="F627" s="12" t="inlineStr">
         <is>
           <t>F-14579</t>
         </is>
@@ -30232,7 +30244,7 @@
           <t>Arriendo</t>
         </is>
       </c>
-      <c r="F628" s="11" t="inlineStr">
+      <c r="F628" s="13" t="inlineStr">
         <is>
           <t>F-14577</t>
         </is>
@@ -30280,7 +30292,7 @@
           <t>Serv. Admin</t>
         </is>
       </c>
-      <c r="F629" s="11" t="inlineStr">
+      <c r="F629" s="13" t="inlineStr">
         <is>
           <t>FEE-14627</t>
         </is>
@@ -30328,7 +30340,7 @@
           <t>Serv. Admin</t>
         </is>
       </c>
-      <c r="F630" s="11" t="inlineStr">
+      <c r="F630" s="13" t="inlineStr">
         <is>
           <t>FEE-14636</t>
         </is>
@@ -30376,7 +30388,7 @@
           <t>Arriendo</t>
         </is>
       </c>
-      <c r="F631" s="10" t="inlineStr">
+      <c r="F631" s="12" t="inlineStr">
         <is>
           <t>F-14587</t>
         </is>
@@ -30424,7 +30436,7 @@
           <t>Arriendo</t>
         </is>
       </c>
-      <c r="F632" s="11" t="inlineStr">
+      <c r="F632" s="13" t="inlineStr">
         <is>
           <t>F-14592</t>
         </is>
@@ -30472,7 +30484,7 @@
           <t>Serv. Admin</t>
         </is>
       </c>
-      <c r="F633" s="11" t="inlineStr">
+      <c r="F633" s="13" t="inlineStr">
         <is>
           <t>FEE-14643</t>
         </is>
@@ -30520,7 +30532,7 @@
           <t>Arriendo</t>
         </is>
       </c>
-      <c r="F634" s="10" t="inlineStr">
+      <c r="F634" s="12" t="inlineStr">
         <is>
           <t>F-14597</t>
         </is>
@@ -30568,7 +30580,7 @@
           <t>Serv. Admin</t>
         </is>
       </c>
-      <c r="F635" s="10" t="inlineStr">
+      <c r="F635" s="12" t="inlineStr">
         <is>
           <t>FEE-14646</t>
         </is>
@@ -30616,7 +30628,7 @@
           <t>Arriendo</t>
         </is>
       </c>
-      <c r="F636" s="11" t="inlineStr">
+      <c r="F636" s="13" t="inlineStr">
         <is>
           <t>F-14589</t>
         </is>
@@ -30664,7 +30676,7 @@
           <t>Arriendo</t>
         </is>
       </c>
-      <c r="F637" s="11" t="inlineStr">
+      <c r="F637" s="13" t="inlineStr">
         <is>
           <t>F-14591</t>
         </is>
@@ -30712,7 +30724,7 @@
           <t>Arriendo</t>
         </is>
       </c>
-      <c r="F638" s="11" t="inlineStr">
+      <c r="F638" s="13" t="inlineStr">
         <is>
           <t>F-14610</t>
         </is>
@@ -30760,7 +30772,7 @@
           <t>Arriendo</t>
         </is>
       </c>
-      <c r="F639" s="11" t="inlineStr">
+      <c r="F639" s="13" t="inlineStr">
         <is>
           <t>F-14615</t>
         </is>
@@ -30808,7 +30820,7 @@
           <t>Arriendo</t>
         </is>
       </c>
-      <c r="F640" s="11" t="inlineStr">
+      <c r="F640" s="13" t="inlineStr">
         <is>
           <t>F-14616</t>
         </is>
@@ -30856,7 +30868,7 @@
           <t>Arriendo</t>
         </is>
       </c>
-      <c r="F641" s="11" t="inlineStr">
+      <c r="F641" s="13" t="inlineStr">
         <is>
           <t>F-14665</t>
         </is>
@@ -30904,7 +30916,7 @@
           <t>Habilitación</t>
         </is>
       </c>
-      <c r="F642" s="11" t="inlineStr">
+      <c r="F642" s="13" t="inlineStr">
         <is>
           <t>F-14614</t>
         </is>
@@ -30952,7 +30964,7 @@
           <t>Serv. Admin</t>
         </is>
       </c>
-      <c r="F643" s="11" t="inlineStr">
+      <c r="F643" s="13" t="inlineStr">
         <is>
           <t>FEE-14641</t>
         </is>
@@ -31000,7 +31012,7 @@
           <t>Serv. Admin</t>
         </is>
       </c>
-      <c r="F644" s="11" t="inlineStr">
+      <c r="F644" s="13" t="inlineStr">
         <is>
           <t>FEE-14642</t>
         </is>
@@ -31048,7 +31060,7 @@
           <t>Serv. Admin</t>
         </is>
       </c>
-      <c r="F645" s="11" t="inlineStr">
+      <c r="F645" s="13" t="inlineStr">
         <is>
           <t>FEE-14654</t>
         </is>
@@ -31096,7 +31108,7 @@
           <t>Serv. Admin</t>
         </is>
       </c>
-      <c r="F646" s="11" t="inlineStr">
+      <c r="F646" s="13" t="inlineStr">
         <is>
           <t>FEE-14658</t>
         </is>
@@ -31144,7 +31156,7 @@
           <t>Serv. Admin</t>
         </is>
       </c>
-      <c r="F647" s="11" t="inlineStr">
+      <c r="F647" s="13" t="inlineStr">
         <is>
           <t>FEE-14659</t>
         </is>
@@ -31192,7 +31204,7 @@
           <t>Arriendo</t>
         </is>
       </c>
-      <c r="F648" s="10" t="inlineStr">
+      <c r="F648" s="12" t="inlineStr">
         <is>
           <t>F-36</t>
         </is>
@@ -31240,7 +31252,7 @@
           <t>Arriendo</t>
         </is>
       </c>
-      <c r="F649" s="11" t="inlineStr">
+      <c r="F649" s="13" t="inlineStr">
         <is>
           <t>F-14593</t>
         </is>
@@ -31288,7 +31300,7 @@
           <t>Serv. Admin</t>
         </is>
       </c>
-      <c r="F650" s="11" t="inlineStr">
+      <c r="F650" s="13" t="inlineStr">
         <is>
           <t>FEE-14644</t>
         </is>
@@ -31336,7 +31348,7 @@
           <t>Arriendo</t>
         </is>
       </c>
-      <c r="F651" s="10" t="inlineStr">
+      <c r="F651" s="12" t="inlineStr">
         <is>
           <t>F-14596</t>
         </is>
@@ -31384,7 +31396,7 @@
           <t>Serv. Admin</t>
         </is>
       </c>
-      <c r="F652" s="10" t="inlineStr">
+      <c r="F652" s="12" t="inlineStr">
         <is>
           <t>FEE-14645</t>
         </is>
@@ -31432,7 +31444,7 @@
           <t>Arriendo</t>
         </is>
       </c>
-      <c r="F653" s="11" t="inlineStr">
+      <c r="F653" s="13" t="inlineStr">
         <is>
           <t>F-14598</t>
         </is>
@@ -31480,7 +31492,7 @@
           <t>Arriendo</t>
         </is>
       </c>
-      <c r="F654" s="10" t="inlineStr">
+      <c r="F654" s="12" t="inlineStr">
         <is>
           <t>F-14608</t>
         </is>
@@ -31528,7 +31540,7 @@
           <t>Serv. Admin</t>
         </is>
       </c>
-      <c r="F655" s="10" t="inlineStr">
+      <c r="F655" s="12" t="inlineStr">
         <is>
           <t>FEE-14651</t>
         </is>
@@ -31576,7 +31588,7 @@
           <t>Arriendo</t>
         </is>
       </c>
-      <c r="F656" s="11" t="inlineStr">
+      <c r="F656" s="13" t="inlineStr">
         <is>
           <t>F-14604</t>
         </is>
@@ -31624,7 +31636,7 @@
           <t>Serv. Admin</t>
         </is>
       </c>
-      <c r="F657" s="11" t="inlineStr">
+      <c r="F657" s="13" t="inlineStr">
         <is>
           <t>FEE-14649</t>
         </is>
@@ -31672,7 +31684,7 @@
           <t>Arriendo</t>
         </is>
       </c>
-      <c r="F658" s="10" t="inlineStr">
+      <c r="F658" s="12" t="inlineStr">
         <is>
           <t>F-14601</t>
         </is>
@@ -31720,7 +31732,7 @@
           <t>Serv. Admin</t>
         </is>
       </c>
-      <c r="F659" s="10" t="inlineStr">
+      <c r="F659" s="12" t="inlineStr">
         <is>
           <t>FEE-14648</t>
         </is>
@@ -31768,7 +31780,7 @@
           <t>Arriendo</t>
         </is>
       </c>
-      <c r="F660" s="11" t="inlineStr">
+      <c r="F660" s="13" t="inlineStr">
         <is>
           <t>F-14594</t>
         </is>
@@ -31816,7 +31828,7 @@
           <t>Arriendo</t>
         </is>
       </c>
-      <c r="F661" s="10" t="inlineStr">
+      <c r="F661" s="12" t="inlineStr">
         <is>
           <t>F-14612</t>
         </is>
@@ -31864,7 +31876,7 @@
           <t>Arriendo</t>
         </is>
       </c>
-      <c r="F662" s="11" t="inlineStr">
+      <c r="F662" s="13" t="inlineStr">
         <is>
           <t>F-14590</t>
         </is>
@@ -31912,7 +31924,7 @@
           <t>Arriendo</t>
         </is>
       </c>
-      <c r="F663" s="10" t="inlineStr">
+      <c r="F663" s="12" t="inlineStr">
         <is>
           <t>F-14599</t>
         </is>
@@ -31960,7 +31972,7 @@
           <t>Serv. Admin</t>
         </is>
       </c>
-      <c r="F664" s="10" t="inlineStr">
+      <c r="F664" s="12" t="inlineStr">
         <is>
           <t>FEE-14647</t>
         </is>
@@ -32008,7 +32020,7 @@
           <t>Arriendo</t>
         </is>
       </c>
-      <c r="F665" s="11" t="inlineStr">
+      <c r="F665" s="13" t="inlineStr">
         <is>
           <t>F-14603</t>
         </is>
@@ -32056,7 +32068,7 @@
           <t>Arriendo</t>
         </is>
       </c>
-      <c r="F666" s="10" t="inlineStr">
+      <c r="F666" s="12" t="inlineStr">
         <is>
           <t>F-14602</t>
         </is>
@@ -32104,7 +32116,7 @@
           <t>Arriendo</t>
         </is>
       </c>
-      <c r="F667" s="10" t="inlineStr">
+      <c r="F667" s="12" t="inlineStr">
         <is>
           <t>F-14606</t>
         </is>
@@ -32152,7 +32164,7 @@
           <t>Arriendo</t>
         </is>
       </c>
-      <c r="F668" s="11" t="inlineStr">
+      <c r="F668" s="13" t="inlineStr">
         <is>
           <t>F-14662</t>
         </is>
@@ -32200,7 +32212,7 @@
           <t>Arriendo</t>
         </is>
       </c>
-      <c r="F669" s="10" t="inlineStr">
+      <c r="F669" s="12" t="inlineStr">
         <is>
           <t>F-14605</t>
         </is>
@@ -32248,7 +32260,7 @@
           <t>Arriendo</t>
         </is>
       </c>
-      <c r="F670" s="11" t="inlineStr">
+      <c r="F670" s="13" t="inlineStr">
         <is>
           <t>F-14595</t>
         </is>
@@ -32296,7 +32308,7 @@
           <t>Arriendo</t>
         </is>
       </c>
-      <c r="F671" s="10" t="inlineStr">
+      <c r="F671" s="12" t="inlineStr">
         <is>
           <t>F-14613</t>
         </is>
@@ -32344,7 +32356,7 @@
           <t>Serv. Admin</t>
         </is>
       </c>
-      <c r="F672" s="10" t="inlineStr">
+      <c r="F672" s="12" t="inlineStr">
         <is>
           <t>FEE-14657</t>
         </is>
@@ -32392,7 +32404,7 @@
           <t>Arriendo</t>
         </is>
       </c>
-      <c r="F673" s="11" t="inlineStr">
+      <c r="F673" s="13" t="inlineStr">
         <is>
           <t>F-14611</t>
         </is>
@@ -32440,7 +32452,7 @@
           <t>Serv. Admin</t>
         </is>
       </c>
-      <c r="F674" s="11" t="inlineStr">
+      <c r="F674" s="13" t="inlineStr">
         <is>
           <t>FEE-14656</t>
         </is>
@@ -32488,7 +32500,7 @@
           <t>Arriendo</t>
         </is>
       </c>
-      <c r="F675" s="10" t="inlineStr">
+      <c r="F675" s="12" t="inlineStr">
         <is>
           <t>F-14607</t>
         </is>
@@ -32536,7 +32548,7 @@
           <t>Arriendo</t>
         </is>
       </c>
-      <c r="F676" s="10" t="inlineStr">
+      <c r="F676" s="12" t="inlineStr">
         <is>
           <t>F-14609</t>
         </is>
@@ -32584,7 +32596,7 @@
           <t>Serv. Admin</t>
         </is>
       </c>
-      <c r="F677" s="10" t="inlineStr">
+      <c r="F677" s="12" t="inlineStr">
         <is>
           <t>FEE-14650</t>
         </is>
@@ -32632,7 +32644,7 @@
           <t>Serv. Admin</t>
         </is>
       </c>
-      <c r="F678" s="10" t="inlineStr">
+      <c r="F678" s="12" t="inlineStr">
         <is>
           <t>FEE-14652</t>
         </is>
@@ -32680,7 +32692,7 @@
           <t>Arriendo</t>
         </is>
       </c>
-      <c r="F679" s="11" t="inlineStr">
+      <c r="F679" s="13" t="inlineStr">
         <is>
           <t>F-37</t>
         </is>
@@ -32728,7 +32740,7 @@
           <t>Serv. Admin</t>
         </is>
       </c>
-      <c r="F680" s="11" t="inlineStr">
+      <c r="F680" s="13" t="inlineStr">
         <is>
           <t>FEE-14653</t>
         </is>
@@ -32776,7 +32788,7 @@
           <t>Arriendo</t>
         </is>
       </c>
-      <c r="F681" s="10" t="inlineStr">
+      <c r="F681" s="12" t="inlineStr">
         <is>
           <t>F-14600</t>
         </is>
@@ -32824,7 +32836,7 @@
           <t>Serv. Admin</t>
         </is>
       </c>
-      <c r="F682" s="10" t="inlineStr">
+      <c r="F682" s="12" t="inlineStr">
         <is>
           <t>FEE-14621</t>
         </is>
@@ -32870,7 +32882,7 @@
           <t>Arriendo</t>
         </is>
       </c>
-      <c r="F683" s="11" t="inlineStr">
+      <c r="F683" s="13" t="inlineStr">
         <is>
           <t>F-14588</t>
         </is>
@@ -32918,7 +32930,7 @@
           <t>Arriendo</t>
         </is>
       </c>
-      <c r="F684" s="10" t="inlineStr">
+      <c r="F684" s="12" t="inlineStr">
         <is>
           <t>F-14618</t>
         </is>
@@ -32966,7 +32978,7 @@
           <t>Arriendo</t>
         </is>
       </c>
-      <c r="F685" s="11" t="inlineStr">
+      <c r="F685" s="13" t="inlineStr">
         <is>
           <t>F-14617</t>
         </is>
@@ -33014,7 +33026,7 @@
           <t>Arriendo</t>
         </is>
       </c>
-      <c r="F686" s="10" t="inlineStr">
+      <c r="F686" s="12" t="inlineStr">
         <is>
           <t>F-39</t>
         </is>
@@ -33062,7 +33074,7 @@
           <t>Arriendo</t>
         </is>
       </c>
-      <c r="F687" s="11" t="inlineStr">
+      <c r="F687" s="13" t="inlineStr">
         <is>
           <t>F-38</t>
         </is>
@@ -33110,7 +33122,7 @@
           <t>Arriendo</t>
         </is>
       </c>
-      <c r="F688" s="11" t="inlineStr">
+      <c r="F688" s="13" t="inlineStr">
         <is>
           <t>F-42</t>
         </is>
@@ -33158,7 +33170,7 @@
           <t>Serv. Admin</t>
         </is>
       </c>
-      <c r="F689" s="11" t="inlineStr">
+      <c r="F689" s="13" t="inlineStr">
         <is>
           <t>FEE-14655</t>
         </is>
@@ -33206,7 +33218,7 @@
           <t>Serv. Admin</t>
         </is>
       </c>
-      <c r="F690" s="11" t="inlineStr">
+      <c r="F690" s="13" t="inlineStr">
         <is>
           <t>FEE-14666</t>
         </is>
@@ -33254,7 +33266,7 @@
           <t>Arriendo</t>
         </is>
       </c>
-      <c r="F691" s="10" t="inlineStr">
+      <c r="F691" s="12" t="inlineStr">
         <is>
           <t>F-14663</t>
         </is>
@@ -33302,7 +33314,7 @@
           <t>Arriendo</t>
         </is>
       </c>
-      <c r="F692" s="10" t="inlineStr">
+      <c r="F692" s="12" t="inlineStr">
         <is>
           <t>F-14664</t>
         </is>
@@ -33350,7 +33362,7 @@
           <t>Arriendo</t>
         </is>
       </c>
-      <c r="F693" s="11" t="inlineStr">
+      <c r="F693" s="13" t="inlineStr">
         <is>
           <t>F-41</t>
         </is>
@@ -33398,7 +33410,7 @@
           <t>Habilitación</t>
         </is>
       </c>
-      <c r="F694" s="10" t="inlineStr">
+      <c r="F694" s="12" t="inlineStr">
         <is>
           <t>F-14667</t>
         </is>
@@ -33446,7 +33458,7 @@
           <t>Serv. Admin</t>
         </is>
       </c>
-      <c r="F695" s="11" t="inlineStr">
+      <c r="F695" s="13" t="inlineStr">
         <is>
           <t>FEE-14660</t>
         </is>
@@ -33494,7 +33506,7 @@
           <t>Serv. Admin</t>
         </is>
       </c>
-      <c r="F696" s="10" t="inlineStr">
+      <c r="F696" s="12" t="inlineStr">
         <is>
           <t>FEE-14619</t>
         </is>
@@ -33540,7 +33552,7 @@
           <t>Serv. Admin</t>
         </is>
       </c>
-      <c r="F697" s="11" t="inlineStr">
+      <c r="F697" s="13" t="inlineStr">
         <is>
           <t>FEE-14661</t>
         </is>
@@ -33588,7 +33600,7 @@
           <t>Arriendo</t>
         </is>
       </c>
-      <c r="F698" s="10" t="inlineStr">
+      <c r="F698" s="12" t="inlineStr">
         <is>
           <t>F-40</t>
         </is>
@@ -33636,7 +33648,7 @@
           <t>Arriendo</t>
         </is>
       </c>
-      <c r="F699" s="11" t="inlineStr">
+      <c r="F699" s="13" t="inlineStr">
         <is>
           <t>F-14682</t>
         </is>
@@ -33684,7 +33696,7 @@
           <t>Arriendo</t>
         </is>
       </c>
-      <c r="F700" s="11" t="inlineStr">
+      <c r="F700" s="13" t="inlineStr">
         <is>
           <t>F-14683</t>
         </is>
@@ -33732,7 +33744,7 @@
           <t>Arriendo</t>
         </is>
       </c>
-      <c r="F701" s="11" t="inlineStr">
+      <c r="F701" s="13" t="inlineStr">
         <is>
           <t>F-14684</t>
         </is>
@@ -33780,7 +33792,7 @@
           <t>Serv. Admin</t>
         </is>
       </c>
-      <c r="F702" s="11" t="inlineStr">
+      <c r="F702" s="13" t="inlineStr">
         <is>
           <t>FEE-14762</t>
         </is>
@@ -33828,7 +33840,7 @@
           <t>Arriendo</t>
         </is>
       </c>
-      <c r="F703" s="10" t="inlineStr">
+      <c r="F703" s="12" t="inlineStr">
         <is>
           <t>F-14681</t>
         </is>
@@ -33876,7 +33888,7 @@
           <t>Arriendo</t>
         </is>
       </c>
-      <c r="F704" s="11" t="inlineStr">
+      <c r="F704" s="13" t="inlineStr">
         <is>
           <t>F-14739</t>
         </is>
@@ -33924,7 +33936,7 @@
           <t>Arriendo</t>
         </is>
       </c>
-      <c r="F705" s="10" t="inlineStr">
+      <c r="F705" s="12" t="inlineStr">
         <is>
           <t>F-14675</t>
         </is>
@@ -33972,7 +33984,7 @@
           <t>Arriendo</t>
         </is>
       </c>
-      <c r="F706" s="11" t="inlineStr">
+      <c r="F706" s="13" t="inlineStr">
         <is>
           <t>F-14679</t>
         </is>
@@ -34020,7 +34032,7 @@
           <t>Arriendo</t>
         </is>
       </c>
-      <c r="F707" s="10" t="inlineStr">
+      <c r="F707" s="12" t="inlineStr">
         <is>
           <t>F-14677</t>
         </is>
@@ -34068,7 +34080,7 @@
           <t>Serv. Admin</t>
         </is>
       </c>
-      <c r="F708" s="10" t="inlineStr">
+      <c r="F708" s="12" t="inlineStr">
         <is>
           <t>FEE-14751</t>
         </is>
@@ -34116,7 +34128,7 @@
           <t>Arriendo</t>
         </is>
       </c>
-      <c r="F709" s="11" t="inlineStr">
+      <c r="F709" s="13" t="inlineStr">
         <is>
           <t>F-14673</t>
         </is>
@@ -34164,7 +34176,7 @@
           <t>Serv. Admin</t>
         </is>
       </c>
-      <c r="F710" s="11" t="inlineStr">
+      <c r="F710" s="13" t="inlineStr">
         <is>
           <t>FEE-14761</t>
         </is>
@@ -34212,7 +34224,7 @@
           <t>Arriendo</t>
         </is>
       </c>
-      <c r="F711" s="10" t="inlineStr">
+      <c r="F711" s="12" t="inlineStr">
         <is>
           <t>F-14676</t>
         </is>
@@ -34260,7 +34272,7 @@
           <t>Arriendo</t>
         </is>
       </c>
-      <c r="F712" s="11" t="inlineStr">
+      <c r="F712" s="13" t="inlineStr">
         <is>
           <t>F-14678</t>
         </is>
@@ -34308,7 +34320,7 @@
           <t>Arriendo</t>
         </is>
       </c>
-      <c r="F713" s="10" t="inlineStr">
+      <c r="F713" s="12" t="inlineStr">
         <is>
           <t>F-14672</t>
         </is>
@@ -34356,7 +34368,7 @@
           <t>Serv. Admin</t>
         </is>
       </c>
-      <c r="F714" s="10" t="inlineStr">
+      <c r="F714" s="12" t="inlineStr">
         <is>
           <t>FEE-14777</t>
         </is>
@@ -34404,7 +34416,7 @@
           <t>Arriendo</t>
         </is>
       </c>
-      <c r="F715" s="11" t="inlineStr">
+      <c r="F715" s="13" t="inlineStr">
         <is>
           <t>F-14680</t>
         </is>
@@ -34452,7 +34464,7 @@
           <t>Arriendo</t>
         </is>
       </c>
-      <c r="F716" s="11" t="inlineStr">
+      <c r="F716" s="13" t="inlineStr">
         <is>
           <t>F-14782</t>
         </is>
@@ -34500,7 +34512,7 @@
           <t>Serv. Admin</t>
         </is>
       </c>
-      <c r="F717" s="11" t="inlineStr">
+      <c r="F717" s="13" t="inlineStr">
         <is>
           <t>FEE-14760</t>
         </is>
@@ -34548,7 +34560,7 @@
           <t>Serv. Admin</t>
         </is>
       </c>
-      <c r="F718" s="11" t="inlineStr">
+      <c r="F718" s="13" t="inlineStr">
         <is>
           <t>FEE-14783</t>
         </is>
@@ -34596,7 +34608,7 @@
           <t>Arriendo</t>
         </is>
       </c>
-      <c r="F719" s="10" t="inlineStr">
+      <c r="F719" s="12" t="inlineStr">
         <is>
           <t>F-14670</t>
         </is>
@@ -34644,7 +34656,7 @@
           <t>Arriendo</t>
         </is>
       </c>
-      <c r="F720" s="10" t="inlineStr">
+      <c r="F720" s="12" t="inlineStr">
         <is>
           <t>F-14671</t>
         </is>
@@ -34692,7 +34704,7 @@
           <t>Arriendo</t>
         </is>
       </c>
-      <c r="F721" s="11" t="inlineStr">
+      <c r="F721" s="13" t="inlineStr">
         <is>
           <t>F-14674</t>
         </is>
@@ -34740,7 +34752,7 @@
           <t>Serv. Admin</t>
         </is>
       </c>
-      <c r="F722" s="11" t="inlineStr">
+      <c r="F722" s="13" t="inlineStr">
         <is>
           <t>FEE-14753</t>
         </is>
@@ -34788,7 +34800,7 @@
           <t>Arriendo</t>
         </is>
       </c>
-      <c r="F723" s="10" t="inlineStr">
+      <c r="F723" s="12" t="inlineStr">
         <is>
           <t>F-14694</t>
         </is>
@@ -34836,7 +34848,7 @@
           <t>Arriendo</t>
         </is>
       </c>
-      <c r="F724" s="11" t="inlineStr">
+      <c r="F724" s="13" t="inlineStr">
         <is>
           <t>F-14697</t>
         </is>
@@ -34884,7 +34896,7 @@
           <t>Serv. Admin</t>
         </is>
       </c>
-      <c r="F725" s="11" t="inlineStr">
+      <c r="F725" s="13" t="inlineStr">
         <is>
           <t>FEE-14755</t>
         </is>
@@ -34932,7 +34944,7 @@
           <t>Arriendo</t>
         </is>
       </c>
-      <c r="F726" s="10" t="inlineStr">
+      <c r="F726" s="12" t="inlineStr">
         <is>
           <t>F-14690</t>
         </is>
@@ -34980,7 +34992,7 @@
           <t>Arriendo</t>
         </is>
       </c>
-      <c r="F727" s="11" t="inlineStr">
+      <c r="F727" s="13" t="inlineStr">
         <is>
           <t>F-14693</t>
         </is>
@@ -35028,7 +35040,7 @@
           <t>Arriendo</t>
         </is>
       </c>
-      <c r="F728" s="10" t="inlineStr">
+      <c r="F728" s="12" t="inlineStr">
         <is>
           <t>F-14699</t>
         </is>
@@ -35076,7 +35088,7 @@
           <t>Serv. Admin</t>
         </is>
       </c>
-      <c r="F729" s="10" t="inlineStr">
+      <c r="F729" s="12" t="inlineStr">
         <is>
           <t>FEE-14780</t>
         </is>
@@ -35122,7 +35134,7 @@
           <t>Arriendo</t>
         </is>
       </c>
-      <c r="F730" s="11" t="inlineStr">
+      <c r="F730" s="13" t="inlineStr">
         <is>
           <t>F-14740</t>
         </is>
@@ -35170,7 +35182,7 @@
           <t>Serv. Admin</t>
         </is>
       </c>
-      <c r="F731" s="11" t="inlineStr">
+      <c r="F731" s="13" t="inlineStr">
         <is>
           <t>FEE-14756</t>
         </is>
@@ -35218,7 +35230,7 @@
           <t>Arriendo</t>
         </is>
       </c>
-      <c r="F732" s="10" t="inlineStr">
+      <c r="F732" s="12" t="inlineStr">
         <is>
           <t>F-14692</t>
         </is>
@@ -35266,7 +35278,7 @@
           <t>Serv. Admin</t>
         </is>
       </c>
-      <c r="F733" s="10" t="inlineStr">
+      <c r="F733" s="12" t="inlineStr">
         <is>
           <t>FEE-14752</t>
         </is>
@@ -35314,7 +35326,7 @@
           <t>Arriendo</t>
         </is>
       </c>
-      <c r="F734" s="11" t="inlineStr">
+      <c r="F734" s="13" t="inlineStr">
         <is>
           <t>F-14698</t>
         </is>
@@ -35362,7 +35374,7 @@
           <t>Serv. Admin</t>
         </is>
       </c>
-      <c r="F735" s="11" t="inlineStr">
+      <c r="F735" s="13" t="inlineStr">
         <is>
           <t>FEE-14759</t>
         </is>
@@ -35410,7 +35422,7 @@
           <t>Arriendo</t>
         </is>
       </c>
-      <c r="F736" s="10" t="inlineStr">
+      <c r="F736" s="12" t="inlineStr">
         <is>
           <t>F-14688</t>
         </is>
@@ -35458,7 +35470,7 @@
           <t>Arriendo</t>
         </is>
       </c>
-      <c r="F737" s="10" t="inlineStr">
+      <c r="F737" s="12" t="inlineStr">
         <is>
           <t>F-14732</t>
         </is>
@@ -35506,7 +35518,7 @@
           <t>Arriendo</t>
         </is>
       </c>
-      <c r="F738" s="10" t="inlineStr">
+      <c r="F738" s="12" t="inlineStr">
         <is>
           <t>F-14734</t>
         </is>
@@ -35554,7 +35566,7 @@
           <t>Serv. Admin</t>
         </is>
       </c>
-      <c r="F739" s="10" t="inlineStr">
+      <c r="F739" s="12" t="inlineStr">
         <is>
           <t>FEE-14764</t>
         </is>
@@ -35602,7 +35614,7 @@
           <t>Arriendo</t>
         </is>
       </c>
-      <c r="F740" s="11" t="inlineStr">
+      <c r="F740" s="13" t="inlineStr">
         <is>
           <t>F-14685</t>
         </is>
@@ -35650,7 +35662,7 @@
           <t>Serv. Admin</t>
         </is>
       </c>
-      <c r="F741" s="11" t="inlineStr">
+      <c r="F741" s="13" t="inlineStr">
         <is>
           <t>FEE-14776</t>
         </is>
@@ -35698,7 +35710,7 @@
           <t>Arriendo</t>
         </is>
       </c>
-      <c r="F742" s="10" t="inlineStr">
+      <c r="F742" s="12" t="inlineStr">
         <is>
           <t>F-14687</t>
         </is>
@@ -35746,7 +35758,7 @@
           <t>Arriendo</t>
         </is>
       </c>
-      <c r="F743" s="11" t="inlineStr">
+      <c r="F743" s="13" t="inlineStr">
         <is>
           <t>F-14781</t>
         </is>
@@ -35794,7 +35806,7 @@
           <t>Serv. Admin</t>
         </is>
       </c>
-      <c r="F744" s="11" t="inlineStr">
+      <c r="F744" s="13" t="inlineStr">
         <is>
           <t>FEE-14773</t>
         </is>
@@ -35842,7 +35854,7 @@
           <t>Arriendo</t>
         </is>
       </c>
-      <c r="F745" s="10" t="inlineStr">
+      <c r="F745" s="12" t="inlineStr">
         <is>
           <t>F-14696</t>
         </is>
@@ -35890,7 +35902,7 @@
           <t>Serv. Admin</t>
         </is>
       </c>
-      <c r="F746" s="10" t="inlineStr">
+      <c r="F746" s="12" t="inlineStr">
         <is>
           <t>FEE-14757</t>
         </is>
@@ -35938,7 +35950,7 @@
           <t>Arriendo</t>
         </is>
       </c>
-      <c r="F747" s="11" t="inlineStr">
+      <c r="F747" s="13" t="inlineStr">
         <is>
           <t>F-14686</t>
         </is>
@@ -35986,7 +35998,7 @@
           <t>Serv. Admin</t>
         </is>
       </c>
-      <c r="F748" s="11" t="inlineStr">
+      <c r="F748" s="13" t="inlineStr">
         <is>
           <t>FEE-14768</t>
         </is>
@@ -36034,7 +36046,7 @@
           <t>Arriendo</t>
         </is>
       </c>
-      <c r="F749" s="10" t="inlineStr">
+      <c r="F749" s="12" t="inlineStr">
         <is>
           <t>F-14700</t>
         </is>
@@ -36082,7 +36094,7 @@
           <t>Arriendo</t>
         </is>
       </c>
-      <c r="F750" s="11" t="inlineStr">
+      <c r="F750" s="13" t="inlineStr">
         <is>
           <t>F-14695</t>
         </is>
@@ -36130,7 +36142,7 @@
           <t>Arriendo</t>
         </is>
       </c>
-      <c r="F751" s="10" t="inlineStr">
+      <c r="F751" s="12" t="inlineStr">
         <is>
           <t>F-14691</t>
         </is>
@@ -36178,7 +36190,7 @@
           <t>Serv. Admin</t>
         </is>
       </c>
-      <c r="F752" s="10" t="inlineStr">
+      <c r="F752" s="12" t="inlineStr">
         <is>
           <t>FEE-14766</t>
         </is>
@@ -36226,7 +36238,7 @@
           <t>Arriendo</t>
         </is>
       </c>
-      <c r="F753" s="11" t="inlineStr">
+      <c r="F753" s="13" t="inlineStr">
         <is>
           <t>F-14689</t>
         </is>
@@ -36274,7 +36286,7 @@
           <t>Arriendo</t>
         </is>
       </c>
-      <c r="F754" s="10" t="inlineStr">
+      <c r="F754" s="12" t="inlineStr">
         <is>
           <t>F-14701</t>
         </is>
@@ -36322,7 +36334,7 @@
           <t>Arriendo</t>
         </is>
       </c>
-      <c r="F755" s="11" t="inlineStr">
+      <c r="F755" s="13" t="inlineStr">
         <is>
           <t>F-14717</t>
         </is>
@@ -36370,7 +36382,7 @@
           <t>Serv. Admin</t>
         </is>
       </c>
-      <c r="F756" s="11" t="inlineStr">
+      <c r="F756" s="13" t="inlineStr">
         <is>
           <t>FEE-14743</t>
         </is>
@@ -36418,7 +36430,7 @@
           <t>Arriendo</t>
         </is>
       </c>
-      <c r="F757" s="10" t="inlineStr">
+      <c r="F757" s="12" t="inlineStr">
         <is>
           <t>F-14718</t>
         </is>
@@ -36466,7 +36478,7 @@
           <t>Serv. Admin</t>
         </is>
       </c>
-      <c r="F758" s="10" t="inlineStr">
+      <c r="F758" s="12" t="inlineStr">
         <is>
           <t>FEE-14748</t>
         </is>
@@ -36514,7 +36526,7 @@
           <t>Arriendo</t>
         </is>
       </c>
-      <c r="F759" s="11" t="inlineStr">
+      <c r="F759" s="13" t="inlineStr">
         <is>
           <t>F-14725</t>
         </is>
@@ -36562,7 +36574,7 @@
           <t>Arriendo</t>
         </is>
       </c>
-      <c r="F760" s="11" t="inlineStr">
+      <c r="F760" s="13" t="inlineStr">
         <is>
           <t>F-14726</t>
         </is>
@@ -36610,7 +36622,7 @@
           <t>Arriendo</t>
         </is>
       </c>
-      <c r="F761" s="11" t="inlineStr">
+      <c r="F761" s="13" t="inlineStr">
         <is>
           <t>F-14727</t>
         </is>
@@ -36658,7 +36670,7 @@
           <t>Arriendo</t>
         </is>
       </c>
-      <c r="F762" s="11" t="inlineStr">
+      <c r="F762" s="13" t="inlineStr">
         <is>
           <t>F-14728</t>
         </is>
@@ -36706,7 +36718,7 @@
           <t>Arriendo</t>
         </is>
       </c>
-      <c r="F763" s="11" t="inlineStr">
+      <c r="F763" s="13" t="inlineStr">
         <is>
           <t>F-14729</t>
         </is>
@@ -36754,7 +36766,7 @@
           <t>Habilitación</t>
         </is>
       </c>
-      <c r="F764" s="11" t="inlineStr">
+      <c r="F764" s="13" t="inlineStr">
         <is>
           <t>F-14730</t>
         </is>
@@ -36802,7 +36814,7 @@
           <t>Serv. Admin</t>
         </is>
       </c>
-      <c r="F765" s="11" t="inlineStr">
+      <c r="F765" s="13" t="inlineStr">
         <is>
           <t>FEE-14741</t>
         </is>
@@ -36850,7 +36862,7 @@
           <t>Serv. Admin</t>
         </is>
       </c>
-      <c r="F766" s="11" t="inlineStr">
+      <c r="F766" s="13" t="inlineStr">
         <is>
           <t>FEE-14742</t>
         </is>
@@ -36898,7 +36910,7 @@
           <t>Serv. Admin</t>
         </is>
       </c>
-      <c r="F767" s="11" t="inlineStr">
+      <c r="F767" s="13" t="inlineStr">
         <is>
           <t>FEE-14769</t>
         </is>
@@ -36946,7 +36958,7 @@
           <t>Serv. Admin</t>
         </is>
       </c>
-      <c r="F768" s="11" t="inlineStr">
+      <c r="F768" s="13" t="inlineStr">
         <is>
           <t>FEE-14772</t>
         </is>
@@ -36994,7 +37006,7 @@
           <t>Serv. Admin</t>
         </is>
       </c>
-      <c r="F769" s="11" t="inlineStr">
+      <c r="F769" s="13" t="inlineStr">
         <is>
           <t>FEE-14774</t>
         </is>
@@ -37042,7 +37054,7 @@
           <t>Arriendo</t>
         </is>
       </c>
-      <c r="F770" s="10" t="inlineStr">
+      <c r="F770" s="12" t="inlineStr">
         <is>
           <t>F-46</t>
         </is>
@@ -37090,7 +37102,7 @@
           <t>Arriendo</t>
         </is>
       </c>
-      <c r="F771" s="11" t="inlineStr">
+      <c r="F771" s="13" t="inlineStr">
         <is>
           <t>F-14721</t>
         </is>
@@ -37138,7 +37150,7 @@
           <t>Serv. Admin</t>
         </is>
       </c>
-      <c r="F772" s="11" t="inlineStr">
+      <c r="F772" s="13" t="inlineStr">
         <is>
           <t>FEE-14745</t>
         </is>
@@ -37186,7 +37198,7 @@
           <t>Arriendo</t>
         </is>
       </c>
-      <c r="F773" s="10" t="inlineStr">
+      <c r="F773" s="12" t="inlineStr">
         <is>
           <t>F-14714</t>
         </is>
@@ -37234,7 +37246,7 @@
           <t>Serv. Admin</t>
         </is>
       </c>
-      <c r="F774" s="10" t="inlineStr">
+      <c r="F774" s="12" t="inlineStr">
         <is>
           <t>FEE-14744</t>
         </is>
@@ -37282,7 +37294,7 @@
           <t>Arriendo</t>
         </is>
       </c>
-      <c r="F775" s="11" t="inlineStr">
+      <c r="F775" s="13" t="inlineStr">
         <is>
           <t>F-14719</t>
         </is>
@@ -37330,7 +37342,7 @@
           <t>Arriendo</t>
         </is>
       </c>
-      <c r="F776" s="10" t="inlineStr">
+      <c r="F776" s="12" t="inlineStr">
         <is>
           <t>F-14712</t>
         </is>
@@ -37378,7 +37390,7 @@
           <t>Serv. Admin</t>
         </is>
       </c>
-      <c r="F777" s="10" t="inlineStr">
+      <c r="F777" s="12" t="inlineStr">
         <is>
           <t>FEE-14765</t>
         </is>
@@ -37426,7 +37438,7 @@
           <t>Arriendo</t>
         </is>
       </c>
-      <c r="F778" s="11" t="inlineStr">
+      <c r="F778" s="13" t="inlineStr">
         <is>
           <t>F-14707</t>
         </is>
@@ -37474,7 +37486,7 @@
           <t>Serv. Admin</t>
         </is>
       </c>
-      <c r="F779" s="11" t="inlineStr">
+      <c r="F779" s="13" t="inlineStr">
         <is>
           <t>FEE-14763</t>
         </is>
@@ -37522,7 +37534,7 @@
           <t>Arriendo</t>
         </is>
       </c>
-      <c r="F780" s="10" t="inlineStr">
+      <c r="F780" s="12" t="inlineStr">
         <is>
           <t>F-14713</t>
         </is>
@@ -37570,7 +37582,7 @@
           <t>Serv. Admin</t>
         </is>
       </c>
-      <c r="F781" s="10" t="inlineStr">
+      <c r="F781" s="12" t="inlineStr">
         <is>
           <t>FEE-14758</t>
         </is>
@@ -37618,7 +37630,7 @@
           <t>Arriendo</t>
         </is>
       </c>
-      <c r="F782" s="11" t="inlineStr">
+      <c r="F782" s="13" t="inlineStr">
         <is>
           <t>F-14716</t>
         </is>
@@ -37666,7 +37678,7 @@
           <t>Arriendo</t>
         </is>
       </c>
-      <c r="F783" s="10" t="inlineStr">
+      <c r="F783" s="12" t="inlineStr">
         <is>
           <t>F-14706</t>
         </is>
@@ -37714,7 +37726,7 @@
           <t>Arriendo</t>
         </is>
       </c>
-      <c r="F784" s="11" t="inlineStr">
+      <c r="F784" s="13" t="inlineStr">
         <is>
           <t>F-14702</t>
         </is>
@@ -37762,7 +37774,7 @@
           <t>Arriendo</t>
         </is>
       </c>
-      <c r="F785" s="10" t="inlineStr">
+      <c r="F785" s="12" t="inlineStr">
         <is>
           <t>F-14715</t>
         </is>
@@ -37810,7 +37822,7 @@
           <t>Serv. Admin</t>
         </is>
       </c>
-      <c r="F786" s="10" t="inlineStr">
+      <c r="F786" s="12" t="inlineStr">
         <is>
           <t>FEE-14754</t>
         </is>
@@ -37858,7 +37870,7 @@
           <t>Arriendo</t>
         </is>
       </c>
-      <c r="F787" s="11" t="inlineStr">
+      <c r="F787" s="13" t="inlineStr">
         <is>
           <t>F-14720</t>
         </is>
@@ -37906,7 +37918,7 @@
           <t>Arriendo</t>
         </is>
       </c>
-      <c r="F788" s="10" t="inlineStr">
+      <c r="F788" s="12" t="inlineStr">
         <is>
           <t>F-14731</t>
         </is>
@@ -37954,7 +37966,7 @@
           <t>Arriendo</t>
         </is>
       </c>
-      <c r="F789" s="10" t="inlineStr">
+      <c r="F789" s="12" t="inlineStr">
         <is>
           <t>F-14733</t>
         </is>
@@ -38002,7 +38014,7 @@
           <t>Arriendo</t>
         </is>
       </c>
-      <c r="F790" s="11" t="inlineStr">
+      <c r="F790" s="13" t="inlineStr">
         <is>
           <t>F-14704</t>
         </is>
@@ -38050,7 +38062,7 @@
           <t>Arriendo</t>
         </is>
       </c>
-      <c r="F791" s="10" t="inlineStr">
+      <c r="F791" s="12" t="inlineStr">
         <is>
           <t>F-14723</t>
         </is>
@@ -38098,7 +38110,7 @@
           <t>Arriendo</t>
         </is>
       </c>
-      <c r="F792" s="11" t="inlineStr">
+      <c r="F792" s="13" t="inlineStr">
         <is>
           <t>F-14705</t>
         </is>
@@ -38146,7 +38158,7 @@
           <t>Serv. Admin</t>
         </is>
       </c>
-      <c r="F793" s="11" t="inlineStr">
+      <c r="F793" s="13" t="inlineStr">
         <is>
           <t>FEE-14771</t>
         </is>
@@ -38194,7 +38206,7 @@
           <t>Arriendo</t>
         </is>
       </c>
-      <c r="F794" s="10" t="inlineStr">
+      <c r="F794" s="12" t="inlineStr">
         <is>
           <t>F-14724</t>
         </is>
@@ -38242,7 +38254,7 @@
           <t>Serv. Admin</t>
         </is>
       </c>
-      <c r="F795" s="10" t="inlineStr">
+      <c r="F795" s="12" t="inlineStr">
         <is>
           <t>FEE-14770</t>
         </is>
@@ -38290,7 +38302,7 @@
           <t>Arriendo</t>
         </is>
       </c>
-      <c r="F796" s="11" t="inlineStr">
+      <c r="F796" s="13" t="inlineStr">
         <is>
           <t>F-14708</t>
         </is>
@@ -38338,7 +38350,7 @@
           <t>Arriendo</t>
         </is>
       </c>
-      <c r="F797" s="11" t="inlineStr">
+      <c r="F797" s="13" t="inlineStr">
         <is>
           <t>F-14709</t>
         </is>
@@ -38386,7 +38398,7 @@
           <t>Serv. Admin</t>
         </is>
       </c>
-      <c r="F798" s="11" t="inlineStr">
+      <c r="F798" s="13" t="inlineStr">
         <is>
           <t>FEE-14749</t>
         </is>
@@ -38434,7 +38446,7 @@
           <t>Serv. Admin</t>
         </is>
       </c>
-      <c r="F799" s="11" t="inlineStr">
+      <c r="F799" s="13" t="inlineStr">
         <is>
           <t>FEE-14750</t>
         </is>
@@ -38482,7 +38494,7 @@
           <t>Arriendo</t>
         </is>
       </c>
-      <c r="F800" s="10" t="inlineStr">
+      <c r="F800" s="12" t="inlineStr">
         <is>
           <t>F-47</t>
         </is>
@@ -38530,7 +38542,7 @@
           <t>Serv. Admin</t>
         </is>
       </c>
-      <c r="F801" s="10" t="inlineStr">
+      <c r="F801" s="12" t="inlineStr">
         <is>
           <t>FEE-14767</t>
         </is>
@@ -38578,7 +38590,7 @@
           <t>Arriendo</t>
         </is>
       </c>
-      <c r="F802" s="11" t="inlineStr">
+      <c r="F802" s="13" t="inlineStr">
         <is>
           <t>F-14711</t>
         </is>
@@ -38626,7 +38638,7 @@
           <t>Serv. Admin</t>
         </is>
       </c>
-      <c r="F803" s="11" t="inlineStr">
+      <c r="F803" s="13" t="inlineStr">
         <is>
           <t>FEE-14779</t>
         </is>
@@ -38672,7 +38684,7 @@
           <t>Arriendo</t>
         </is>
       </c>
-      <c r="F804" s="10" t="inlineStr">
+      <c r="F804" s="12" t="inlineStr">
         <is>
           <t>F-14703</t>
         </is>
@@ -38720,7 +38732,7 @@
           <t>Arriendo</t>
         </is>
       </c>
-      <c r="F805" s="11" t="inlineStr">
+      <c r="F805" s="13" t="inlineStr">
         <is>
           <t>F-14710</t>
         </is>
@@ -38768,7 +38780,7 @@
           <t>Arriendo</t>
         </is>
       </c>
-      <c r="F806" s="10" t="inlineStr">
+      <c r="F806" s="12" t="inlineStr">
         <is>
           <t>F-14722</t>
         </is>
@@ -38816,7 +38828,7 @@
           <t>Arriendo</t>
         </is>
       </c>
-      <c r="F807" s="11" t="inlineStr">
+      <c r="F807" s="13" t="inlineStr">
         <is>
           <t>F-45</t>
         </is>
@@ -38864,7 +38876,7 @@
           <t>Arriendo</t>
         </is>
       </c>
-      <c r="F808" s="10" t="inlineStr">
+      <c r="F808" s="12" t="inlineStr">
         <is>
           <t>F-44</t>
         </is>
@@ -38912,7 +38924,7 @@
           <t>Arriendo</t>
         </is>
       </c>
-      <c r="F809" s="10" t="inlineStr">
+      <c r="F809" s="12" t="inlineStr">
         <is>
           <t>F-48</t>
         </is>
@@ -38960,7 +38972,7 @@
           <t>Serv. Admin</t>
         </is>
       </c>
-      <c r="F810" s="10" t="inlineStr">
+      <c r="F810" s="12" t="inlineStr">
         <is>
           <t>FEE-14747</t>
         </is>
@@ -39008,7 +39020,7 @@
           <t>Serv. Admin</t>
         </is>
       </c>
-      <c r="F811" s="11" t="inlineStr">
+      <c r="F811" s="13" t="inlineStr">
         <is>
           <t>FEE-14746</t>
         </is>
@@ -39056,7 +39068,7 @@
           <t>Serv. Admin</t>
         </is>
       </c>
-      <c r="F812" s="10" t="inlineStr">
+      <c r="F812" s="12" t="inlineStr">
         <is>
           <t>FEE-14778</t>
         </is>
@@ -39102,7 +39114,7 @@
           <t>Serv. Admin</t>
         </is>
       </c>
-      <c r="F813" s="11" t="inlineStr">
+      <c r="F813" s="13" t="inlineStr">
         <is>
           <t>FEE-14775</t>
         </is>
@@ -39150,7 +39162,7 @@
           <t>Arriendo</t>
         </is>
       </c>
-      <c r="F814" s="10" t="inlineStr">
+      <c r="F814" s="12" t="inlineStr">
         <is>
           <t>F-43</t>
         </is>
